--- a/artfynd/A 11097-2024 artfynd.xlsx
+++ b/artfynd/A 11097-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124808156</v>
+        <v>124808183</v>
       </c>
       <c r="B2" t="n">
-        <v>57513</v>
+        <v>91299</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>466027</v>
+        <v>465924</v>
       </c>
       <c r="R2" t="n">
-        <v>7055757</v>
+        <v>7055722</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124808148</v>
+        <v>124808159</v>
       </c>
       <c r="B3" t="n">
         <v>57513</v>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466190</v>
+        <v>465930</v>
       </c>
       <c r="R3" t="n">
-        <v>7055952</v>
+        <v>7055704</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +857,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124808145</v>
+        <v>124808154</v>
       </c>
       <c r="B4" t="n">
         <v>57513</v>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>466217</v>
+        <v>466093</v>
       </c>
       <c r="R4" t="n">
-        <v>7056120</v>
+        <v>7055760</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124808183</v>
+        <v>124808189</v>
       </c>
       <c r="B5" t="n">
-        <v>91299</v>
+        <v>91030</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465924</v>
+        <v>466286</v>
       </c>
       <c r="R5" t="n">
-        <v>7055722</v>
+        <v>7056084</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,7 +1093,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124808136</v>
+        <v>124808155</v>
       </c>
       <c r="B6" t="n">
         <v>57513</v>
@@ -1138,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466032</v>
+        <v>466025</v>
       </c>
       <c r="R6" t="n">
-        <v>7055802</v>
+        <v>7055769</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,7 +1200,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124808193</v>
+        <v>124808190</v>
       </c>
       <c r="B7" t="n">
         <v>91030</v>
@@ -1245,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466155</v>
+        <v>466147</v>
       </c>
       <c r="R7" t="n">
-        <v>7055735</v>
+        <v>7056067</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1307,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124808138</v>
+        <v>124808193</v>
       </c>
       <c r="B8" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,21 +1318,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1347,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466123</v>
+        <v>466155</v>
       </c>
       <c r="R8" t="n">
-        <v>7055839</v>
+        <v>7055735</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1383,11 +1378,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1414,7 +1404,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124808134</v>
+        <v>124808148</v>
       </c>
       <c r="B9" t="n">
         <v>57513</v>
@@ -1454,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466020</v>
+        <v>466190</v>
       </c>
       <c r="R9" t="n">
-        <v>7055801</v>
+        <v>7055952</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1521,7 +1511,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124808125</v>
+        <v>124808145</v>
       </c>
       <c r="B10" t="n">
         <v>57513</v>
@@ -1555,24 +1545,16 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Åkerån, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466019</v>
+        <v>466217</v>
       </c>
       <c r="R10" t="n">
-        <v>7055741</v>
+        <v>7056120</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1609,7 +1591,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Bohål ca 6m upp i bruten gran</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1636,10 +1618,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124808194</v>
+        <v>124808134</v>
       </c>
       <c r="B11" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1652,21 +1634,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1679,7 +1661,7 @@
         <v>466020</v>
       </c>
       <c r="R11" t="n">
-        <v>7055742</v>
+        <v>7055801</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1712,6 +1694,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1738,7 +1725,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124808190</v>
+        <v>124808195</v>
       </c>
       <c r="B12" t="n">
         <v>91030</v>
@@ -1778,10 +1765,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466147</v>
+        <v>466026</v>
       </c>
       <c r="R12" t="n">
-        <v>7056067</v>
+        <v>7055714</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1840,7 +1827,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124808139</v>
+        <v>124808125</v>
       </c>
       <c r="B13" t="n">
         <v>57513</v>
@@ -1874,16 +1861,24 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Åkerån, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466126</v>
+        <v>466019</v>
       </c>
       <c r="R13" t="n">
-        <v>7055914</v>
+        <v>7055741</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1920,7 +1915,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Bohål ca 6m upp i bruten gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1947,10 +1942,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124808140</v>
+        <v>124808194</v>
       </c>
       <c r="B14" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1963,21 +1958,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1987,10 +1982,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>466113</v>
+        <v>466020</v>
       </c>
       <c r="R14" t="n">
-        <v>7055912</v>
+        <v>7055742</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2023,11 +2018,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2054,7 +2044,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124808146</v>
+        <v>124808132</v>
       </c>
       <c r="B15" t="n">
         <v>57513</v>
@@ -2094,10 +2084,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>466210</v>
+        <v>466002</v>
       </c>
       <c r="R15" t="n">
-        <v>7056130</v>
+        <v>7055866</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2161,7 +2151,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124808152</v>
+        <v>124808131</v>
       </c>
       <c r="B16" t="n">
         <v>57513</v>
@@ -2201,10 +2191,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466072</v>
+        <v>466023</v>
       </c>
       <c r="R16" t="n">
-        <v>7055589</v>
+        <v>7055886</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2268,7 +2258,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124808132</v>
+        <v>124808136</v>
       </c>
       <c r="B17" t="n">
         <v>57513</v>
@@ -2308,10 +2298,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466002</v>
+        <v>466032</v>
       </c>
       <c r="R17" t="n">
-        <v>7055866</v>
+        <v>7055802</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2375,7 +2365,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124808131</v>
+        <v>124808139</v>
       </c>
       <c r="B18" t="n">
         <v>57513</v>
@@ -2415,10 +2405,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466023</v>
+        <v>466126</v>
       </c>
       <c r="R18" t="n">
-        <v>7055886</v>
+        <v>7055914</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2455,7 +2445,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2482,10 +2472,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124808189</v>
+        <v>124808182</v>
       </c>
       <c r="B19" t="n">
-        <v>91030</v>
+        <v>79892</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2498,21 +2488,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2522,10 +2512,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466286</v>
+        <v>466191</v>
       </c>
       <c r="R19" t="n">
-        <v>7056084</v>
+        <v>7055781</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2584,7 +2574,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124808129</v>
+        <v>124808138</v>
       </c>
       <c r="B20" t="n">
         <v>57513</v>
@@ -2624,10 +2614,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>465997</v>
+        <v>466123</v>
       </c>
       <c r="R20" t="n">
-        <v>7055926</v>
+        <v>7055839</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2664,7 +2654,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2691,7 +2681,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124808150</v>
+        <v>124808156</v>
       </c>
       <c r="B21" t="n">
         <v>57513</v>
@@ -2731,10 +2721,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>466187</v>
+        <v>466027</v>
       </c>
       <c r="R21" t="n">
-        <v>7055846</v>
+        <v>7055757</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2771,7 +2761,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2798,10 +2788,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124808160</v>
+        <v>124808185</v>
       </c>
       <c r="B22" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2814,21 +2804,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2838,10 +2828,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>465939</v>
+        <v>466191</v>
       </c>
       <c r="R22" t="n">
-        <v>7055717</v>
+        <v>7055781</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2874,11 +2864,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2905,7 +2890,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124808135</v>
+        <v>124808152</v>
       </c>
       <c r="B23" t="n">
         <v>57513</v>
@@ -2945,10 +2930,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>466024</v>
+        <v>466072</v>
       </c>
       <c r="R23" t="n">
-        <v>7055801</v>
+        <v>7055589</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3012,7 +2997,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124808126</v>
+        <v>124808157</v>
       </c>
       <c r="B24" t="n">
         <v>57513</v>
@@ -3052,10 +3037,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>465931</v>
+        <v>466023</v>
       </c>
       <c r="R24" t="n">
-        <v>7055792</v>
+        <v>7055706</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3226,7 +3211,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124808147</v>
+        <v>124808144</v>
       </c>
       <c r="B26" t="n">
         <v>57513</v>
@@ -3266,10 +3251,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466151</v>
+        <v>466231</v>
       </c>
       <c r="R26" t="n">
-        <v>7055999</v>
+        <v>7056150</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3333,10 +3318,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124808185</v>
+        <v>124808140</v>
       </c>
       <c r="B27" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3349,21 +3334,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3373,10 +3358,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466191</v>
+        <v>466113</v>
       </c>
       <c r="R27" t="n">
-        <v>7055781</v>
+        <v>7055912</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3409,6 +3394,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3435,10 +3425,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124808123</v>
+        <v>124808141</v>
       </c>
       <c r="B28" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3451,21 +3441,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3475,10 +3465,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>465924</v>
+        <v>466172</v>
       </c>
       <c r="R28" t="n">
-        <v>7055720</v>
+        <v>7056129</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3511,6 +3501,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3537,7 +3532,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124808159</v>
+        <v>124808127</v>
       </c>
       <c r="B29" t="n">
         <v>57513</v>
@@ -3577,10 +3572,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>465930</v>
+        <v>465979</v>
       </c>
       <c r="R29" t="n">
-        <v>7055704</v>
+        <v>7055862</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3617,7 +3612,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3644,10 +3639,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124808141</v>
+        <v>124808184</v>
       </c>
       <c r="B30" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3660,21 +3655,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3684,10 +3679,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>466172</v>
+        <v>466183</v>
       </c>
       <c r="R30" t="n">
-        <v>7056129</v>
+        <v>7056145</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3720,11 +3715,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3751,7 +3741,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124808142</v>
+        <v>124808137</v>
       </c>
       <c r="B31" t="n">
         <v>57513</v>
@@ -3791,10 +3781,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466212</v>
+        <v>466097</v>
       </c>
       <c r="R31" t="n">
-        <v>7056170</v>
+        <v>7055831</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3831,7 +3821,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3858,10 +3848,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124808143</v>
+        <v>124808188</v>
       </c>
       <c r="B32" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3874,21 +3864,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3898,10 +3888,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466291</v>
+        <v>466015</v>
       </c>
       <c r="R32" t="n">
-        <v>7056076</v>
+        <v>7055934</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3934,11 +3924,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3965,10 +3950,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124808187</v>
+        <v>124808135</v>
       </c>
       <c r="B33" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3981,21 +3966,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4005,10 +3990,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>465961</v>
+        <v>466024</v>
       </c>
       <c r="R33" t="n">
-        <v>7055835</v>
+        <v>7055801</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4041,6 +4026,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4067,7 +4057,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124808137</v>
+        <v>124808146</v>
       </c>
       <c r="B34" t="n">
         <v>57513</v>
@@ -4107,10 +4097,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>466097</v>
+        <v>466210</v>
       </c>
       <c r="R34" t="n">
-        <v>7055831</v>
+        <v>7056130</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4147,7 +4137,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4174,7 +4164,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124808151</v>
+        <v>124808162</v>
       </c>
       <c r="B35" t="n">
         <v>57513</v>
@@ -4214,10 +4204,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>466148</v>
+        <v>465856</v>
       </c>
       <c r="R35" t="n">
-        <v>7055732</v>
+        <v>7055738</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4281,7 +4271,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124808144</v>
+        <v>124808126</v>
       </c>
       <c r="B36" t="n">
         <v>57513</v>
@@ -4321,10 +4311,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>466231</v>
+        <v>465931</v>
       </c>
       <c r="R36" t="n">
-        <v>7056150</v>
+        <v>7055792</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4388,10 +4378,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124808184</v>
+        <v>124808151</v>
       </c>
       <c r="B37" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4404,21 +4394,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4428,10 +4418,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>466183</v>
+        <v>466148</v>
       </c>
       <c r="R37" t="n">
-        <v>7056145</v>
+        <v>7055732</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4464,6 +4454,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4490,10 +4485,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124808188</v>
+        <v>124808161</v>
       </c>
       <c r="B38" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4506,21 +4501,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4530,10 +4525,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>466015</v>
+        <v>465859</v>
       </c>
       <c r="R38" t="n">
-        <v>7055934</v>
+        <v>7055744</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4566,6 +4561,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4592,7 +4592,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124808154</v>
+        <v>124808142</v>
       </c>
       <c r="B39" t="n">
         <v>57513</v>
@@ -4632,10 +4632,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>466093</v>
+        <v>466212</v>
       </c>
       <c r="R39" t="n">
-        <v>7055760</v>
+        <v>7056170</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4699,7 +4699,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124808161</v>
+        <v>124808160</v>
       </c>
       <c r="B40" t="n">
         <v>57513</v>
@@ -4739,10 +4739,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>465859</v>
+        <v>465939</v>
       </c>
       <c r="R40" t="n">
-        <v>7055744</v>
+        <v>7055717</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4806,7 +4806,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124808162</v>
+        <v>124808147</v>
       </c>
       <c r="B41" t="n">
         <v>57513</v>
@@ -4846,10 +4846,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>465856</v>
+        <v>466151</v>
       </c>
       <c r="R41" t="n">
-        <v>7055738</v>
+        <v>7055999</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4913,10 +4913,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124808133</v>
+        <v>124808123</v>
       </c>
       <c r="B42" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4929,21 +4929,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4953,10 +4953,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>466022</v>
+        <v>465924</v>
       </c>
       <c r="R42" t="n">
-        <v>7055840</v>
+        <v>7055720</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4989,11 +4989,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5020,7 +5015,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124808155</v>
+        <v>124808149</v>
       </c>
       <c r="B43" t="n">
         <v>57513</v>
@@ -5060,10 +5055,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>466025</v>
+        <v>466219</v>
       </c>
       <c r="R43" t="n">
-        <v>7055769</v>
+        <v>7055842</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5100,7 +5095,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5127,7 +5122,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124808157</v>
+        <v>124808129</v>
       </c>
       <c r="B44" t="n">
         <v>57513</v>
@@ -5167,10 +5162,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>466023</v>
+        <v>465997</v>
       </c>
       <c r="R44" t="n">
-        <v>7055706</v>
+        <v>7055926</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5207,7 +5202,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5234,10 +5229,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124808149</v>
+        <v>124808187</v>
       </c>
       <c r="B45" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5250,21 +5245,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5274,10 +5269,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>466219</v>
+        <v>465961</v>
       </c>
       <c r="R45" t="n">
-        <v>7055842</v>
+        <v>7055835</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5310,11 +5305,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5341,10 +5331,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124808195</v>
+        <v>124808133</v>
       </c>
       <c r="B46" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5357,21 +5347,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5381,10 +5371,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>466026</v>
+        <v>466022</v>
       </c>
       <c r="R46" t="n">
-        <v>7055714</v>
+        <v>7055840</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5417,6 +5407,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5443,7 +5438,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124808127</v>
+        <v>124808143</v>
       </c>
       <c r="B47" t="n">
         <v>57513</v>
@@ -5483,10 +5478,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>465979</v>
+        <v>466291</v>
       </c>
       <c r="R47" t="n">
-        <v>7055862</v>
+        <v>7056076</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5550,10 +5545,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124808182</v>
+        <v>124808150</v>
       </c>
       <c r="B48" t="n">
-        <v>79892</v>
+        <v>57513</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5566,21 +5561,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5590,10 +5585,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>466191</v>
+        <v>466187</v>
       </c>
       <c r="R48" t="n">
-        <v>7055781</v>
+        <v>7055846</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5626,6 +5621,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">

--- a/artfynd/A 11097-2024 artfynd.xlsx
+++ b/artfynd/A 11097-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124808183</v>
+        <v>124808193</v>
       </c>
       <c r="B2" t="n">
-        <v>91299</v>
+        <v>91030</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>465924</v>
+        <v>466155</v>
       </c>
       <c r="R2" t="n">
-        <v>7055722</v>
+        <v>7055735</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124808159</v>
+        <v>124808144</v>
       </c>
       <c r="B3" t="n">
         <v>57513</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465930</v>
+        <v>466231</v>
       </c>
       <c r="R3" t="n">
-        <v>7055704</v>
+        <v>7056150</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124808154</v>
+        <v>124808159</v>
       </c>
       <c r="B4" t="n">
         <v>57513</v>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>466093</v>
+        <v>465930</v>
       </c>
       <c r="R4" t="n">
-        <v>7055760</v>
+        <v>7055704</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +964,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124808189</v>
+        <v>124808147</v>
       </c>
       <c r="B5" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>466286</v>
+        <v>466151</v>
       </c>
       <c r="R5" t="n">
-        <v>7056084</v>
+        <v>7055999</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,6 +1067,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,7 +1098,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124808155</v>
+        <v>124808142</v>
       </c>
       <c r="B6" t="n">
         <v>57513</v>
@@ -1133,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466025</v>
+        <v>466212</v>
       </c>
       <c r="R6" t="n">
-        <v>7055769</v>
+        <v>7056170</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124808190</v>
+        <v>124808157</v>
       </c>
       <c r="B7" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1216,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466147</v>
+        <v>466023</v>
       </c>
       <c r="R7" t="n">
-        <v>7056067</v>
+        <v>7055706</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1276,6 +1281,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1302,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124808193</v>
+        <v>124808129</v>
       </c>
       <c r="B8" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1318,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466155</v>
+        <v>465997</v>
       </c>
       <c r="R8" t="n">
-        <v>7055735</v>
+        <v>7055926</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1378,6 +1388,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1404,7 +1419,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124808148</v>
+        <v>124808139</v>
       </c>
       <c r="B9" t="n">
         <v>57513</v>
@@ -1444,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466190</v>
+        <v>466126</v>
       </c>
       <c r="R9" t="n">
-        <v>7055952</v>
+        <v>7055914</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1484,7 +1499,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1511,7 +1526,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124808145</v>
+        <v>124808151</v>
       </c>
       <c r="B10" t="n">
         <v>57513</v>
@@ -1551,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466217</v>
+        <v>466148</v>
       </c>
       <c r="R10" t="n">
-        <v>7056120</v>
+        <v>7055732</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1618,7 +1633,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124808134</v>
+        <v>124808131</v>
       </c>
       <c r="B11" t="n">
         <v>57513</v>
@@ -1658,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466020</v>
+        <v>466023</v>
       </c>
       <c r="R11" t="n">
-        <v>7055801</v>
+        <v>7055886</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1725,10 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124808195</v>
+        <v>124808133</v>
       </c>
       <c r="B12" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1741,21 +1756,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1765,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466026</v>
+        <v>466022</v>
       </c>
       <c r="R12" t="n">
-        <v>7055714</v>
+        <v>7055840</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1801,6 +1816,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1827,7 +1847,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124808125</v>
+        <v>124808154</v>
       </c>
       <c r="B13" t="n">
         <v>57513</v>
@@ -1861,24 +1881,16 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Åkerån, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466019</v>
+        <v>466093</v>
       </c>
       <c r="R13" t="n">
-        <v>7055741</v>
+        <v>7055760</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1915,7 +1927,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Bohål ca 6m upp i bruten gran</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1942,10 +1954,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124808194</v>
+        <v>124808138</v>
       </c>
       <c r="B14" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1958,21 +1970,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1982,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>466020</v>
+        <v>466123</v>
       </c>
       <c r="R14" t="n">
-        <v>7055742</v>
+        <v>7055839</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2018,6 +2030,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2044,7 +2061,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124808132</v>
+        <v>124808140</v>
       </c>
       <c r="B15" t="n">
         <v>57513</v>
@@ -2084,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>466002</v>
+        <v>466113</v>
       </c>
       <c r="R15" t="n">
-        <v>7055866</v>
+        <v>7055912</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2151,7 +2168,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124808131</v>
+        <v>124808135</v>
       </c>
       <c r="B16" t="n">
         <v>57513</v>
@@ -2191,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466023</v>
+        <v>466024</v>
       </c>
       <c r="R16" t="n">
-        <v>7055886</v>
+        <v>7055801</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2258,10 +2275,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124808136</v>
+        <v>124808182</v>
       </c>
       <c r="B17" t="n">
-        <v>57513</v>
+        <v>79892</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2274,21 +2291,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2298,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466032</v>
+        <v>466191</v>
       </c>
       <c r="R17" t="n">
-        <v>7055802</v>
+        <v>7055781</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2334,11 +2351,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2365,7 +2377,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124808139</v>
+        <v>124808145</v>
       </c>
       <c r="B18" t="n">
         <v>57513</v>
@@ -2405,10 +2417,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466126</v>
+        <v>466217</v>
       </c>
       <c r="R18" t="n">
-        <v>7055914</v>
+        <v>7056120</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2445,7 +2457,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2472,10 +2484,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124808182</v>
+        <v>124808127</v>
       </c>
       <c r="B19" t="n">
-        <v>79892</v>
+        <v>57513</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2488,21 +2500,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2512,10 +2524,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466191</v>
+        <v>465979</v>
       </c>
       <c r="R19" t="n">
-        <v>7055781</v>
+        <v>7055862</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2548,6 +2560,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2574,10 +2591,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124808138</v>
+        <v>124808184</v>
       </c>
       <c r="B20" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2590,21 +2607,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2614,10 +2631,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466123</v>
+        <v>466183</v>
       </c>
       <c r="R20" t="n">
-        <v>7055839</v>
+        <v>7056145</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2650,11 +2667,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2681,10 +2693,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124808156</v>
+        <v>124808183</v>
       </c>
       <c r="B21" t="n">
-        <v>57513</v>
+        <v>91299</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2697,21 +2709,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2721,10 +2733,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>466027</v>
+        <v>465924</v>
       </c>
       <c r="R21" t="n">
-        <v>7055757</v>
+        <v>7055722</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2757,11 +2769,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2788,10 +2795,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124808185</v>
+        <v>124808125</v>
       </c>
       <c r="B22" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2804,34 +2811,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Åkerån, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>466191</v>
+        <v>466019</v>
       </c>
       <c r="R22" t="n">
-        <v>7055781</v>
+        <v>7055741</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2864,6 +2879,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Bohål ca 6m upp i bruten gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2890,7 +2910,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124808152</v>
+        <v>124808156</v>
       </c>
       <c r="B23" t="n">
         <v>57513</v>
@@ -2930,10 +2950,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>466072</v>
+        <v>466027</v>
       </c>
       <c r="R23" t="n">
-        <v>7055589</v>
+        <v>7055757</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2997,7 +3017,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124808157</v>
+        <v>124808162</v>
       </c>
       <c r="B24" t="n">
         <v>57513</v>
@@ -3037,10 +3057,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>466023</v>
+        <v>465856</v>
       </c>
       <c r="R24" t="n">
-        <v>7055706</v>
+        <v>7055738</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3104,10 +3124,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124808158</v>
+        <v>124808195</v>
       </c>
       <c r="B25" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3120,21 +3140,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3144,10 +3164,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>465957</v>
+        <v>466026</v>
       </c>
       <c r="R25" t="n">
-        <v>7055698</v>
+        <v>7055714</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3180,11 +3200,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3211,7 +3226,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124808144</v>
+        <v>124808152</v>
       </c>
       <c r="B26" t="n">
         <v>57513</v>
@@ -3251,10 +3266,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466231</v>
+        <v>466072</v>
       </c>
       <c r="R26" t="n">
-        <v>7056150</v>
+        <v>7055589</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3318,10 +3333,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124808140</v>
+        <v>124808190</v>
       </c>
       <c r="B27" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3334,21 +3349,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3358,10 +3373,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466113</v>
+        <v>466147</v>
       </c>
       <c r="R27" t="n">
-        <v>7055912</v>
+        <v>7056067</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3394,11 +3409,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3425,7 +3435,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124808141</v>
+        <v>124808149</v>
       </c>
       <c r="B28" t="n">
         <v>57513</v>
@@ -3465,10 +3475,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466172</v>
+        <v>466219</v>
       </c>
       <c r="R28" t="n">
-        <v>7056129</v>
+        <v>7055842</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3505,7 +3515,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3532,7 +3542,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124808127</v>
+        <v>124808143</v>
       </c>
       <c r="B29" t="n">
         <v>57513</v>
@@ -3572,10 +3582,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>465979</v>
+        <v>466291</v>
       </c>
       <c r="R29" t="n">
-        <v>7055862</v>
+        <v>7056076</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3639,10 +3649,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124808184</v>
+        <v>124808189</v>
       </c>
       <c r="B30" t="n">
-        <v>79891</v>
+        <v>91030</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3655,21 +3665,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3679,10 +3689,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>466183</v>
+        <v>466286</v>
       </c>
       <c r="R30" t="n">
-        <v>7056145</v>
+        <v>7056084</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3741,10 +3751,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124808137</v>
+        <v>124808185</v>
       </c>
       <c r="B31" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3757,21 +3767,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3781,10 +3791,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466097</v>
+        <v>466191</v>
       </c>
       <c r="R31" t="n">
-        <v>7055831</v>
+        <v>7055781</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3817,11 +3827,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3848,10 +3853,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124808188</v>
+        <v>124808161</v>
       </c>
       <c r="B32" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3864,21 +3869,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3888,10 +3893,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466015</v>
+        <v>465859</v>
       </c>
       <c r="R32" t="n">
-        <v>7055934</v>
+        <v>7055744</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3924,6 +3929,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3950,10 +3960,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124808135</v>
+        <v>124808187</v>
       </c>
       <c r="B33" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3966,21 +3976,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3990,10 +4000,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466024</v>
+        <v>465961</v>
       </c>
       <c r="R33" t="n">
-        <v>7055801</v>
+        <v>7055835</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4026,11 +4036,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4057,7 +4062,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124808146</v>
+        <v>124808160</v>
       </c>
       <c r="B34" t="n">
         <v>57513</v>
@@ -4097,10 +4102,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>466210</v>
+        <v>465939</v>
       </c>
       <c r="R34" t="n">
-        <v>7056130</v>
+        <v>7055717</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4164,7 +4169,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124808162</v>
+        <v>124808158</v>
       </c>
       <c r="B35" t="n">
         <v>57513</v>
@@ -4204,10 +4209,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>465856</v>
+        <v>465957</v>
       </c>
       <c r="R35" t="n">
-        <v>7055738</v>
+        <v>7055698</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4271,7 +4276,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124808126</v>
+        <v>124808155</v>
       </c>
       <c r="B36" t="n">
         <v>57513</v>
@@ -4311,10 +4316,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>465931</v>
+        <v>466025</v>
       </c>
       <c r="R36" t="n">
-        <v>7055792</v>
+        <v>7055769</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4378,7 +4383,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124808151</v>
+        <v>124808134</v>
       </c>
       <c r="B37" t="n">
         <v>57513</v>
@@ -4418,10 +4423,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>466148</v>
+        <v>466020</v>
       </c>
       <c r="R37" t="n">
-        <v>7055732</v>
+        <v>7055801</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4485,7 +4490,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124808161</v>
+        <v>124808148</v>
       </c>
       <c r="B38" t="n">
         <v>57513</v>
@@ -4525,10 +4530,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>465859</v>
+        <v>466190</v>
       </c>
       <c r="R38" t="n">
-        <v>7055744</v>
+        <v>7055952</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4592,7 +4597,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124808142</v>
+        <v>124808141</v>
       </c>
       <c r="B39" t="n">
         <v>57513</v>
@@ -4632,10 +4637,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>466212</v>
+        <v>466172</v>
       </c>
       <c r="R39" t="n">
-        <v>7056170</v>
+        <v>7056129</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4699,7 +4704,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124808160</v>
+        <v>124808136</v>
       </c>
       <c r="B40" t="n">
         <v>57513</v>
@@ -4739,10 +4744,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>465939</v>
+        <v>466032</v>
       </c>
       <c r="R40" t="n">
-        <v>7055717</v>
+        <v>7055802</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4806,7 +4811,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124808147</v>
+        <v>124808126</v>
       </c>
       <c r="B41" t="n">
         <v>57513</v>
@@ -4846,10 +4851,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>466151</v>
+        <v>465931</v>
       </c>
       <c r="R41" t="n">
-        <v>7055999</v>
+        <v>7055792</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4913,10 +4918,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124808123</v>
+        <v>124808132</v>
       </c>
       <c r="B42" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4929,21 +4934,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4953,10 +4958,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>465924</v>
+        <v>466002</v>
       </c>
       <c r="R42" t="n">
-        <v>7055720</v>
+        <v>7055866</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4989,6 +4994,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5015,7 +5025,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124808149</v>
+        <v>124808137</v>
       </c>
       <c r="B43" t="n">
         <v>57513</v>
@@ -5055,10 +5065,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>466219</v>
+        <v>466097</v>
       </c>
       <c r="R43" t="n">
-        <v>7055842</v>
+        <v>7055831</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5122,10 +5132,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124808129</v>
+        <v>124808194</v>
       </c>
       <c r="B44" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5138,21 +5148,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5162,10 +5172,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>465997</v>
+        <v>466020</v>
       </c>
       <c r="R44" t="n">
-        <v>7055926</v>
+        <v>7055742</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5198,11 +5208,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5229,10 +5234,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124808187</v>
+        <v>124808146</v>
       </c>
       <c r="B45" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5245,21 +5250,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5269,10 +5274,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>465961</v>
+        <v>466210</v>
       </c>
       <c r="R45" t="n">
-        <v>7055835</v>
+        <v>7056130</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5305,6 +5310,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5331,10 +5341,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124808133</v>
+        <v>124808188</v>
       </c>
       <c r="B46" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5347,21 +5357,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5371,10 +5381,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>466022</v>
+        <v>466015</v>
       </c>
       <c r="R46" t="n">
-        <v>7055840</v>
+        <v>7055934</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5407,11 +5417,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5438,10 +5443,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124808143</v>
+        <v>124808123</v>
       </c>
       <c r="B47" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5454,21 +5459,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5478,10 +5483,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>466291</v>
+        <v>465924</v>
       </c>
       <c r="R47" t="n">
-        <v>7056076</v>
+        <v>7055720</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5514,11 +5519,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">

--- a/artfynd/A 11097-2024 artfynd.xlsx
+++ b/artfynd/A 11097-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124808193</v>
+        <v>124808144</v>
       </c>
       <c r="B2" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>466155</v>
+        <v>466231</v>
       </c>
       <c r="R2" t="n">
-        <v>7055735</v>
+        <v>7056150</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124808144</v>
+        <v>124808159</v>
       </c>
       <c r="B3" t="n">
         <v>57513</v>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466231</v>
+        <v>465930</v>
       </c>
       <c r="R3" t="n">
-        <v>7056150</v>
+        <v>7055704</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124808159</v>
+        <v>124808147</v>
       </c>
       <c r="B4" t="n">
         <v>57513</v>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465930</v>
+        <v>466151</v>
       </c>
       <c r="R4" t="n">
-        <v>7055704</v>
+        <v>7055999</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124808147</v>
+        <v>124808193</v>
       </c>
       <c r="B5" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>466151</v>
+        <v>466155</v>
       </c>
       <c r="R5" t="n">
-        <v>7055999</v>
+        <v>7055735</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,11 +1072,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -2061,10 +2061,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124808140</v>
+        <v>124808182</v>
       </c>
       <c r="B15" t="n">
-        <v>57513</v>
+        <v>79892</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2077,21 +2077,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>466113</v>
+        <v>466191</v>
       </c>
       <c r="R15" t="n">
-        <v>7055912</v>
+        <v>7055781</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2137,11 +2137,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2168,7 +2163,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124808135</v>
+        <v>124808140</v>
       </c>
       <c r="B16" t="n">
         <v>57513</v>
@@ -2208,10 +2203,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466024</v>
+        <v>466113</v>
       </c>
       <c r="R16" t="n">
-        <v>7055801</v>
+        <v>7055912</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2275,10 +2270,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124808182</v>
+        <v>124808135</v>
       </c>
       <c r="B17" t="n">
-        <v>79892</v>
+        <v>57513</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2291,21 +2286,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2315,10 +2310,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466191</v>
+        <v>466024</v>
       </c>
       <c r="R17" t="n">
-        <v>7055781</v>
+        <v>7055801</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2351,6 +2346,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2591,10 +2591,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124808184</v>
+        <v>124808183</v>
       </c>
       <c r="B20" t="n">
-        <v>79891</v>
+        <v>91299</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2607,21 +2607,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2631,10 +2631,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466183</v>
+        <v>465924</v>
       </c>
       <c r="R20" t="n">
-        <v>7056145</v>
+        <v>7055722</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2693,10 +2693,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124808183</v>
+        <v>124808184</v>
       </c>
       <c r="B21" t="n">
-        <v>91299</v>
+        <v>79891</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2709,21 +2709,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2733,10 +2733,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>465924</v>
+        <v>466183</v>
       </c>
       <c r="R21" t="n">
-        <v>7055722</v>
+        <v>7056145</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3124,10 +3124,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124808195</v>
+        <v>124808152</v>
       </c>
       <c r="B25" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3140,21 +3140,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3164,10 +3164,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>466026</v>
+        <v>466072</v>
       </c>
       <c r="R25" t="n">
-        <v>7055714</v>
+        <v>7055589</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3200,6 +3200,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3226,10 +3231,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124808152</v>
+        <v>124808195</v>
       </c>
       <c r="B26" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3242,21 +3247,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3266,10 +3271,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466072</v>
+        <v>466026</v>
       </c>
       <c r="R26" t="n">
-        <v>7055589</v>
+        <v>7055714</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3302,11 +3307,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3542,10 +3542,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124808143</v>
+        <v>124808189</v>
       </c>
       <c r="B29" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3558,21 +3558,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3582,10 +3582,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466291</v>
+        <v>466286</v>
       </c>
       <c r="R29" t="n">
-        <v>7056076</v>
+        <v>7056084</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3618,11 +3618,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3649,10 +3644,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124808189</v>
+        <v>124808185</v>
       </c>
       <c r="B30" t="n">
-        <v>91030</v>
+        <v>79891</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3665,21 +3660,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3689,10 +3684,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>466286</v>
+        <v>466191</v>
       </c>
       <c r="R30" t="n">
-        <v>7056084</v>
+        <v>7055781</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3751,10 +3746,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124808185</v>
+        <v>124808161</v>
       </c>
       <c r="B31" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3767,21 +3762,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3791,10 +3786,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466191</v>
+        <v>465859</v>
       </c>
       <c r="R31" t="n">
-        <v>7055781</v>
+        <v>7055744</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3827,6 +3822,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3853,7 +3853,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124808161</v>
+        <v>124808143</v>
       </c>
       <c r="B32" t="n">
         <v>57513</v>
@@ -3893,10 +3893,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>465859</v>
+        <v>466291</v>
       </c>
       <c r="R32" t="n">
-        <v>7055744</v>
+        <v>7056076</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -5132,10 +5132,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124808194</v>
+        <v>124808146</v>
       </c>
       <c r="B44" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5148,21 +5148,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5172,10 +5172,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>466020</v>
+        <v>466210</v>
       </c>
       <c r="R44" t="n">
-        <v>7055742</v>
+        <v>7056130</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5208,6 +5208,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5234,10 +5239,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124808146</v>
+        <v>124808194</v>
       </c>
       <c r="B45" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5250,21 +5255,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5274,10 +5279,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>466210</v>
+        <v>466020</v>
       </c>
       <c r="R45" t="n">
-        <v>7056130</v>
+        <v>7055742</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5310,11 +5315,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">

--- a/artfynd/A 11097-2024 artfynd.xlsx
+++ b/artfynd/A 11097-2024 artfynd.xlsx
@@ -3124,10 +3124,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124808152</v>
+        <v>124808195</v>
       </c>
       <c r="B25" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3140,21 +3140,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3164,10 +3164,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>466072</v>
+        <v>466026</v>
       </c>
       <c r="R25" t="n">
-        <v>7055589</v>
+        <v>7055714</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3200,11 +3200,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3231,10 +3226,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124808195</v>
+        <v>124808152</v>
       </c>
       <c r="B26" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3247,21 +3242,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3271,10 +3266,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466026</v>
+        <v>466072</v>
       </c>
       <c r="R26" t="n">
-        <v>7055714</v>
+        <v>7055589</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3307,6 +3302,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 11097-2024 artfynd.xlsx
+++ b/artfynd/A 11097-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124808144</v>
+        <v>124808182</v>
       </c>
       <c r="B2" t="n">
-        <v>57513</v>
+        <v>79892</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>466231</v>
+        <v>466191</v>
       </c>
       <c r="R2" t="n">
-        <v>7056150</v>
+        <v>7055781</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124808159</v>
+        <v>124808190</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465930</v>
+        <v>466147</v>
       </c>
       <c r="R3" t="n">
-        <v>7055704</v>
+        <v>7056067</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124808147</v>
+        <v>124808148</v>
       </c>
       <c r="B4" t="n">
         <v>57513</v>
@@ -929,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>466151</v>
+        <v>466190</v>
       </c>
       <c r="R4" t="n">
-        <v>7055999</v>
+        <v>7055952</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124808193</v>
+        <v>124808151</v>
       </c>
       <c r="B5" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>466155</v>
+        <v>466148</v>
       </c>
       <c r="R5" t="n">
-        <v>7055735</v>
+        <v>7055732</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,6 +1062,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1205,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124808157</v>
+        <v>124808184</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466023</v>
+        <v>466183</v>
       </c>
       <c r="R7" t="n">
-        <v>7055706</v>
+        <v>7056145</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,11 +1276,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,7 +1302,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124808129</v>
+        <v>124808145</v>
       </c>
       <c r="B8" t="n">
         <v>57513</v>
@@ -1352,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>465997</v>
+        <v>466217</v>
       </c>
       <c r="R8" t="n">
-        <v>7055926</v>
+        <v>7056120</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,7 +1382,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,7 +1409,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124808139</v>
+        <v>124808147</v>
       </c>
       <c r="B9" t="n">
         <v>57513</v>
@@ -1459,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466126</v>
+        <v>466151</v>
       </c>
       <c r="R9" t="n">
-        <v>7055914</v>
+        <v>7055999</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,7 +1489,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,7 +1516,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124808151</v>
+        <v>124808133</v>
       </c>
       <c r="B10" t="n">
         <v>57513</v>
@@ -1566,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466148</v>
+        <v>466022</v>
       </c>
       <c r="R10" t="n">
-        <v>7055732</v>
+        <v>7055840</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1633,7 +1623,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124808131</v>
+        <v>124808129</v>
       </c>
       <c r="B11" t="n">
         <v>57513</v>
@@ -1673,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466023</v>
+        <v>465997</v>
       </c>
       <c r="R11" t="n">
-        <v>7055886</v>
+        <v>7055926</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1713,7 +1703,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1740,7 +1730,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124808133</v>
+        <v>124808159</v>
       </c>
       <c r="B12" t="n">
         <v>57513</v>
@@ -1780,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466022</v>
+        <v>465930</v>
       </c>
       <c r="R12" t="n">
-        <v>7055840</v>
+        <v>7055704</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1820,7 +1810,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1847,7 +1837,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124808154</v>
+        <v>124808136</v>
       </c>
       <c r="B13" t="n">
         <v>57513</v>
@@ -1887,10 +1877,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466093</v>
+        <v>466032</v>
       </c>
       <c r="R13" t="n">
-        <v>7055760</v>
+        <v>7055802</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1954,10 +1944,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124808138</v>
+        <v>124808183</v>
       </c>
       <c r="B14" t="n">
-        <v>57513</v>
+        <v>91299</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1970,21 +1960,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,10 +1984,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>466123</v>
+        <v>465924</v>
       </c>
       <c r="R14" t="n">
-        <v>7055839</v>
+        <v>7055722</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2030,11 +2020,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2061,10 +2046,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124808182</v>
+        <v>124808185</v>
       </c>
       <c r="B15" t="n">
-        <v>79892</v>
+        <v>79891</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2077,21 +2062,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2163,10 +2148,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124808140</v>
+        <v>124808193</v>
       </c>
       <c r="B16" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2179,21 +2164,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2203,10 +2188,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466113</v>
+        <v>466155</v>
       </c>
       <c r="R16" t="n">
-        <v>7055912</v>
+        <v>7055735</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2239,11 +2224,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2270,7 +2250,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124808135</v>
+        <v>124808157</v>
       </c>
       <c r="B17" t="n">
         <v>57513</v>
@@ -2310,10 +2290,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466024</v>
+        <v>466023</v>
       </c>
       <c r="R17" t="n">
-        <v>7055801</v>
+        <v>7055706</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2377,7 +2357,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124808145</v>
+        <v>124808150</v>
       </c>
       <c r="B18" t="n">
         <v>57513</v>
@@ -2417,10 +2397,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466217</v>
+        <v>466187</v>
       </c>
       <c r="R18" t="n">
-        <v>7056120</v>
+        <v>7055846</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2457,7 +2437,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2484,10 +2464,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124808127</v>
+        <v>124808194</v>
       </c>
       <c r="B19" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2500,21 +2480,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2524,10 +2504,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>465979</v>
+        <v>466020</v>
       </c>
       <c r="R19" t="n">
-        <v>7055862</v>
+        <v>7055742</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2560,11 +2540,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2591,10 +2566,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124808183</v>
+        <v>124808149</v>
       </c>
       <c r="B20" t="n">
-        <v>91299</v>
+        <v>57513</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2607,21 +2582,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2631,10 +2606,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>465924</v>
+        <v>466219</v>
       </c>
       <c r="R20" t="n">
-        <v>7055722</v>
+        <v>7055842</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2667,6 +2642,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2693,10 +2673,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124808184</v>
+        <v>124808135</v>
       </c>
       <c r="B21" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2709,21 +2689,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2733,10 +2713,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>466183</v>
+        <v>466024</v>
       </c>
       <c r="R21" t="n">
-        <v>7056145</v>
+        <v>7055801</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2769,6 +2749,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2795,7 +2780,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124808125</v>
+        <v>124808161</v>
       </c>
       <c r="B22" t="n">
         <v>57513</v>
@@ -2829,24 +2814,16 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Åkerån, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>466019</v>
+        <v>465859</v>
       </c>
       <c r="R22" t="n">
-        <v>7055741</v>
+        <v>7055744</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2883,7 +2860,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Bohål ca 6m upp i bruten gran</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2910,7 +2887,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124808156</v>
+        <v>124808154</v>
       </c>
       <c r="B23" t="n">
         <v>57513</v>
@@ -2950,10 +2927,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>466027</v>
+        <v>466093</v>
       </c>
       <c r="R23" t="n">
-        <v>7055757</v>
+        <v>7055760</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3017,7 +2994,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124808162</v>
+        <v>124808155</v>
       </c>
       <c r="B24" t="n">
         <v>57513</v>
@@ -3057,10 +3034,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>465856</v>
+        <v>466025</v>
       </c>
       <c r="R24" t="n">
-        <v>7055738</v>
+        <v>7055769</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3124,10 +3101,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124808195</v>
+        <v>124808156</v>
       </c>
       <c r="B25" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3140,21 +3117,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3164,10 +3141,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>466026</v>
+        <v>466027</v>
       </c>
       <c r="R25" t="n">
-        <v>7055714</v>
+        <v>7055757</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3200,6 +3177,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3226,7 +3208,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124808152</v>
+        <v>124808127</v>
       </c>
       <c r="B26" t="n">
         <v>57513</v>
@@ -3266,10 +3248,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466072</v>
+        <v>465979</v>
       </c>
       <c r="R26" t="n">
-        <v>7055589</v>
+        <v>7055862</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3333,10 +3315,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124808190</v>
+        <v>124808138</v>
       </c>
       <c r="B27" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3349,21 +3331,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3373,10 +3355,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466147</v>
+        <v>466123</v>
       </c>
       <c r="R27" t="n">
-        <v>7056067</v>
+        <v>7055839</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3409,6 +3391,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3435,10 +3422,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124808149</v>
+        <v>124808123</v>
       </c>
       <c r="B28" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3451,21 +3438,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3475,10 +3462,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466219</v>
+        <v>465924</v>
       </c>
       <c r="R28" t="n">
-        <v>7055842</v>
+        <v>7055720</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3511,11 +3498,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3542,7 +3524,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124808189</v>
+        <v>124808188</v>
       </c>
       <c r="B29" t="n">
         <v>91030</v>
@@ -3582,10 +3564,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466286</v>
+        <v>466015</v>
       </c>
       <c r="R29" t="n">
-        <v>7056084</v>
+        <v>7055934</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3644,10 +3626,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124808185</v>
+        <v>124808162</v>
       </c>
       <c r="B30" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3660,21 +3642,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3684,10 +3666,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>466191</v>
+        <v>465856</v>
       </c>
       <c r="R30" t="n">
-        <v>7055781</v>
+        <v>7055738</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3720,6 +3702,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3746,7 +3733,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124808161</v>
+        <v>124808139</v>
       </c>
       <c r="B31" t="n">
         <v>57513</v>
@@ -3786,10 +3773,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>465859</v>
+        <v>466126</v>
       </c>
       <c r="R31" t="n">
-        <v>7055744</v>
+        <v>7055914</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3826,7 +3813,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3853,10 +3840,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124808143</v>
+        <v>124808195</v>
       </c>
       <c r="B32" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3869,21 +3856,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3893,10 +3880,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466291</v>
+        <v>466026</v>
       </c>
       <c r="R32" t="n">
-        <v>7056076</v>
+        <v>7055714</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3929,11 +3916,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3960,10 +3942,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124808187</v>
+        <v>124808144</v>
       </c>
       <c r="B33" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3976,21 +3958,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4000,10 +3982,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>465961</v>
+        <v>466231</v>
       </c>
       <c r="R33" t="n">
-        <v>7055835</v>
+        <v>7056150</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4036,6 +4018,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4062,7 +4049,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124808160</v>
+        <v>124808132</v>
       </c>
       <c r="B34" t="n">
         <v>57513</v>
@@ -4102,10 +4089,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>465939</v>
+        <v>466002</v>
       </c>
       <c r="R34" t="n">
-        <v>7055717</v>
+        <v>7055866</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4169,7 +4156,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124808158</v>
+        <v>124808146</v>
       </c>
       <c r="B35" t="n">
         <v>57513</v>
@@ -4209,10 +4196,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>465957</v>
+        <v>466210</v>
       </c>
       <c r="R35" t="n">
-        <v>7055698</v>
+        <v>7056130</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4276,7 +4263,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124808155</v>
+        <v>124808126</v>
       </c>
       <c r="B36" t="n">
         <v>57513</v>
@@ -4316,10 +4303,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>466025</v>
+        <v>465931</v>
       </c>
       <c r="R36" t="n">
-        <v>7055769</v>
+        <v>7055792</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4383,10 +4370,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124808134</v>
+        <v>124808187</v>
       </c>
       <c r="B37" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4399,21 +4386,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4423,10 +4410,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>466020</v>
+        <v>465961</v>
       </c>
       <c r="R37" t="n">
-        <v>7055801</v>
+        <v>7055835</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4459,11 +4446,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4490,7 +4472,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124808148</v>
+        <v>124808160</v>
       </c>
       <c r="B38" t="n">
         <v>57513</v>
@@ -4530,10 +4512,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>466190</v>
+        <v>465939</v>
       </c>
       <c r="R38" t="n">
-        <v>7055952</v>
+        <v>7055717</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4597,7 +4579,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124808141</v>
+        <v>124808152</v>
       </c>
       <c r="B39" t="n">
         <v>57513</v>
@@ -4637,10 +4619,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>466172</v>
+        <v>466072</v>
       </c>
       <c r="R39" t="n">
-        <v>7056129</v>
+        <v>7055589</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4704,7 +4686,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124808136</v>
+        <v>124808143</v>
       </c>
       <c r="B40" t="n">
         <v>57513</v>
@@ -4744,10 +4726,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>466032</v>
+        <v>466291</v>
       </c>
       <c r="R40" t="n">
-        <v>7055802</v>
+        <v>7056076</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4811,7 +4793,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124808126</v>
+        <v>124808158</v>
       </c>
       <c r="B41" t="n">
         <v>57513</v>
@@ -4851,10 +4833,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>465931</v>
+        <v>465957</v>
       </c>
       <c r="R41" t="n">
-        <v>7055792</v>
+        <v>7055698</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4918,10 +4900,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124808132</v>
+        <v>124808189</v>
       </c>
       <c r="B42" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4934,21 +4916,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4958,10 +4940,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>466002</v>
+        <v>466286</v>
       </c>
       <c r="R42" t="n">
-        <v>7055866</v>
+        <v>7056084</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4994,11 +4976,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5025,7 +5002,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124808137</v>
+        <v>124808125</v>
       </c>
       <c r="B43" t="n">
         <v>57513</v>
@@ -5059,16 +5036,24 @@
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Åkerån, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>466097</v>
+        <v>466019</v>
       </c>
       <c r="R43" t="n">
-        <v>7055831</v>
+        <v>7055741</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5105,7 +5090,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Bohål ca 6m upp i bruten gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5132,7 +5117,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124808146</v>
+        <v>124808134</v>
       </c>
       <c r="B44" t="n">
         <v>57513</v>
@@ -5172,10 +5157,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>466210</v>
+        <v>466020</v>
       </c>
       <c r="R44" t="n">
-        <v>7056130</v>
+        <v>7055801</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5239,10 +5224,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124808194</v>
+        <v>124808131</v>
       </c>
       <c r="B45" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5255,21 +5240,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5279,10 +5264,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>466020</v>
+        <v>466023</v>
       </c>
       <c r="R45" t="n">
-        <v>7055742</v>
+        <v>7055886</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5315,6 +5300,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5341,10 +5331,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124808188</v>
+        <v>124808137</v>
       </c>
       <c r="B46" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5357,21 +5347,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5381,10 +5371,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>466015</v>
+        <v>466097</v>
       </c>
       <c r="R46" t="n">
-        <v>7055934</v>
+        <v>7055831</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5417,6 +5407,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5443,10 +5438,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124808123</v>
+        <v>124808141</v>
       </c>
       <c r="B47" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5459,21 +5454,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5483,10 +5478,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>465924</v>
+        <v>466172</v>
       </c>
       <c r="R47" t="n">
-        <v>7055720</v>
+        <v>7056129</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5519,6 +5514,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5545,7 +5545,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124808150</v>
+        <v>124808140</v>
       </c>
       <c r="B48" t="n">
         <v>57513</v>
@@ -5585,10 +5585,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>466187</v>
+        <v>466113</v>
       </c>
       <c r="R48" t="n">
-        <v>7055846</v>
+        <v>7055912</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5625,7 +5625,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">

--- a/artfynd/A 11097-2024 artfynd.xlsx
+++ b/artfynd/A 11097-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124808182</v>
+        <v>124808135</v>
       </c>
       <c r="B2" t="n">
-        <v>79892</v>
+        <v>57513</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>466191</v>
+        <v>466024</v>
       </c>
       <c r="R2" t="n">
-        <v>7055781</v>
+        <v>7055801</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124808148</v>
+        <v>124808193</v>
       </c>
       <c r="B4" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>466190</v>
+        <v>466155</v>
       </c>
       <c r="R4" t="n">
-        <v>7055952</v>
+        <v>7055735</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,11 +960,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124808151</v>
+        <v>124808188</v>
       </c>
       <c r="B5" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>466148</v>
+        <v>466015</v>
       </c>
       <c r="R5" t="n">
-        <v>7055732</v>
+        <v>7055934</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,11 +1062,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124808142</v>
+        <v>124808183</v>
       </c>
       <c r="B6" t="n">
-        <v>57513</v>
+        <v>91299</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466212</v>
+        <v>465924</v>
       </c>
       <c r="R6" t="n">
-        <v>7056170</v>
+        <v>7055722</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,11 +1164,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124808184</v>
+        <v>124808147</v>
       </c>
       <c r="B7" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1216,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466183</v>
+        <v>466151</v>
       </c>
       <c r="R7" t="n">
-        <v>7056145</v>
+        <v>7055999</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1276,6 +1266,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1302,7 +1297,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124808145</v>
+        <v>124808134</v>
       </c>
       <c r="B8" t="n">
         <v>57513</v>
@@ -1342,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466217</v>
+        <v>466020</v>
       </c>
       <c r="R8" t="n">
-        <v>7056120</v>
+        <v>7055801</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1409,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124808147</v>
+        <v>124808123</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1425,21 +1420,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1449,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466151</v>
+        <v>465924</v>
       </c>
       <c r="R9" t="n">
-        <v>7055999</v>
+        <v>7055720</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1485,11 +1480,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1516,7 +1506,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124808133</v>
+        <v>124808159</v>
       </c>
       <c r="B10" t="n">
         <v>57513</v>
@@ -1556,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466022</v>
+        <v>465930</v>
       </c>
       <c r="R10" t="n">
-        <v>7055840</v>
+        <v>7055704</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1596,7 +1586,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1623,10 +1613,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124808129</v>
+        <v>124808195</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1639,21 +1629,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1663,10 +1653,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>465997</v>
+        <v>466026</v>
       </c>
       <c r="R11" t="n">
-        <v>7055926</v>
+        <v>7055714</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1699,11 +1689,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1730,7 +1715,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124808159</v>
+        <v>124808140</v>
       </c>
       <c r="B12" t="n">
         <v>57513</v>
@@ -1770,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>465930</v>
+        <v>466113</v>
       </c>
       <c r="R12" t="n">
-        <v>7055704</v>
+        <v>7055912</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1810,7 +1795,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1837,7 +1822,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124808136</v>
+        <v>124808160</v>
       </c>
       <c r="B13" t="n">
         <v>57513</v>
@@ -1877,10 +1862,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466032</v>
+        <v>465939</v>
       </c>
       <c r="R13" t="n">
-        <v>7055802</v>
+        <v>7055717</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1944,10 +1929,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124808183</v>
+        <v>124808149</v>
       </c>
       <c r="B14" t="n">
-        <v>91299</v>
+        <v>57513</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1960,21 +1945,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1984,10 +1969,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>465924</v>
+        <v>466219</v>
       </c>
       <c r="R14" t="n">
-        <v>7055722</v>
+        <v>7055842</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2020,6 +2005,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2046,10 +2036,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124808185</v>
+        <v>124808157</v>
       </c>
       <c r="B15" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2062,21 +2052,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2086,10 +2076,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>466191</v>
+        <v>466023</v>
       </c>
       <c r="R15" t="n">
-        <v>7055781</v>
+        <v>7055706</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2122,6 +2112,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2148,10 +2143,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124808193</v>
+        <v>124808136</v>
       </c>
       <c r="B16" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2164,21 +2159,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2188,10 +2183,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466155</v>
+        <v>466032</v>
       </c>
       <c r="R16" t="n">
-        <v>7055735</v>
+        <v>7055802</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2224,6 +2219,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2250,7 +2250,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124808157</v>
+        <v>124808139</v>
       </c>
       <c r="B17" t="n">
         <v>57513</v>
@@ -2290,10 +2290,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466023</v>
+        <v>466126</v>
       </c>
       <c r="R17" t="n">
-        <v>7055706</v>
+        <v>7055914</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2357,10 +2357,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124808150</v>
+        <v>124808182</v>
       </c>
       <c r="B18" t="n">
-        <v>57513</v>
+        <v>79892</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2373,21 +2373,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2397,10 +2397,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466187</v>
+        <v>466191</v>
       </c>
       <c r="R18" t="n">
-        <v>7055846</v>
+        <v>7055781</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2433,11 +2433,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2464,10 +2459,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124808194</v>
+        <v>124808133</v>
       </c>
       <c r="B19" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2480,21 +2475,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2504,10 +2499,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466020</v>
+        <v>466022</v>
       </c>
       <c r="R19" t="n">
-        <v>7055742</v>
+        <v>7055840</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2540,6 +2535,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2566,7 +2566,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124808149</v>
+        <v>124808150</v>
       </c>
       <c r="B20" t="n">
         <v>57513</v>
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466219</v>
+        <v>466187</v>
       </c>
       <c r="R20" t="n">
-        <v>7055842</v>
+        <v>7055846</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2673,7 +2673,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124808135</v>
+        <v>124808144</v>
       </c>
       <c r="B21" t="n">
         <v>57513</v>
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>466024</v>
+        <v>466231</v>
       </c>
       <c r="R21" t="n">
-        <v>7055801</v>
+        <v>7056150</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2780,7 +2780,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124808161</v>
+        <v>124808148</v>
       </c>
       <c r="B22" t="n">
         <v>57513</v>
@@ -2820,10 +2820,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>465859</v>
+        <v>466190</v>
       </c>
       <c r="R22" t="n">
-        <v>7055744</v>
+        <v>7055952</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2887,10 +2887,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124808154</v>
+        <v>124808189</v>
       </c>
       <c r="B23" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2903,21 +2903,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2927,10 +2927,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>466093</v>
+        <v>466286</v>
       </c>
       <c r="R23" t="n">
-        <v>7055760</v>
+        <v>7056084</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2963,11 +2963,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2994,7 +2989,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124808155</v>
+        <v>124808127</v>
       </c>
       <c r="B24" t="n">
         <v>57513</v>
@@ -3034,10 +3029,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>466025</v>
+        <v>465979</v>
       </c>
       <c r="R24" t="n">
-        <v>7055769</v>
+        <v>7055862</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3101,7 +3096,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124808156</v>
+        <v>124808155</v>
       </c>
       <c r="B25" t="n">
         <v>57513</v>
@@ -3141,10 +3136,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>466027</v>
+        <v>466025</v>
       </c>
       <c r="R25" t="n">
-        <v>7055757</v>
+        <v>7055769</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3208,7 +3203,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124808127</v>
+        <v>124808161</v>
       </c>
       <c r="B26" t="n">
         <v>57513</v>
@@ -3248,10 +3243,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>465979</v>
+        <v>465859</v>
       </c>
       <c r="R26" t="n">
-        <v>7055862</v>
+        <v>7055744</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3315,7 +3310,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124808138</v>
+        <v>124808137</v>
       </c>
       <c r="B27" t="n">
         <v>57513</v>
@@ -3355,10 +3350,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466123</v>
+        <v>466097</v>
       </c>
       <c r="R27" t="n">
-        <v>7055839</v>
+        <v>7055831</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3395,7 +3390,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3422,10 +3417,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124808123</v>
+        <v>124808138</v>
       </c>
       <c r="B28" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3438,21 +3433,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3462,10 +3457,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>465924</v>
+        <v>466123</v>
       </c>
       <c r="R28" t="n">
-        <v>7055720</v>
+        <v>7055839</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3498,6 +3493,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3524,10 +3524,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124808188</v>
+        <v>124808156</v>
       </c>
       <c r="B29" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3540,21 +3540,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3564,10 +3564,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466015</v>
+        <v>466027</v>
       </c>
       <c r="R29" t="n">
-        <v>7055934</v>
+        <v>7055757</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3600,6 +3600,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3626,7 +3631,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124808162</v>
+        <v>124808143</v>
       </c>
       <c r="B30" t="n">
         <v>57513</v>
@@ -3666,10 +3671,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>465856</v>
+        <v>466291</v>
       </c>
       <c r="R30" t="n">
-        <v>7055738</v>
+        <v>7056076</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3733,7 +3738,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124808139</v>
+        <v>124808162</v>
       </c>
       <c r="B31" t="n">
         <v>57513</v>
@@ -3773,10 +3778,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466126</v>
+        <v>465856</v>
       </c>
       <c r="R31" t="n">
-        <v>7055914</v>
+        <v>7055738</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3813,7 +3818,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3840,10 +3845,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124808195</v>
+        <v>124808142</v>
       </c>
       <c r="B32" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3856,21 +3861,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3880,10 +3885,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466026</v>
+        <v>466212</v>
       </c>
       <c r="R32" t="n">
-        <v>7055714</v>
+        <v>7056170</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3916,6 +3921,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3942,7 +3952,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124808144</v>
+        <v>124808126</v>
       </c>
       <c r="B33" t="n">
         <v>57513</v>
@@ -3982,10 +3992,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466231</v>
+        <v>465931</v>
       </c>
       <c r="R33" t="n">
-        <v>7056150</v>
+        <v>7055792</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4049,10 +4059,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124808132</v>
+        <v>124808194</v>
       </c>
       <c r="B34" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4065,21 +4075,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4089,10 +4099,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>466002</v>
+        <v>466020</v>
       </c>
       <c r="R34" t="n">
-        <v>7055866</v>
+        <v>7055742</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4125,11 +4135,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4156,7 +4161,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124808146</v>
+        <v>124808132</v>
       </c>
       <c r="B35" t="n">
         <v>57513</v>
@@ -4196,10 +4201,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>466210</v>
+        <v>466002</v>
       </c>
       <c r="R35" t="n">
-        <v>7056130</v>
+        <v>7055866</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4263,7 +4268,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124808126</v>
+        <v>124808145</v>
       </c>
       <c r="B36" t="n">
         <v>57513</v>
@@ -4303,10 +4308,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>465931</v>
+        <v>466217</v>
       </c>
       <c r="R36" t="n">
-        <v>7055792</v>
+        <v>7056120</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4370,10 +4375,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124808187</v>
+        <v>124808129</v>
       </c>
       <c r="B37" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4386,21 +4391,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4410,10 +4415,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>465961</v>
+        <v>465997</v>
       </c>
       <c r="R37" t="n">
-        <v>7055835</v>
+        <v>7055926</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4446,6 +4451,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4472,7 +4482,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124808160</v>
+        <v>124808146</v>
       </c>
       <c r="B38" t="n">
         <v>57513</v>
@@ -4512,10 +4522,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>465939</v>
+        <v>466210</v>
       </c>
       <c r="R38" t="n">
-        <v>7055717</v>
+        <v>7056130</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4579,10 +4589,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124808152</v>
+        <v>124808187</v>
       </c>
       <c r="B39" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4595,21 +4605,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4619,10 +4629,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>466072</v>
+        <v>465961</v>
       </c>
       <c r="R39" t="n">
-        <v>7055589</v>
+        <v>7055835</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4655,11 +4665,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4686,10 +4691,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124808143</v>
+        <v>124808184</v>
       </c>
       <c r="B40" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4702,21 +4707,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4726,10 +4731,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>466291</v>
+        <v>466183</v>
       </c>
       <c r="R40" t="n">
-        <v>7056076</v>
+        <v>7056145</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4762,11 +4767,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4793,10 +4793,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124808158</v>
+        <v>124808185</v>
       </c>
       <c r="B41" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4809,21 +4809,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4833,10 +4833,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>465957</v>
+        <v>466191</v>
       </c>
       <c r="R41" t="n">
-        <v>7055698</v>
+        <v>7055781</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4869,11 +4869,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4900,10 +4895,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124808189</v>
+        <v>124808125</v>
       </c>
       <c r="B42" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4916,34 +4911,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Åkerån, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>466286</v>
+        <v>466019</v>
       </c>
       <c r="R42" t="n">
-        <v>7056084</v>
+        <v>7055741</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4976,6 +4979,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Bohål ca 6m upp i bruten gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5002,7 +5010,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124808125</v>
+        <v>124808158</v>
       </c>
       <c r="B43" t="n">
         <v>57513</v>
@@ -5036,24 +5044,16 @@
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Åkerån, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>466019</v>
+        <v>465957</v>
       </c>
       <c r="R43" t="n">
-        <v>7055741</v>
+        <v>7055698</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5090,7 +5090,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Bohål ca 6m upp i bruten gran</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5117,7 +5117,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124808134</v>
+        <v>124808152</v>
       </c>
       <c r="B44" t="n">
         <v>57513</v>
@@ -5157,10 +5157,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>466020</v>
+        <v>466072</v>
       </c>
       <c r="R44" t="n">
-        <v>7055801</v>
+        <v>7055589</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5224,7 +5224,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124808131</v>
+        <v>124808151</v>
       </c>
       <c r="B45" t="n">
         <v>57513</v>
@@ -5264,10 +5264,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>466023</v>
+        <v>466148</v>
       </c>
       <c r="R45" t="n">
-        <v>7055886</v>
+        <v>7055732</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5331,7 +5331,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124808137</v>
+        <v>124808131</v>
       </c>
       <c r="B46" t="n">
         <v>57513</v>
@@ -5371,10 +5371,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>466097</v>
+        <v>466023</v>
       </c>
       <c r="R46" t="n">
-        <v>7055831</v>
+        <v>7055886</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5545,7 +5545,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124808140</v>
+        <v>124808154</v>
       </c>
       <c r="B48" t="n">
         <v>57513</v>
@@ -5585,10 +5585,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>466113</v>
+        <v>466093</v>
       </c>
       <c r="R48" t="n">
-        <v>7055912</v>
+        <v>7055760</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>

--- a/artfynd/A 11097-2024 artfynd.xlsx
+++ b/artfynd/A 11097-2024 artfynd.xlsx
@@ -1404,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124808123</v>
+        <v>124808159</v>
       </c>
       <c r="B9" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1420,21 +1420,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1444,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>465924</v>
+        <v>465930</v>
       </c>
       <c r="R9" t="n">
-        <v>7055720</v>
+        <v>7055704</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1480,6 +1480,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1506,10 +1511,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124808159</v>
+        <v>124808123</v>
       </c>
       <c r="B10" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1522,21 +1527,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1546,10 +1551,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>465930</v>
+        <v>465924</v>
       </c>
       <c r="R10" t="n">
-        <v>7055704</v>
+        <v>7055720</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1582,11 +1587,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1715,7 +1715,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124808140</v>
+        <v>124808160</v>
       </c>
       <c r="B12" t="n">
         <v>57513</v>
@@ -1755,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466113</v>
+        <v>465939</v>
       </c>
       <c r="R12" t="n">
-        <v>7055912</v>
+        <v>7055717</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1822,7 +1822,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124808160</v>
+        <v>124808149</v>
       </c>
       <c r="B13" t="n">
         <v>57513</v>
@@ -1862,10 +1862,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>465939</v>
+        <v>466219</v>
       </c>
       <c r="R13" t="n">
-        <v>7055717</v>
+        <v>7055842</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1929,7 +1929,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124808149</v>
+        <v>124808140</v>
       </c>
       <c r="B14" t="n">
         <v>57513</v>
@@ -1969,10 +1969,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>466219</v>
+        <v>466113</v>
       </c>
       <c r="R14" t="n">
-        <v>7055842</v>
+        <v>7055912</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2009,7 +2009,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 11097-2024 artfynd.xlsx
+++ b/artfynd/A 11097-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124808135</v>
+        <v>124808182</v>
       </c>
       <c r="B2" t="n">
-        <v>57513</v>
+        <v>79892</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>466024</v>
+        <v>466191</v>
       </c>
       <c r="R2" t="n">
-        <v>7055801</v>
+        <v>7055781</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124808190</v>
+        <v>124808150</v>
       </c>
       <c r="B3" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466147</v>
+        <v>466187</v>
       </c>
       <c r="R3" t="n">
-        <v>7056067</v>
+        <v>7055846</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124808193</v>
+        <v>124808147</v>
       </c>
       <c r="B4" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>466155</v>
+        <v>466151</v>
       </c>
       <c r="R4" t="n">
-        <v>7055735</v>
+        <v>7055999</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,6 +960,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124808188</v>
+        <v>124808127</v>
       </c>
       <c r="B5" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>466015</v>
+        <v>465979</v>
       </c>
       <c r="R5" t="n">
-        <v>7055934</v>
+        <v>7055862</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,6 +1067,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124808183</v>
+        <v>124808133</v>
       </c>
       <c r="B6" t="n">
-        <v>91299</v>
+        <v>57513</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>465924</v>
+        <v>466022</v>
       </c>
       <c r="R6" t="n">
-        <v>7055722</v>
+        <v>7055840</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1164,6 +1174,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1190,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124808147</v>
+        <v>124808138</v>
       </c>
       <c r="B7" t="n">
         <v>57513</v>
@@ -1230,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466151</v>
+        <v>466123</v>
       </c>
       <c r="R7" t="n">
-        <v>7055999</v>
+        <v>7055839</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124808134</v>
+        <v>124808193</v>
       </c>
       <c r="B8" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1313,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466020</v>
+        <v>466155</v>
       </c>
       <c r="R8" t="n">
-        <v>7055801</v>
+        <v>7055735</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1373,11 +1388,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1404,7 +1414,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124808159</v>
+        <v>124808129</v>
       </c>
       <c r="B9" t="n">
         <v>57513</v>
@@ -1444,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>465930</v>
+        <v>465997</v>
       </c>
       <c r="R9" t="n">
-        <v>7055704</v>
+        <v>7055926</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1511,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124808123</v>
+        <v>124808161</v>
       </c>
       <c r="B10" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1527,21 +1537,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1551,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>465924</v>
+        <v>465859</v>
       </c>
       <c r="R10" t="n">
-        <v>7055720</v>
+        <v>7055744</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1587,6 +1597,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1613,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124808195</v>
+        <v>124808152</v>
       </c>
       <c r="B11" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1629,21 +1644,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1653,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466026</v>
+        <v>466072</v>
       </c>
       <c r="R11" t="n">
-        <v>7055714</v>
+        <v>7055589</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1689,6 +1704,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1715,7 +1735,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124808160</v>
+        <v>124808136</v>
       </c>
       <c r="B12" t="n">
         <v>57513</v>
@@ -1755,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>465939</v>
+        <v>466032</v>
       </c>
       <c r="R12" t="n">
-        <v>7055717</v>
+        <v>7055802</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1822,7 +1842,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124808149</v>
+        <v>124808162</v>
       </c>
       <c r="B13" t="n">
         <v>57513</v>
@@ -1862,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466219</v>
+        <v>465856</v>
       </c>
       <c r="R13" t="n">
-        <v>7055842</v>
+        <v>7055738</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1902,7 +1922,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1929,7 +1949,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124808140</v>
+        <v>124808131</v>
       </c>
       <c r="B14" t="n">
         <v>57513</v>
@@ -1969,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>466113</v>
+        <v>466023</v>
       </c>
       <c r="R14" t="n">
-        <v>7055912</v>
+        <v>7055886</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2036,7 +2056,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124808157</v>
+        <v>124808135</v>
       </c>
       <c r="B15" t="n">
         <v>57513</v>
@@ -2076,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>466023</v>
+        <v>466024</v>
       </c>
       <c r="R15" t="n">
-        <v>7055706</v>
+        <v>7055801</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2143,10 +2163,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124808136</v>
+        <v>124808123</v>
       </c>
       <c r="B16" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2159,21 +2179,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2183,10 +2203,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466032</v>
+        <v>465924</v>
       </c>
       <c r="R16" t="n">
-        <v>7055802</v>
+        <v>7055720</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2219,11 +2239,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2250,7 +2265,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124808139</v>
+        <v>124808142</v>
       </c>
       <c r="B17" t="n">
         <v>57513</v>
@@ -2290,10 +2305,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466126</v>
+        <v>466212</v>
       </c>
       <c r="R17" t="n">
-        <v>7055914</v>
+        <v>7056170</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2330,7 +2345,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2357,10 +2372,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124808182</v>
+        <v>124808158</v>
       </c>
       <c r="B18" t="n">
-        <v>79892</v>
+        <v>57513</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2373,21 +2388,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2397,10 +2412,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466191</v>
+        <v>465957</v>
       </c>
       <c r="R18" t="n">
-        <v>7055781</v>
+        <v>7055698</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2433,6 +2448,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2459,7 +2479,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124808133</v>
+        <v>124808125</v>
       </c>
       <c r="B19" t="n">
         <v>57513</v>
@@ -2493,16 +2513,24 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Åkerån, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466022</v>
+        <v>466019</v>
       </c>
       <c r="R19" t="n">
-        <v>7055840</v>
+        <v>7055741</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2539,7 +2567,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Bohål ca 6m upp i bruten gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2566,10 +2594,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124808150</v>
+        <v>124808194</v>
       </c>
       <c r="B20" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2582,21 +2610,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2606,10 +2634,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466187</v>
+        <v>466020</v>
       </c>
       <c r="R20" t="n">
-        <v>7055846</v>
+        <v>7055742</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2642,11 +2670,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2780,10 +2803,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124808148</v>
+        <v>124808183</v>
       </c>
       <c r="B22" t="n">
-        <v>57513</v>
+        <v>91299</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2796,21 +2819,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2820,10 +2843,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>466190</v>
+        <v>465924</v>
       </c>
       <c r="R22" t="n">
-        <v>7055952</v>
+        <v>7055722</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2856,11 +2879,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2887,10 +2905,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124808189</v>
+        <v>124808160</v>
       </c>
       <c r="B23" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2903,21 +2921,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2927,10 +2945,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>466286</v>
+        <v>465939</v>
       </c>
       <c r="R23" t="n">
-        <v>7056084</v>
+        <v>7055717</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2963,6 +2981,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2989,7 +3012,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124808127</v>
+        <v>124808149</v>
       </c>
       <c r="B24" t="n">
         <v>57513</v>
@@ -3029,10 +3052,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>465979</v>
+        <v>466219</v>
       </c>
       <c r="R24" t="n">
-        <v>7055862</v>
+        <v>7055842</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3069,7 +3092,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3203,7 +3226,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124808161</v>
+        <v>124808146</v>
       </c>
       <c r="B26" t="n">
         <v>57513</v>
@@ -3243,10 +3266,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>465859</v>
+        <v>466210</v>
       </c>
       <c r="R26" t="n">
-        <v>7055744</v>
+        <v>7056130</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3310,7 +3333,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124808137</v>
+        <v>124808143</v>
       </c>
       <c r="B27" t="n">
         <v>57513</v>
@@ -3350,10 +3373,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466097</v>
+        <v>466291</v>
       </c>
       <c r="R27" t="n">
-        <v>7055831</v>
+        <v>7056076</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3390,7 +3413,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3417,10 +3440,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124808138</v>
+        <v>124808184</v>
       </c>
       <c r="B28" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3433,21 +3456,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3457,10 +3480,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466123</v>
+        <v>466183</v>
       </c>
       <c r="R28" t="n">
-        <v>7055839</v>
+        <v>7056145</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3493,11 +3516,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3524,7 +3542,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124808156</v>
+        <v>124808140</v>
       </c>
       <c r="B29" t="n">
         <v>57513</v>
@@ -3564,10 +3582,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466027</v>
+        <v>466113</v>
       </c>
       <c r="R29" t="n">
-        <v>7055757</v>
+        <v>7055912</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3631,7 +3649,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124808143</v>
+        <v>124808141</v>
       </c>
       <c r="B30" t="n">
         <v>57513</v>
@@ -3671,10 +3689,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>466291</v>
+        <v>466172</v>
       </c>
       <c r="R30" t="n">
-        <v>7056076</v>
+        <v>7056129</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3738,10 +3756,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124808162</v>
+        <v>124808188</v>
       </c>
       <c r="B31" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3754,21 +3772,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3778,10 +3796,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>465856</v>
+        <v>466015</v>
       </c>
       <c r="R31" t="n">
-        <v>7055738</v>
+        <v>7055934</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3814,11 +3832,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3845,10 +3858,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124808142</v>
+        <v>124808195</v>
       </c>
       <c r="B32" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3861,21 +3874,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3885,10 +3898,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466212</v>
+        <v>466026</v>
       </c>
       <c r="R32" t="n">
-        <v>7056170</v>
+        <v>7055714</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3921,11 +3934,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3952,7 +3960,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124808126</v>
+        <v>124808159</v>
       </c>
       <c r="B33" t="n">
         <v>57513</v>
@@ -3992,10 +4000,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>465931</v>
+        <v>465930</v>
       </c>
       <c r="R33" t="n">
-        <v>7055792</v>
+        <v>7055704</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4032,7 +4040,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4059,7 +4067,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124808194</v>
+        <v>124808190</v>
       </c>
       <c r="B34" t="n">
         <v>91030</v>
@@ -4099,10 +4107,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>466020</v>
+        <v>466147</v>
       </c>
       <c r="R34" t="n">
-        <v>7055742</v>
+        <v>7056067</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4161,7 +4169,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124808132</v>
+        <v>124808139</v>
       </c>
       <c r="B35" t="n">
         <v>57513</v>
@@ -4201,10 +4209,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>466002</v>
+        <v>466126</v>
       </c>
       <c r="R35" t="n">
-        <v>7055866</v>
+        <v>7055914</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4241,7 +4249,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4268,7 +4276,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124808145</v>
+        <v>124808157</v>
       </c>
       <c r="B36" t="n">
         <v>57513</v>
@@ -4308,10 +4316,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>466217</v>
+        <v>466023</v>
       </c>
       <c r="R36" t="n">
-        <v>7056120</v>
+        <v>7055706</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4375,7 +4383,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124808129</v>
+        <v>124808145</v>
       </c>
       <c r="B37" t="n">
         <v>57513</v>
@@ -4415,10 +4423,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>465997</v>
+        <v>466217</v>
       </c>
       <c r="R37" t="n">
-        <v>7055926</v>
+        <v>7056120</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4455,7 +4463,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4482,10 +4490,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124808146</v>
+        <v>124808185</v>
       </c>
       <c r="B38" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4498,21 +4506,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4522,10 +4530,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>466210</v>
+        <v>466191</v>
       </c>
       <c r="R38" t="n">
-        <v>7056130</v>
+        <v>7055781</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4558,11 +4566,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4589,7 +4592,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124808187</v>
+        <v>124808189</v>
       </c>
       <c r="B39" t="n">
         <v>91030</v>
@@ -4629,10 +4632,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>465961</v>
+        <v>466286</v>
       </c>
       <c r="R39" t="n">
-        <v>7055835</v>
+        <v>7056084</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4691,10 +4694,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124808184</v>
+        <v>124808148</v>
       </c>
       <c r="B40" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4707,21 +4710,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4731,10 +4734,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>466183</v>
+        <v>466190</v>
       </c>
       <c r="R40" t="n">
-        <v>7056145</v>
+        <v>7055952</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4767,6 +4770,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4793,10 +4801,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124808185</v>
+        <v>124808151</v>
       </c>
       <c r="B41" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4809,21 +4817,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4833,10 +4841,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>466191</v>
+        <v>466148</v>
       </c>
       <c r="R41" t="n">
-        <v>7055781</v>
+        <v>7055732</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4869,6 +4877,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4895,7 +4908,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124808125</v>
+        <v>124808137</v>
       </c>
       <c r="B42" t="n">
         <v>57513</v>
@@ -4929,24 +4942,16 @@
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Åkerån, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>466019</v>
+        <v>466097</v>
       </c>
       <c r="R42" t="n">
-        <v>7055741</v>
+        <v>7055831</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4983,7 +4988,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Bohål ca 6m upp i bruten gran</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5010,7 +5015,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124808158</v>
+        <v>124808132</v>
       </c>
       <c r="B43" t="n">
         <v>57513</v>
@@ -5050,10 +5055,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>465957</v>
+        <v>466002</v>
       </c>
       <c r="R43" t="n">
-        <v>7055698</v>
+        <v>7055866</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5117,7 +5122,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124808152</v>
+        <v>124808156</v>
       </c>
       <c r="B44" t="n">
         <v>57513</v>
@@ -5157,10 +5162,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>466072</v>
+        <v>466027</v>
       </c>
       <c r="R44" t="n">
-        <v>7055589</v>
+        <v>7055757</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5224,7 +5229,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124808151</v>
+        <v>124808154</v>
       </c>
       <c r="B45" t="n">
         <v>57513</v>
@@ -5264,10 +5269,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>466148</v>
+        <v>466093</v>
       </c>
       <c r="R45" t="n">
-        <v>7055732</v>
+        <v>7055760</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5331,10 +5336,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124808131</v>
+        <v>124808187</v>
       </c>
       <c r="B46" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5347,21 +5352,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5371,10 +5376,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>466023</v>
+        <v>465961</v>
       </c>
       <c r="R46" t="n">
-        <v>7055886</v>
+        <v>7055835</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5407,11 +5412,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5438,7 +5438,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124808141</v>
+        <v>124808134</v>
       </c>
       <c r="B47" t="n">
         <v>57513</v>
@@ -5478,10 +5478,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>466172</v>
+        <v>466020</v>
       </c>
       <c r="R47" t="n">
-        <v>7056129</v>
+        <v>7055801</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5545,7 +5545,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124808154</v>
+        <v>124808126</v>
       </c>
       <c r="B48" t="n">
         <v>57513</v>
@@ -5585,10 +5585,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>466093</v>
+        <v>465931</v>
       </c>
       <c r="R48" t="n">
-        <v>7055760</v>
+        <v>7055792</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>

--- a/artfynd/A 11097-2024 artfynd.xlsx
+++ b/artfynd/A 11097-2024 artfynd.xlsx
@@ -2905,7 +2905,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124808160</v>
+        <v>124808149</v>
       </c>
       <c r="B23" t="n">
         <v>57513</v>
@@ -2945,10 +2945,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>465939</v>
+        <v>466219</v>
       </c>
       <c r="R23" t="n">
-        <v>7055717</v>
+        <v>7055842</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2985,7 +2985,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3012,7 +3012,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124808149</v>
+        <v>124808160</v>
       </c>
       <c r="B24" t="n">
         <v>57513</v>
@@ -3052,10 +3052,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>466219</v>
+        <v>465939</v>
       </c>
       <c r="R24" t="n">
-        <v>7055842</v>
+        <v>7055717</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3092,7 +3092,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3226,10 +3226,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124808146</v>
+        <v>124808184</v>
       </c>
       <c r="B26" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3242,21 +3242,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3266,10 +3266,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466210</v>
+        <v>466183</v>
       </c>
       <c r="R26" t="n">
-        <v>7056130</v>
+        <v>7056145</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3302,11 +3302,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3333,7 +3328,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124808143</v>
+        <v>124808140</v>
       </c>
       <c r="B27" t="n">
         <v>57513</v>
@@ -3373,10 +3368,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466291</v>
+        <v>466113</v>
       </c>
       <c r="R27" t="n">
-        <v>7056076</v>
+        <v>7055912</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3440,10 +3435,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124808184</v>
+        <v>124808146</v>
       </c>
       <c r="B28" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3456,21 +3451,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3480,10 +3475,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466183</v>
+        <v>466210</v>
       </c>
       <c r="R28" t="n">
-        <v>7056145</v>
+        <v>7056130</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3516,6 +3511,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3542,7 +3542,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124808140</v>
+        <v>124808143</v>
       </c>
       <c r="B29" t="n">
         <v>57513</v>
@@ -3582,10 +3582,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466113</v>
+        <v>466291</v>
       </c>
       <c r="R29" t="n">
-        <v>7055912</v>
+        <v>7056076</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3960,7 +3960,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124808159</v>
+        <v>124808139</v>
       </c>
       <c r="B33" t="n">
         <v>57513</v>
@@ -4000,10 +4000,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>465930</v>
+        <v>466126</v>
       </c>
       <c r="R33" t="n">
-        <v>7055704</v>
+        <v>7055914</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4040,7 +4040,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4067,10 +4067,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124808190</v>
+        <v>124808157</v>
       </c>
       <c r="B34" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4083,21 +4083,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4107,10 +4107,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>466147</v>
+        <v>466023</v>
       </c>
       <c r="R34" t="n">
-        <v>7056067</v>
+        <v>7055706</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4143,6 +4143,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4169,10 +4174,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124808139</v>
+        <v>124808190</v>
       </c>
       <c r="B35" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4185,21 +4190,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4209,10 +4214,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>466126</v>
+        <v>466147</v>
       </c>
       <c r="R35" t="n">
-        <v>7055914</v>
+        <v>7056067</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4245,11 +4250,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4276,7 +4276,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124808157</v>
+        <v>124808159</v>
       </c>
       <c r="B36" t="n">
         <v>57513</v>
@@ -4316,10 +4316,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>466023</v>
+        <v>465930</v>
       </c>
       <c r="R36" t="n">
-        <v>7055706</v>
+        <v>7055704</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 11097-2024 artfynd.xlsx
+++ b/artfynd/A 11097-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124808182</v>
+        <v>124808129</v>
       </c>
       <c r="B2" t="n">
-        <v>79892</v>
+        <v>57513</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>466191</v>
+        <v>465997</v>
       </c>
       <c r="R2" t="n">
-        <v>7055781</v>
+        <v>7055926</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124808150</v>
+        <v>124808158</v>
       </c>
       <c r="B3" t="n">
         <v>57513</v>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466187</v>
+        <v>465957</v>
       </c>
       <c r="R3" t="n">
-        <v>7055846</v>
+        <v>7055698</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124808147</v>
+        <v>124808182</v>
       </c>
       <c r="B4" t="n">
-        <v>57513</v>
+        <v>79892</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>466151</v>
+        <v>466191</v>
       </c>
       <c r="R4" t="n">
-        <v>7055999</v>
+        <v>7055781</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,11 +965,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124808127</v>
+        <v>124808194</v>
       </c>
       <c r="B5" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465979</v>
+        <v>466020</v>
       </c>
       <c r="R5" t="n">
-        <v>7055862</v>
+        <v>7055742</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,11 +1067,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,7 +1093,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124808133</v>
+        <v>124808155</v>
       </c>
       <c r="B6" t="n">
         <v>57513</v>
@@ -1138,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466022</v>
+        <v>466025</v>
       </c>
       <c r="R6" t="n">
-        <v>7055840</v>
+        <v>7055769</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,7 +1200,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124808138</v>
+        <v>124808131</v>
       </c>
       <c r="B7" t="n">
         <v>57513</v>
@@ -1245,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466123</v>
+        <v>466023</v>
       </c>
       <c r="R7" t="n">
-        <v>7055839</v>
+        <v>7055886</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1312,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124808193</v>
+        <v>124808152</v>
       </c>
       <c r="B8" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,21 +1323,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466155</v>
+        <v>466072</v>
       </c>
       <c r="R8" t="n">
-        <v>7055735</v>
+        <v>7055589</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1388,6 +1383,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1414,7 +1414,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124808129</v>
+        <v>124808144</v>
       </c>
       <c r="B9" t="n">
         <v>57513</v>
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>465997</v>
+        <v>466231</v>
       </c>
       <c r="R9" t="n">
-        <v>7055926</v>
+        <v>7056150</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,7 +1521,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124808161</v>
+        <v>124808137</v>
       </c>
       <c r="B10" t="n">
         <v>57513</v>
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>465859</v>
+        <v>466097</v>
       </c>
       <c r="R10" t="n">
-        <v>7055744</v>
+        <v>7055831</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1628,7 +1628,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124808152</v>
+        <v>124808149</v>
       </c>
       <c r="B11" t="n">
         <v>57513</v>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466072</v>
+        <v>466219</v>
       </c>
       <c r="R11" t="n">
-        <v>7055589</v>
+        <v>7055842</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,7 +1735,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124808136</v>
+        <v>124808127</v>
       </c>
       <c r="B12" t="n">
         <v>57513</v>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466032</v>
+        <v>465979</v>
       </c>
       <c r="R12" t="n">
-        <v>7055802</v>
+        <v>7055862</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1842,10 +1842,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124808162</v>
+        <v>124808184</v>
       </c>
       <c r="B13" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1858,21 +1858,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1882,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>465856</v>
+        <v>466183</v>
       </c>
       <c r="R13" t="n">
-        <v>7055738</v>
+        <v>7056145</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1918,11 +1918,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1949,7 +1944,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124808131</v>
+        <v>124808139</v>
       </c>
       <c r="B14" t="n">
         <v>57513</v>
@@ -1989,10 +1984,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>466023</v>
+        <v>466126</v>
       </c>
       <c r="R14" t="n">
-        <v>7055886</v>
+        <v>7055914</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2024,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2056,7 +2051,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124808135</v>
+        <v>124808162</v>
       </c>
       <c r="B15" t="n">
         <v>57513</v>
@@ -2096,10 +2091,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>466024</v>
+        <v>465856</v>
       </c>
       <c r="R15" t="n">
-        <v>7055801</v>
+        <v>7055738</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2163,10 +2158,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124808123</v>
+        <v>124808190</v>
       </c>
       <c r="B16" t="n">
-        <v>91012</v>
+        <v>91030</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2179,21 +2174,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2203,10 +2198,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>465924</v>
+        <v>466147</v>
       </c>
       <c r="R16" t="n">
-        <v>7055720</v>
+        <v>7056067</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2265,7 +2260,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124808142</v>
+        <v>124808148</v>
       </c>
       <c r="B17" t="n">
         <v>57513</v>
@@ -2305,10 +2300,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466212</v>
+        <v>466190</v>
       </c>
       <c r="R17" t="n">
-        <v>7056170</v>
+        <v>7055952</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2372,7 +2367,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124808158</v>
+        <v>124808159</v>
       </c>
       <c r="B18" t="n">
         <v>57513</v>
@@ -2412,10 +2407,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>465957</v>
+        <v>465930</v>
       </c>
       <c r="R18" t="n">
-        <v>7055698</v>
+        <v>7055704</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2452,7 +2447,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2479,7 +2474,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124808125</v>
+        <v>124808161</v>
       </c>
       <c r="B19" t="n">
         <v>57513</v>
@@ -2513,24 +2508,16 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Åkerån, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466019</v>
+        <v>465859</v>
       </c>
       <c r="R19" t="n">
-        <v>7055741</v>
+        <v>7055744</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2567,7 +2554,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Bohål ca 6m upp i bruten gran</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2594,10 +2581,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124808194</v>
+        <v>124808146</v>
       </c>
       <c r="B20" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2610,21 +2597,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2634,10 +2621,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466020</v>
+        <v>466210</v>
       </c>
       <c r="R20" t="n">
-        <v>7055742</v>
+        <v>7056130</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2670,6 +2657,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2696,10 +2688,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124808144</v>
+        <v>124808188</v>
       </c>
       <c r="B21" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2712,21 +2704,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2736,10 +2728,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>466231</v>
+        <v>466015</v>
       </c>
       <c r="R21" t="n">
-        <v>7056150</v>
+        <v>7055934</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2772,11 +2764,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2803,10 +2790,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124808183</v>
+        <v>124808136</v>
       </c>
       <c r="B22" t="n">
-        <v>91299</v>
+        <v>57513</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2819,21 +2806,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2843,10 +2830,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>465924</v>
+        <v>466032</v>
       </c>
       <c r="R22" t="n">
-        <v>7055722</v>
+        <v>7055802</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2879,6 +2866,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2905,7 +2897,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124808149</v>
+        <v>124808154</v>
       </c>
       <c r="B23" t="n">
         <v>57513</v>
@@ -2945,10 +2937,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>466219</v>
+        <v>466093</v>
       </c>
       <c r="R23" t="n">
-        <v>7055842</v>
+        <v>7055760</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2985,7 +2977,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3012,7 +3004,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124808160</v>
+        <v>124808135</v>
       </c>
       <c r="B24" t="n">
         <v>57513</v>
@@ -3052,10 +3044,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>465939</v>
+        <v>466024</v>
       </c>
       <c r="R24" t="n">
-        <v>7055717</v>
+        <v>7055801</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3119,10 +3111,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124808155</v>
+        <v>124808183</v>
       </c>
       <c r="B25" t="n">
-        <v>57513</v>
+        <v>91299</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3135,21 +3127,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3159,10 +3151,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>466025</v>
+        <v>465924</v>
       </c>
       <c r="R25" t="n">
-        <v>7055769</v>
+        <v>7055722</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3195,11 +3187,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3226,10 +3213,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124808184</v>
+        <v>124808160</v>
       </c>
       <c r="B26" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3242,21 +3229,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3266,10 +3253,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466183</v>
+        <v>465939</v>
       </c>
       <c r="R26" t="n">
-        <v>7056145</v>
+        <v>7055717</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3302,6 +3289,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3328,7 +3320,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124808140</v>
+        <v>124808151</v>
       </c>
       <c r="B27" t="n">
         <v>57513</v>
@@ -3368,10 +3360,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466113</v>
+        <v>466148</v>
       </c>
       <c r="R27" t="n">
-        <v>7055912</v>
+        <v>7055732</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3435,7 +3427,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124808146</v>
+        <v>124808134</v>
       </c>
       <c r="B28" t="n">
         <v>57513</v>
@@ -3475,10 +3467,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466210</v>
+        <v>466020</v>
       </c>
       <c r="R28" t="n">
-        <v>7056130</v>
+        <v>7055801</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3542,7 +3534,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124808143</v>
+        <v>124808156</v>
       </c>
       <c r="B29" t="n">
         <v>57513</v>
@@ -3582,10 +3574,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466291</v>
+        <v>466027</v>
       </c>
       <c r="R29" t="n">
-        <v>7056076</v>
+        <v>7055757</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3649,7 +3641,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124808141</v>
+        <v>124808142</v>
       </c>
       <c r="B30" t="n">
         <v>57513</v>
@@ -3689,10 +3681,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>466172</v>
+        <v>466212</v>
       </c>
       <c r="R30" t="n">
-        <v>7056129</v>
+        <v>7056170</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3756,10 +3748,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124808188</v>
+        <v>124808126</v>
       </c>
       <c r="B31" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3772,21 +3764,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3796,10 +3788,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466015</v>
+        <v>465931</v>
       </c>
       <c r="R31" t="n">
-        <v>7055934</v>
+        <v>7055792</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3832,6 +3824,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3858,10 +3855,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124808195</v>
+        <v>124808147</v>
       </c>
       <c r="B32" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3874,21 +3871,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3898,10 +3895,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466026</v>
+        <v>466151</v>
       </c>
       <c r="R32" t="n">
-        <v>7055714</v>
+        <v>7055999</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3934,6 +3931,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3960,7 +3962,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124808139</v>
+        <v>124808132</v>
       </c>
       <c r="B33" t="n">
         <v>57513</v>
@@ -4000,10 +4002,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466126</v>
+        <v>466002</v>
       </c>
       <c r="R33" t="n">
-        <v>7055914</v>
+        <v>7055866</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4040,7 +4042,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4067,7 +4069,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124808157</v>
+        <v>124808138</v>
       </c>
       <c r="B34" t="n">
         <v>57513</v>
@@ -4107,10 +4109,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>466023</v>
+        <v>466123</v>
       </c>
       <c r="R34" t="n">
-        <v>7055706</v>
+        <v>7055839</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4174,10 +4176,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124808190</v>
+        <v>124808150</v>
       </c>
       <c r="B35" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4190,21 +4192,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4214,10 +4216,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>466147</v>
+        <v>466187</v>
       </c>
       <c r="R35" t="n">
-        <v>7056067</v>
+        <v>7055846</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4250,6 +4252,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4276,7 +4283,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124808159</v>
+        <v>124808140</v>
       </c>
       <c r="B36" t="n">
         <v>57513</v>
@@ -4316,10 +4323,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>465930</v>
+        <v>466113</v>
       </c>
       <c r="R36" t="n">
-        <v>7055704</v>
+        <v>7055912</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4356,7 +4363,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4490,10 +4497,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124808185</v>
+        <v>124808125</v>
       </c>
       <c r="B38" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4506,34 +4513,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Åkerån, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>466191</v>
+        <v>466019</v>
       </c>
       <c r="R38" t="n">
-        <v>7055781</v>
+        <v>7055741</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4566,6 +4581,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Bohål ca 6m upp i bruten gran</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4592,10 +4612,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124808189</v>
+        <v>124808133</v>
       </c>
       <c r="B39" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4608,21 +4628,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4632,10 +4652,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>466286</v>
+        <v>466022</v>
       </c>
       <c r="R39" t="n">
-        <v>7056084</v>
+        <v>7055840</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4668,6 +4688,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4694,10 +4719,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124808148</v>
+        <v>124808123</v>
       </c>
       <c r="B40" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4710,21 +4735,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4734,10 +4759,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>466190</v>
+        <v>465924</v>
       </c>
       <c r="R40" t="n">
-        <v>7055952</v>
+        <v>7055720</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4770,11 +4795,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4801,10 +4821,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124808151</v>
+        <v>124808189</v>
       </c>
       <c r="B41" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4817,21 +4837,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4841,10 +4861,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>466148</v>
+        <v>466286</v>
       </c>
       <c r="R41" t="n">
-        <v>7055732</v>
+        <v>7056084</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4877,11 +4897,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4908,10 +4923,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124808137</v>
+        <v>124808195</v>
       </c>
       <c r="B42" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4924,21 +4939,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4948,10 +4963,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>466097</v>
+        <v>466026</v>
       </c>
       <c r="R42" t="n">
-        <v>7055831</v>
+        <v>7055714</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4984,11 +4999,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5015,7 +5025,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124808132</v>
+        <v>124808143</v>
       </c>
       <c r="B43" t="n">
         <v>57513</v>
@@ -5055,10 +5065,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>466002</v>
+        <v>466291</v>
       </c>
       <c r="R43" t="n">
-        <v>7055866</v>
+        <v>7056076</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5122,7 +5132,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124808156</v>
+        <v>124808141</v>
       </c>
       <c r="B44" t="n">
         <v>57513</v>
@@ -5162,10 +5172,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>466027</v>
+        <v>466172</v>
       </c>
       <c r="R44" t="n">
-        <v>7055757</v>
+        <v>7056129</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5229,10 +5239,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124808154</v>
+        <v>124808193</v>
       </c>
       <c r="B45" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5245,21 +5255,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5269,10 +5279,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>466093</v>
+        <v>466155</v>
       </c>
       <c r="R45" t="n">
-        <v>7055760</v>
+        <v>7055735</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5305,11 +5315,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5438,10 +5443,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124808134</v>
+        <v>124808185</v>
       </c>
       <c r="B47" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5454,21 +5459,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5478,10 +5483,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>466020</v>
+        <v>466191</v>
       </c>
       <c r="R47" t="n">
-        <v>7055801</v>
+        <v>7055781</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5514,11 +5519,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5545,7 +5545,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124808126</v>
+        <v>124808157</v>
       </c>
       <c r="B48" t="n">
         <v>57513</v>
@@ -5585,10 +5585,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>465931</v>
+        <v>466023</v>
       </c>
       <c r="R48" t="n">
-        <v>7055792</v>
+        <v>7055706</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>

--- a/artfynd/A 11097-2024 artfynd.xlsx
+++ b/artfynd/A 11097-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124808129</v>
+        <v>124808125</v>
       </c>
       <c r="B2" t="n">
         <v>57513</v>
@@ -709,16 +709,24 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Åkerån, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>465997</v>
+        <v>466019</v>
       </c>
       <c r="R2" t="n">
-        <v>7055926</v>
+        <v>7055741</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +763,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Bohål ca 6m upp i bruten gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124808158</v>
+        <v>124808187</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +806,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465957</v>
+        <v>465961</v>
       </c>
       <c r="R3" t="n">
-        <v>7055698</v>
+        <v>7055835</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,11 +866,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124808182</v>
+        <v>124808127</v>
       </c>
       <c r="B4" t="n">
-        <v>79892</v>
+        <v>57513</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>466191</v>
+        <v>465979</v>
       </c>
       <c r="R4" t="n">
-        <v>7055781</v>
+        <v>7055862</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,6 +968,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124808194</v>
+        <v>124808123</v>
       </c>
       <c r="B5" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,21 +1015,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>466020</v>
+        <v>465924</v>
       </c>
       <c r="R5" t="n">
-        <v>7055742</v>
+        <v>7055720</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124808155</v>
+        <v>124808193</v>
       </c>
       <c r="B6" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1117,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1141,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466025</v>
+        <v>466155</v>
       </c>
       <c r="R6" t="n">
-        <v>7055769</v>
+        <v>7055735</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,11 +1177,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,7 +1203,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124808131</v>
+        <v>124808135</v>
       </c>
       <c r="B7" t="n">
         <v>57513</v>
@@ -1240,10 +1243,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466023</v>
+        <v>466024</v>
       </c>
       <c r="R7" t="n">
-        <v>7055886</v>
+        <v>7055801</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1414,7 +1417,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124808144</v>
+        <v>124808151</v>
       </c>
       <c r="B9" t="n">
         <v>57513</v>
@@ -1454,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466231</v>
+        <v>466148</v>
       </c>
       <c r="R9" t="n">
-        <v>7056150</v>
+        <v>7055732</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1521,10 +1524,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124808137</v>
+        <v>124808189</v>
       </c>
       <c r="B10" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1537,21 +1540,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1561,10 +1564,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466097</v>
+        <v>466286</v>
       </c>
       <c r="R10" t="n">
-        <v>7055831</v>
+        <v>7056084</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1597,11 +1600,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1628,7 +1626,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124808149</v>
+        <v>124808150</v>
       </c>
       <c r="B11" t="n">
         <v>57513</v>
@@ -1668,10 +1666,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466219</v>
+        <v>466187</v>
       </c>
       <c r="R11" t="n">
-        <v>7055842</v>
+        <v>7055846</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,7 +1733,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124808127</v>
+        <v>124808129</v>
       </c>
       <c r="B12" t="n">
         <v>57513</v>
@@ -1775,10 +1773,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>465979</v>
+        <v>465997</v>
       </c>
       <c r="R12" t="n">
-        <v>7055862</v>
+        <v>7055926</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,7 +1813,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1842,10 +1840,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124808184</v>
+        <v>124808188</v>
       </c>
       <c r="B13" t="n">
-        <v>79891</v>
+        <v>91030</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1858,21 +1856,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1882,10 +1880,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466183</v>
+        <v>466015</v>
       </c>
       <c r="R13" t="n">
-        <v>7056145</v>
+        <v>7055934</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1944,7 +1942,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124808139</v>
+        <v>124808140</v>
       </c>
       <c r="B14" t="n">
         <v>57513</v>
@@ -1984,10 +1982,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>466126</v>
+        <v>466113</v>
       </c>
       <c r="R14" t="n">
-        <v>7055914</v>
+        <v>7055912</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2024,7 +2022,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2051,7 +2049,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124808162</v>
+        <v>124808158</v>
       </c>
       <c r="B15" t="n">
         <v>57513</v>
@@ -2091,10 +2089,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>465856</v>
+        <v>465957</v>
       </c>
       <c r="R15" t="n">
-        <v>7055738</v>
+        <v>7055698</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2158,10 +2156,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124808190</v>
+        <v>124808144</v>
       </c>
       <c r="B16" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2174,21 +2172,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2198,10 +2196,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466147</v>
+        <v>466231</v>
       </c>
       <c r="R16" t="n">
-        <v>7056067</v>
+        <v>7056150</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2234,6 +2232,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2260,7 +2263,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124808148</v>
+        <v>124808142</v>
       </c>
       <c r="B17" t="n">
         <v>57513</v>
@@ -2300,10 +2303,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466190</v>
+        <v>466212</v>
       </c>
       <c r="R17" t="n">
-        <v>7055952</v>
+        <v>7056170</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2367,7 +2370,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124808159</v>
+        <v>124808133</v>
       </c>
       <c r="B18" t="n">
         <v>57513</v>
@@ -2407,10 +2410,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>465930</v>
+        <v>466022</v>
       </c>
       <c r="R18" t="n">
-        <v>7055704</v>
+        <v>7055840</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2447,7 +2450,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2474,7 +2477,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124808161</v>
+        <v>124808154</v>
       </c>
       <c r="B19" t="n">
         <v>57513</v>
@@ -2514,10 +2517,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>465859</v>
+        <v>466093</v>
       </c>
       <c r="R19" t="n">
-        <v>7055744</v>
+        <v>7055760</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2581,10 +2584,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124808146</v>
+        <v>124808190</v>
       </c>
       <c r="B20" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2597,21 +2600,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2621,10 +2624,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466210</v>
+        <v>466147</v>
       </c>
       <c r="R20" t="n">
-        <v>7056130</v>
+        <v>7056067</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2657,11 +2660,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2688,10 +2686,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124808188</v>
+        <v>124808143</v>
       </c>
       <c r="B21" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2704,21 +2702,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2728,10 +2726,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>466015</v>
+        <v>466291</v>
       </c>
       <c r="R21" t="n">
-        <v>7055934</v>
+        <v>7056076</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2764,6 +2762,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2790,10 +2793,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124808136</v>
+        <v>124808183</v>
       </c>
       <c r="B22" t="n">
-        <v>57513</v>
+        <v>91299</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2806,21 +2809,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2830,10 +2833,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>466032</v>
+        <v>465924</v>
       </c>
       <c r="R22" t="n">
-        <v>7055802</v>
+        <v>7055722</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2866,11 +2869,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2897,7 +2895,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124808154</v>
+        <v>124808148</v>
       </c>
       <c r="B23" t="n">
         <v>57513</v>
@@ -2937,10 +2935,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>466093</v>
+        <v>466190</v>
       </c>
       <c r="R23" t="n">
-        <v>7055760</v>
+        <v>7055952</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3004,7 +3002,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124808135</v>
+        <v>124808160</v>
       </c>
       <c r="B24" t="n">
         <v>57513</v>
@@ -3044,10 +3042,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>466024</v>
+        <v>465939</v>
       </c>
       <c r="R24" t="n">
-        <v>7055801</v>
+        <v>7055717</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3111,10 +3109,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124808183</v>
+        <v>124808161</v>
       </c>
       <c r="B25" t="n">
-        <v>91299</v>
+        <v>57513</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3127,21 +3125,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3151,10 +3149,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>465924</v>
+        <v>465859</v>
       </c>
       <c r="R25" t="n">
-        <v>7055722</v>
+        <v>7055744</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3187,6 +3185,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3213,7 +3216,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124808160</v>
+        <v>124808162</v>
       </c>
       <c r="B26" t="n">
         <v>57513</v>
@@ -3253,10 +3256,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>465939</v>
+        <v>465856</v>
       </c>
       <c r="R26" t="n">
-        <v>7055717</v>
+        <v>7055738</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3320,10 +3323,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124808151</v>
+        <v>124808185</v>
       </c>
       <c r="B27" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3336,21 +3339,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3360,10 +3363,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466148</v>
+        <v>466191</v>
       </c>
       <c r="R27" t="n">
-        <v>7055732</v>
+        <v>7055781</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3396,11 +3399,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3427,7 +3425,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124808134</v>
+        <v>124808146</v>
       </c>
       <c r="B28" t="n">
         <v>57513</v>
@@ -3467,10 +3465,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466020</v>
+        <v>466210</v>
       </c>
       <c r="R28" t="n">
-        <v>7055801</v>
+        <v>7056130</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3534,10 +3532,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124808156</v>
+        <v>124808184</v>
       </c>
       <c r="B29" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3550,21 +3548,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3574,10 +3572,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466027</v>
+        <v>466183</v>
       </c>
       <c r="R29" t="n">
-        <v>7055757</v>
+        <v>7056145</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3610,11 +3608,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3641,10 +3634,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124808142</v>
+        <v>124808182</v>
       </c>
       <c r="B30" t="n">
-        <v>57513</v>
+        <v>79892</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3657,21 +3650,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3681,10 +3674,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>466212</v>
+        <v>466191</v>
       </c>
       <c r="R30" t="n">
-        <v>7056170</v>
+        <v>7055781</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3717,11 +3710,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3748,7 +3736,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124808126</v>
+        <v>124808139</v>
       </c>
       <c r="B31" t="n">
         <v>57513</v>
@@ -3788,10 +3776,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>465931</v>
+        <v>466126</v>
       </c>
       <c r="R31" t="n">
-        <v>7055792</v>
+        <v>7055914</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3828,7 +3816,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3855,7 +3843,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124808147</v>
+        <v>124808156</v>
       </c>
       <c r="B32" t="n">
         <v>57513</v>
@@ -3895,10 +3883,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466151</v>
+        <v>466027</v>
       </c>
       <c r="R32" t="n">
-        <v>7055999</v>
+        <v>7055757</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3962,7 +3950,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124808132</v>
+        <v>124808149</v>
       </c>
       <c r="B33" t="n">
         <v>57513</v>
@@ -4002,10 +3990,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466002</v>
+        <v>466219</v>
       </c>
       <c r="R33" t="n">
-        <v>7055866</v>
+        <v>7055842</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4042,7 +4030,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4069,7 +4057,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124808138</v>
+        <v>124808134</v>
       </c>
       <c r="B34" t="n">
         <v>57513</v>
@@ -4109,10 +4097,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>466123</v>
+        <v>466020</v>
       </c>
       <c r="R34" t="n">
-        <v>7055839</v>
+        <v>7055801</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4176,7 +4164,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124808150</v>
+        <v>124808136</v>
       </c>
       <c r="B35" t="n">
         <v>57513</v>
@@ -4216,10 +4204,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>466187</v>
+        <v>466032</v>
       </c>
       <c r="R35" t="n">
-        <v>7055846</v>
+        <v>7055802</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4256,7 +4244,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4283,7 +4271,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124808140</v>
+        <v>124808132</v>
       </c>
       <c r="B36" t="n">
         <v>57513</v>
@@ -4323,10 +4311,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>466113</v>
+        <v>466002</v>
       </c>
       <c r="R36" t="n">
-        <v>7055912</v>
+        <v>7055866</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4390,7 +4378,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124808145</v>
+        <v>124808138</v>
       </c>
       <c r="B37" t="n">
         <v>57513</v>
@@ -4430,10 +4418,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>466217</v>
+        <v>466123</v>
       </c>
       <c r="R37" t="n">
-        <v>7056120</v>
+        <v>7055839</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4497,7 +4485,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124808125</v>
+        <v>124808131</v>
       </c>
       <c r="B38" t="n">
         <v>57513</v>
@@ -4531,24 +4519,16 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Åkerån, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>466019</v>
+        <v>466023</v>
       </c>
       <c r="R38" t="n">
-        <v>7055741</v>
+        <v>7055886</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4585,7 +4565,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Bohål ca 6m upp i bruten gran</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4612,7 +4592,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124808133</v>
+        <v>124808126</v>
       </c>
       <c r="B39" t="n">
         <v>57513</v>
@@ -4652,10 +4632,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>466022</v>
+        <v>465931</v>
       </c>
       <c r="R39" t="n">
-        <v>7055840</v>
+        <v>7055792</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4719,10 +4699,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124808123</v>
+        <v>124808157</v>
       </c>
       <c r="B40" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4735,21 +4715,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4759,10 +4739,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>465924</v>
+        <v>466023</v>
       </c>
       <c r="R40" t="n">
-        <v>7055720</v>
+        <v>7055706</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4795,6 +4775,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4821,7 +4806,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124808189</v>
+        <v>124808195</v>
       </c>
       <c r="B41" t="n">
         <v>91030</v>
@@ -4861,10 +4846,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>466286</v>
+        <v>466026</v>
       </c>
       <c r="R41" t="n">
-        <v>7056084</v>
+        <v>7055714</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4923,10 +4908,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124808195</v>
+        <v>124808145</v>
       </c>
       <c r="B42" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4939,21 +4924,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4963,10 +4948,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>466026</v>
+        <v>466217</v>
       </c>
       <c r="R42" t="n">
-        <v>7055714</v>
+        <v>7056120</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4999,6 +4984,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5025,10 +5015,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124808143</v>
+        <v>124808194</v>
       </c>
       <c r="B43" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5041,21 +5031,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5065,10 +5055,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>466291</v>
+        <v>466020</v>
       </c>
       <c r="R43" t="n">
-        <v>7056076</v>
+        <v>7055742</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5101,11 +5091,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5239,10 +5224,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124808193</v>
+        <v>124808137</v>
       </c>
       <c r="B45" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5255,21 +5240,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5279,10 +5264,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>466155</v>
+        <v>466097</v>
       </c>
       <c r="R45" t="n">
-        <v>7055735</v>
+        <v>7055831</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5315,6 +5300,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5341,10 +5331,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124808187</v>
+        <v>124808159</v>
       </c>
       <c r="B46" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5357,21 +5347,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5381,10 +5371,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>465961</v>
+        <v>465930</v>
       </c>
       <c r="R46" t="n">
-        <v>7055835</v>
+        <v>7055704</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5417,6 +5407,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5443,10 +5438,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124808185</v>
+        <v>124808155</v>
       </c>
       <c r="B47" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5459,21 +5454,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5483,10 +5478,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>466191</v>
+        <v>466025</v>
       </c>
       <c r="R47" t="n">
-        <v>7055781</v>
+        <v>7055769</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5519,6 +5514,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5545,7 +5545,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124808157</v>
+        <v>124808147</v>
       </c>
       <c r="B48" t="n">
         <v>57513</v>
@@ -5585,10 +5585,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>466023</v>
+        <v>466151</v>
       </c>
       <c r="R48" t="n">
-        <v>7055706</v>
+        <v>7055999</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>

--- a/artfynd/A 11097-2024 artfynd.xlsx
+++ b/artfynd/A 11097-2024 artfynd.xlsx
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124808187</v>
+        <v>124808127</v>
       </c>
       <c r="B3" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,21 +806,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465961</v>
+        <v>465979</v>
       </c>
       <c r="R3" t="n">
-        <v>7055835</v>
+        <v>7055862</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,6 +866,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124808127</v>
+        <v>124808187</v>
       </c>
       <c r="B4" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465979</v>
+        <v>465961</v>
       </c>
       <c r="R4" t="n">
-        <v>7055862</v>
+        <v>7055835</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -968,11 +973,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -2370,7 +2370,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124808133</v>
+        <v>124808154</v>
       </c>
       <c r="B18" t="n">
         <v>57513</v>
@@ -2410,10 +2410,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466022</v>
+        <v>466093</v>
       </c>
       <c r="R18" t="n">
-        <v>7055840</v>
+        <v>7055760</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2477,7 +2477,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124808154</v>
+        <v>124808133</v>
       </c>
       <c r="B19" t="n">
         <v>57513</v>
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466093</v>
+        <v>466022</v>
       </c>
       <c r="R19" t="n">
-        <v>7055760</v>
+        <v>7055840</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 11097-2024 artfynd.xlsx
+++ b/artfynd/A 11097-2024 artfynd.xlsx
@@ -1840,10 +1840,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124808188</v>
+        <v>124808140</v>
       </c>
       <c r="B13" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1856,21 +1856,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1880,10 +1880,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466015</v>
+        <v>466113</v>
       </c>
       <c r="R13" t="n">
-        <v>7055934</v>
+        <v>7055912</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1916,6 +1916,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1942,7 +1947,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124808140</v>
+        <v>124808158</v>
       </c>
       <c r="B14" t="n">
         <v>57513</v>
@@ -1982,10 +1987,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>466113</v>
+        <v>465957</v>
       </c>
       <c r="R14" t="n">
-        <v>7055912</v>
+        <v>7055698</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2049,10 +2054,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124808158</v>
+        <v>124808188</v>
       </c>
       <c r="B15" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2065,21 +2070,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2089,10 +2094,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>465957</v>
+        <v>466015</v>
       </c>
       <c r="R15" t="n">
-        <v>7055698</v>
+        <v>7055934</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2125,11 +2130,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 11097-2024 artfynd.xlsx
+++ b/artfynd/A 11097-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124808125</v>
+        <v>124808187</v>
       </c>
       <c r="B2" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,42 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Åkerån, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>466019</v>
+        <v>465961</v>
       </c>
       <c r="R2" t="n">
-        <v>7055741</v>
+        <v>7055835</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Bohål ca 6m upp i bruten gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124808127</v>
+        <v>124808160</v>
       </c>
       <c r="B3" t="n">
         <v>57513</v>
@@ -830,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465979</v>
+        <v>465939</v>
       </c>
       <c r="R3" t="n">
-        <v>7055862</v>
+        <v>7055717</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124808187</v>
+        <v>124808139</v>
       </c>
       <c r="B4" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465961</v>
+        <v>466126</v>
       </c>
       <c r="R4" t="n">
-        <v>7055835</v>
+        <v>7055914</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -973,6 +960,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124808123</v>
+        <v>124808136</v>
       </c>
       <c r="B5" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1015,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1039,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465924</v>
+        <v>466032</v>
       </c>
       <c r="R5" t="n">
-        <v>7055720</v>
+        <v>7055802</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1075,6 +1067,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1101,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124808193</v>
+        <v>124808148</v>
       </c>
       <c r="B6" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1117,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1141,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466155</v>
+        <v>466190</v>
       </c>
       <c r="R6" t="n">
-        <v>7055735</v>
+        <v>7055952</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1177,6 +1174,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1203,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124808135</v>
+        <v>124808161</v>
       </c>
       <c r="B7" t="n">
         <v>57513</v>
@@ -1243,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466024</v>
+        <v>465859</v>
       </c>
       <c r="R7" t="n">
-        <v>7055801</v>
+        <v>7055744</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1310,7 +1312,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124808152</v>
+        <v>124808158</v>
       </c>
       <c r="B8" t="n">
         <v>57513</v>
@@ -1350,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466072</v>
+        <v>465957</v>
       </c>
       <c r="R8" t="n">
-        <v>7055589</v>
+        <v>7055698</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124808151</v>
+        <v>124808182</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>79892</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466148</v>
+        <v>466191</v>
       </c>
       <c r="R9" t="n">
-        <v>7055732</v>
+        <v>7055781</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1493,11 +1495,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1524,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124808189</v>
+        <v>124808183</v>
       </c>
       <c r="B10" t="n">
-        <v>91030</v>
+        <v>91299</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1540,21 +1537,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1564,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466286</v>
+        <v>465924</v>
       </c>
       <c r="R10" t="n">
-        <v>7056084</v>
+        <v>7055722</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1626,7 +1623,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124808150</v>
+        <v>124808144</v>
       </c>
       <c r="B11" t="n">
         <v>57513</v>
@@ -1666,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466187</v>
+        <v>466231</v>
       </c>
       <c r="R11" t="n">
-        <v>7055846</v>
+        <v>7056150</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1706,7 +1703,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1733,7 +1730,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124808129</v>
+        <v>124808131</v>
       </c>
       <c r="B12" t="n">
         <v>57513</v>
@@ -1773,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>465997</v>
+        <v>466023</v>
       </c>
       <c r="R12" t="n">
-        <v>7055926</v>
+        <v>7055886</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1813,7 +1810,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1840,7 +1837,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124808140</v>
+        <v>124808157</v>
       </c>
       <c r="B13" t="n">
         <v>57513</v>
@@ -1880,10 +1877,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466113</v>
+        <v>466023</v>
       </c>
       <c r="R13" t="n">
-        <v>7055912</v>
+        <v>7055706</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,7 +1944,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124808158</v>
+        <v>124808155</v>
       </c>
       <c r="B14" t="n">
         <v>57513</v>
@@ -1987,10 +1984,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>465957</v>
+        <v>466025</v>
       </c>
       <c r="R14" t="n">
-        <v>7055698</v>
+        <v>7055769</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2054,10 +2051,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124808188</v>
+        <v>124808184</v>
       </c>
       <c r="B15" t="n">
-        <v>91030</v>
+        <v>79891</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2070,21 +2067,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2094,10 +2091,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>466015</v>
+        <v>466183</v>
       </c>
       <c r="R15" t="n">
-        <v>7055934</v>
+        <v>7056145</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2156,7 +2153,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124808144</v>
+        <v>124808145</v>
       </c>
       <c r="B16" t="n">
         <v>57513</v>
@@ -2196,10 +2193,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466231</v>
+        <v>466217</v>
       </c>
       <c r="R16" t="n">
-        <v>7056150</v>
+        <v>7056120</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2263,10 +2260,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124808142</v>
+        <v>124808123</v>
       </c>
       <c r="B17" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2279,21 +2276,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2303,10 +2300,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466212</v>
+        <v>465924</v>
       </c>
       <c r="R17" t="n">
-        <v>7056170</v>
+        <v>7055720</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2339,11 +2336,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2370,10 +2362,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124808154</v>
+        <v>124808194</v>
       </c>
       <c r="B18" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2386,21 +2378,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2410,10 +2402,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466093</v>
+        <v>466020</v>
       </c>
       <c r="R18" t="n">
-        <v>7055760</v>
+        <v>7055742</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2446,11 +2438,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2477,10 +2464,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124808133</v>
+        <v>124808195</v>
       </c>
       <c r="B19" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2493,21 +2480,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2517,10 +2504,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466022</v>
+        <v>466026</v>
       </c>
       <c r="R19" t="n">
-        <v>7055840</v>
+        <v>7055714</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2553,11 +2540,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2584,10 +2566,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124808190</v>
+        <v>124808143</v>
       </c>
       <c r="B20" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2600,21 +2582,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2624,10 +2606,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466147</v>
+        <v>466291</v>
       </c>
       <c r="R20" t="n">
-        <v>7056067</v>
+        <v>7056076</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2660,6 +2642,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2686,7 +2673,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124808143</v>
+        <v>124808138</v>
       </c>
       <c r="B21" t="n">
         <v>57513</v>
@@ -2726,10 +2713,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>466291</v>
+        <v>466123</v>
       </c>
       <c r="R21" t="n">
-        <v>7056076</v>
+        <v>7055839</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2793,10 +2780,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124808183</v>
+        <v>124808189</v>
       </c>
       <c r="B22" t="n">
-        <v>91299</v>
+        <v>91030</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2809,21 +2796,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2833,10 +2820,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>465924</v>
+        <v>466286</v>
       </c>
       <c r="R22" t="n">
-        <v>7055722</v>
+        <v>7056084</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2895,7 +2882,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124808148</v>
+        <v>124808134</v>
       </c>
       <c r="B23" t="n">
         <v>57513</v>
@@ -2935,10 +2922,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>466190</v>
+        <v>466020</v>
       </c>
       <c r="R23" t="n">
-        <v>7055952</v>
+        <v>7055801</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3002,10 +2989,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124808160</v>
+        <v>124808188</v>
       </c>
       <c r="B24" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3018,21 +3005,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3042,10 +3029,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>465939</v>
+        <v>466015</v>
       </c>
       <c r="R24" t="n">
-        <v>7055717</v>
+        <v>7055934</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3078,11 +3065,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3109,10 +3091,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124808161</v>
+        <v>124808185</v>
       </c>
       <c r="B25" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3125,21 +3107,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3149,10 +3131,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>465859</v>
+        <v>466191</v>
       </c>
       <c r="R25" t="n">
-        <v>7055744</v>
+        <v>7055781</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3185,11 +3167,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3216,7 +3193,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124808162</v>
+        <v>124808125</v>
       </c>
       <c r="B26" t="n">
         <v>57513</v>
@@ -3250,16 +3227,24 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Åkerån, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>465856</v>
+        <v>466019</v>
       </c>
       <c r="R26" t="n">
-        <v>7055738</v>
+        <v>7055741</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3296,7 +3281,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Bohål ca 6m upp i bruten gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3323,10 +3308,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124808185</v>
+        <v>124808147</v>
       </c>
       <c r="B27" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3339,21 +3324,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3363,10 +3348,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466191</v>
+        <v>466151</v>
       </c>
       <c r="R27" t="n">
-        <v>7055781</v>
+        <v>7055999</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3399,6 +3384,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3425,7 +3415,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124808146</v>
+        <v>124808154</v>
       </c>
       <c r="B28" t="n">
         <v>57513</v>
@@ -3465,10 +3455,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466210</v>
+        <v>466093</v>
       </c>
       <c r="R28" t="n">
-        <v>7056130</v>
+        <v>7055760</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3532,10 +3522,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124808184</v>
+        <v>124808152</v>
       </c>
       <c r="B29" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3548,21 +3538,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3572,10 +3562,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466183</v>
+        <v>466072</v>
       </c>
       <c r="R29" t="n">
-        <v>7056145</v>
+        <v>7055589</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3608,6 +3598,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3634,10 +3629,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124808182</v>
+        <v>124808146</v>
       </c>
       <c r="B30" t="n">
-        <v>79892</v>
+        <v>57513</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3650,21 +3645,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3674,10 +3669,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>466191</v>
+        <v>466210</v>
       </c>
       <c r="R30" t="n">
-        <v>7055781</v>
+        <v>7056130</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3710,6 +3705,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3736,7 +3736,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124808139</v>
+        <v>124808141</v>
       </c>
       <c r="B31" t="n">
         <v>57513</v>
@@ -3776,10 +3776,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466126</v>
+        <v>466172</v>
       </c>
       <c r="R31" t="n">
-        <v>7055914</v>
+        <v>7056129</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3816,7 +3816,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3843,7 +3843,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124808156</v>
+        <v>124808162</v>
       </c>
       <c r="B32" t="n">
         <v>57513</v>
@@ -3883,10 +3883,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466027</v>
+        <v>465856</v>
       </c>
       <c r="R32" t="n">
-        <v>7055757</v>
+        <v>7055738</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3950,10 +3950,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124808149</v>
+        <v>124808193</v>
       </c>
       <c r="B33" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3966,21 +3966,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3990,10 +3990,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466219</v>
+        <v>466155</v>
       </c>
       <c r="R33" t="n">
-        <v>7055842</v>
+        <v>7055735</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4026,11 +4026,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4057,7 +4052,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124808134</v>
+        <v>124808129</v>
       </c>
       <c r="B34" t="n">
         <v>57513</v>
@@ -4097,10 +4092,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>466020</v>
+        <v>465997</v>
       </c>
       <c r="R34" t="n">
-        <v>7055801</v>
+        <v>7055926</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4137,7 +4132,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4164,7 +4159,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124808136</v>
+        <v>124808159</v>
       </c>
       <c r="B35" t="n">
         <v>57513</v>
@@ -4204,10 +4199,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>466032</v>
+        <v>465930</v>
       </c>
       <c r="R35" t="n">
-        <v>7055802</v>
+        <v>7055704</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4244,7 +4239,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4378,7 +4373,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124808138</v>
+        <v>124808137</v>
       </c>
       <c r="B37" t="n">
         <v>57513</v>
@@ -4418,10 +4413,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>466123</v>
+        <v>466097</v>
       </c>
       <c r="R37" t="n">
-        <v>7055839</v>
+        <v>7055831</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4458,7 +4453,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4485,10 +4480,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124808131</v>
+        <v>124808190</v>
       </c>
       <c r="B38" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4501,21 +4496,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4525,10 +4520,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>466023</v>
+        <v>466147</v>
       </c>
       <c r="R38" t="n">
-        <v>7055886</v>
+        <v>7056067</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4561,11 +4556,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4592,7 +4582,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124808126</v>
+        <v>124808149</v>
       </c>
       <c r="B39" t="n">
         <v>57513</v>
@@ -4632,10 +4622,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>465931</v>
+        <v>466219</v>
       </c>
       <c r="R39" t="n">
-        <v>7055792</v>
+        <v>7055842</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4672,7 +4662,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4699,7 +4689,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124808157</v>
+        <v>124808133</v>
       </c>
       <c r="B40" t="n">
         <v>57513</v>
@@ -4739,10 +4729,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>466023</v>
+        <v>466022</v>
       </c>
       <c r="R40" t="n">
-        <v>7055706</v>
+        <v>7055840</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4806,10 +4796,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124808195</v>
+        <v>124808150</v>
       </c>
       <c r="B41" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4822,21 +4812,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4846,10 +4836,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>466026</v>
+        <v>466187</v>
       </c>
       <c r="R41" t="n">
-        <v>7055714</v>
+        <v>7055846</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4882,6 +4872,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4908,7 +4903,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124808145</v>
+        <v>124808140</v>
       </c>
       <c r="B42" t="n">
         <v>57513</v>
@@ -4948,10 +4943,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>466217</v>
+        <v>466113</v>
       </c>
       <c r="R42" t="n">
-        <v>7056120</v>
+        <v>7055912</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5015,10 +5010,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124808194</v>
+        <v>124808135</v>
       </c>
       <c r="B43" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5031,21 +5026,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5055,10 +5050,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>466020</v>
+        <v>466024</v>
       </c>
       <c r="R43" t="n">
-        <v>7055742</v>
+        <v>7055801</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5091,6 +5086,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5117,7 +5117,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124808141</v>
+        <v>124808142</v>
       </c>
       <c r="B44" t="n">
         <v>57513</v>
@@ -5157,10 +5157,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>466172</v>
+        <v>466212</v>
       </c>
       <c r="R44" t="n">
-        <v>7056129</v>
+        <v>7056170</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5224,7 +5224,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124808137</v>
+        <v>124808151</v>
       </c>
       <c r="B45" t="n">
         <v>57513</v>
@@ -5264,10 +5264,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>466097</v>
+        <v>466148</v>
       </c>
       <c r="R45" t="n">
-        <v>7055831</v>
+        <v>7055732</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5304,7 +5304,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5331,7 +5331,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124808159</v>
+        <v>124808156</v>
       </c>
       <c r="B46" t="n">
         <v>57513</v>
@@ -5371,10 +5371,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>465930</v>
+        <v>466027</v>
       </c>
       <c r="R46" t="n">
-        <v>7055704</v>
+        <v>7055757</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5438,7 +5438,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124808155</v>
+        <v>124808126</v>
       </c>
       <c r="B47" t="n">
         <v>57513</v>
@@ -5478,10 +5478,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>466025</v>
+        <v>465931</v>
       </c>
       <c r="R47" t="n">
-        <v>7055769</v>
+        <v>7055792</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5545,7 +5545,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124808147</v>
+        <v>124808127</v>
       </c>
       <c r="B48" t="n">
         <v>57513</v>
@@ -5585,10 +5585,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>466151</v>
+        <v>465979</v>
       </c>
       <c r="R48" t="n">
-        <v>7055999</v>
+        <v>7055862</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>

--- a/artfynd/A 11097-2024 artfynd.xlsx
+++ b/artfynd/A 11097-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124808187</v>
+        <v>124808155</v>
       </c>
       <c r="B2" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>465961</v>
+        <v>466025</v>
       </c>
       <c r="R2" t="n">
-        <v>7055835</v>
+        <v>7055769</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124808160</v>
+        <v>124808158</v>
       </c>
       <c r="B3" t="n">
         <v>57513</v>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465939</v>
+        <v>465957</v>
       </c>
       <c r="R3" t="n">
-        <v>7055717</v>
+        <v>7055698</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124808139</v>
+        <v>124808127</v>
       </c>
       <c r="B4" t="n">
         <v>57513</v>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>466126</v>
+        <v>465979</v>
       </c>
       <c r="R4" t="n">
-        <v>7055914</v>
+        <v>7055862</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124808136</v>
+        <v>124808162</v>
       </c>
       <c r="B5" t="n">
         <v>57513</v>
@@ -1031,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>466032</v>
+        <v>465856</v>
       </c>
       <c r="R5" t="n">
-        <v>7055802</v>
+        <v>7055738</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124808148</v>
+        <v>124808183</v>
       </c>
       <c r="B6" t="n">
-        <v>57513</v>
+        <v>91299</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466190</v>
+        <v>465924</v>
       </c>
       <c r="R6" t="n">
-        <v>7055952</v>
+        <v>7055722</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1174,11 +1179,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124808161</v>
+        <v>124808139</v>
       </c>
       <c r="B7" t="n">
         <v>57513</v>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>465859</v>
+        <v>466126</v>
       </c>
       <c r="R7" t="n">
-        <v>7055744</v>
+        <v>7055914</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,7 +1312,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124808158</v>
+        <v>124808143</v>
       </c>
       <c r="B8" t="n">
         <v>57513</v>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>465957</v>
+        <v>466291</v>
       </c>
       <c r="R8" t="n">
-        <v>7055698</v>
+        <v>7056076</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1419,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124808182</v>
+        <v>124808154</v>
       </c>
       <c r="B9" t="n">
-        <v>79892</v>
+        <v>57513</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1435,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466191</v>
+        <v>466093</v>
       </c>
       <c r="R9" t="n">
-        <v>7055781</v>
+        <v>7055760</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1495,6 +1495,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,10 +1526,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124808183</v>
+        <v>124808147</v>
       </c>
       <c r="B10" t="n">
-        <v>91299</v>
+        <v>57513</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1537,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1561,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>465924</v>
+        <v>466151</v>
       </c>
       <c r="R10" t="n">
-        <v>7055722</v>
+        <v>7055999</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1597,6 +1602,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1623,10 +1633,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124808144</v>
+        <v>124808194</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1639,21 +1649,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1663,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466231</v>
+        <v>466020</v>
       </c>
       <c r="R11" t="n">
-        <v>7056150</v>
+        <v>7055742</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1699,11 +1709,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1730,7 +1735,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124808131</v>
+        <v>124808132</v>
       </c>
       <c r="B12" t="n">
         <v>57513</v>
@@ -1770,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466023</v>
+        <v>466002</v>
       </c>
       <c r="R12" t="n">
-        <v>7055886</v>
+        <v>7055866</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1837,10 +1842,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124808157</v>
+        <v>124808193</v>
       </c>
       <c r="B13" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1853,21 +1858,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1877,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466023</v>
+        <v>466155</v>
       </c>
       <c r="R13" t="n">
-        <v>7055706</v>
+        <v>7055735</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1913,11 +1918,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1944,10 +1944,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124808155</v>
+        <v>124808195</v>
       </c>
       <c r="B14" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1960,21 +1960,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1984,10 +1984,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>466025</v>
+        <v>466026</v>
       </c>
       <c r="R14" t="n">
-        <v>7055769</v>
+        <v>7055714</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2020,11 +2020,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2051,10 +2046,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124808184</v>
+        <v>124808129</v>
       </c>
       <c r="B15" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2067,21 +2062,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2091,10 +2086,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>466183</v>
+        <v>465997</v>
       </c>
       <c r="R15" t="n">
-        <v>7056145</v>
+        <v>7055926</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2127,6 +2122,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2260,10 +2260,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124808123</v>
+        <v>124808160</v>
       </c>
       <c r="B17" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2276,21 +2276,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2300,10 +2300,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>465924</v>
+        <v>465939</v>
       </c>
       <c r="R17" t="n">
-        <v>7055720</v>
+        <v>7055717</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2336,6 +2336,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2362,7 +2367,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124808194</v>
+        <v>124808189</v>
       </c>
       <c r="B18" t="n">
         <v>91030</v>
@@ -2402,10 +2407,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466020</v>
+        <v>466286</v>
       </c>
       <c r="R18" t="n">
-        <v>7055742</v>
+        <v>7056084</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2464,10 +2469,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124808195</v>
+        <v>124808123</v>
       </c>
       <c r="B19" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2480,21 +2485,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2504,10 +2509,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466026</v>
+        <v>465924</v>
       </c>
       <c r="R19" t="n">
-        <v>7055714</v>
+        <v>7055720</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2566,7 +2571,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124808143</v>
+        <v>124808131</v>
       </c>
       <c r="B20" t="n">
         <v>57513</v>
@@ -2606,10 +2611,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466291</v>
+        <v>466023</v>
       </c>
       <c r="R20" t="n">
-        <v>7056076</v>
+        <v>7055886</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2673,7 +2678,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124808138</v>
+        <v>124808146</v>
       </c>
       <c r="B21" t="n">
         <v>57513</v>
@@ -2713,10 +2718,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>466123</v>
+        <v>466210</v>
       </c>
       <c r="R21" t="n">
-        <v>7055839</v>
+        <v>7056130</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2780,10 +2785,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124808189</v>
+        <v>124808142</v>
       </c>
       <c r="B22" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2796,21 +2801,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2820,10 +2825,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>466286</v>
+        <v>466212</v>
       </c>
       <c r="R22" t="n">
-        <v>7056084</v>
+        <v>7056170</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2856,6 +2861,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2882,10 +2892,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124808134</v>
+        <v>124808182</v>
       </c>
       <c r="B23" t="n">
-        <v>57513</v>
+        <v>79892</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2898,21 +2908,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2922,10 +2932,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>466020</v>
+        <v>466191</v>
       </c>
       <c r="R23" t="n">
-        <v>7055801</v>
+        <v>7055781</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2958,11 +2968,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2989,7 +2994,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124808188</v>
+        <v>124808187</v>
       </c>
       <c r="B24" t="n">
         <v>91030</v>
@@ -3029,10 +3034,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>466015</v>
+        <v>465961</v>
       </c>
       <c r="R24" t="n">
-        <v>7055934</v>
+        <v>7055835</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3091,10 +3096,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124808185</v>
+        <v>124808125</v>
       </c>
       <c r="B25" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3107,34 +3112,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Åkerån, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>466191</v>
+        <v>466019</v>
       </c>
       <c r="R25" t="n">
-        <v>7055781</v>
+        <v>7055741</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3167,6 +3180,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Bohål ca 6m upp i bruten gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3193,7 +3211,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124808125</v>
+        <v>124808148</v>
       </c>
       <c r="B26" t="n">
         <v>57513</v>
@@ -3227,24 +3245,16 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Åkerån, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466019</v>
+        <v>466190</v>
       </c>
       <c r="R26" t="n">
-        <v>7055741</v>
+        <v>7055952</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3281,7 +3291,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Bohål ca 6m upp i bruten gran</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3308,7 +3318,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124808147</v>
+        <v>124808151</v>
       </c>
       <c r="B27" t="n">
         <v>57513</v>
@@ -3348,10 +3358,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466151</v>
+        <v>466148</v>
       </c>
       <c r="R27" t="n">
-        <v>7055999</v>
+        <v>7055732</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3415,7 +3425,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124808154</v>
+        <v>124808136</v>
       </c>
       <c r="B28" t="n">
         <v>57513</v>
@@ -3455,10 +3465,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466093</v>
+        <v>466032</v>
       </c>
       <c r="R28" t="n">
-        <v>7055760</v>
+        <v>7055802</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3522,7 +3532,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124808152</v>
+        <v>124808144</v>
       </c>
       <c r="B29" t="n">
         <v>57513</v>
@@ -3562,10 +3572,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466072</v>
+        <v>466231</v>
       </c>
       <c r="R29" t="n">
-        <v>7055589</v>
+        <v>7056150</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3629,7 +3639,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124808146</v>
+        <v>124808140</v>
       </c>
       <c r="B30" t="n">
         <v>57513</v>
@@ -3669,10 +3679,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>466210</v>
+        <v>466113</v>
       </c>
       <c r="R30" t="n">
-        <v>7056130</v>
+        <v>7055912</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3843,7 +3853,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124808162</v>
+        <v>124808133</v>
       </c>
       <c r="B32" t="n">
         <v>57513</v>
@@ -3883,10 +3893,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>465856</v>
+        <v>466022</v>
       </c>
       <c r="R32" t="n">
-        <v>7055738</v>
+        <v>7055840</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3950,10 +3960,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124808193</v>
+        <v>124808126</v>
       </c>
       <c r="B33" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3966,21 +3976,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3990,10 +4000,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466155</v>
+        <v>465931</v>
       </c>
       <c r="R33" t="n">
-        <v>7055735</v>
+        <v>7055792</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4026,6 +4036,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4052,7 +4067,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124808129</v>
+        <v>124808157</v>
       </c>
       <c r="B34" t="n">
         <v>57513</v>
@@ -4092,10 +4107,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>465997</v>
+        <v>466023</v>
       </c>
       <c r="R34" t="n">
-        <v>7055926</v>
+        <v>7055706</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4132,7 +4147,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4159,7 +4174,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124808159</v>
+        <v>124808161</v>
       </c>
       <c r="B35" t="n">
         <v>57513</v>
@@ -4199,10 +4214,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>465930</v>
+        <v>465859</v>
       </c>
       <c r="R35" t="n">
-        <v>7055704</v>
+        <v>7055744</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4239,7 +4254,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4266,10 +4281,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124808132</v>
+        <v>124808185</v>
       </c>
       <c r="B36" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4282,21 +4297,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4306,10 +4321,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>466002</v>
+        <v>466191</v>
       </c>
       <c r="R36" t="n">
-        <v>7055866</v>
+        <v>7055781</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4342,11 +4357,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4373,10 +4383,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124808137</v>
+        <v>124808184</v>
       </c>
       <c r="B37" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4389,21 +4399,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4413,10 +4423,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>466097</v>
+        <v>466183</v>
       </c>
       <c r="R37" t="n">
-        <v>7055831</v>
+        <v>7056145</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4449,11 +4459,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4480,10 +4485,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124808190</v>
+        <v>124808156</v>
       </c>
       <c r="B38" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4496,21 +4501,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4520,10 +4525,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>466147</v>
+        <v>466027</v>
       </c>
       <c r="R38" t="n">
-        <v>7056067</v>
+        <v>7055757</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4556,6 +4561,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4582,7 +4592,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124808149</v>
+        <v>124808150</v>
       </c>
       <c r="B39" t="n">
         <v>57513</v>
@@ -4622,10 +4632,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>466219</v>
+        <v>466187</v>
       </c>
       <c r="R39" t="n">
-        <v>7055842</v>
+        <v>7055846</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4689,7 +4699,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124808133</v>
+        <v>124808138</v>
       </c>
       <c r="B40" t="n">
         <v>57513</v>
@@ -4729,10 +4739,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>466022</v>
+        <v>466123</v>
       </c>
       <c r="R40" t="n">
-        <v>7055840</v>
+        <v>7055839</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4796,7 +4806,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124808150</v>
+        <v>124808159</v>
       </c>
       <c r="B41" t="n">
         <v>57513</v>
@@ -4836,10 +4846,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>466187</v>
+        <v>465930</v>
       </c>
       <c r="R41" t="n">
-        <v>7055846</v>
+        <v>7055704</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4903,10 +4913,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124808140</v>
+        <v>124808190</v>
       </c>
       <c r="B42" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4919,21 +4929,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4943,10 +4953,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>466113</v>
+        <v>466147</v>
       </c>
       <c r="R42" t="n">
-        <v>7055912</v>
+        <v>7056067</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4979,11 +4989,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5010,10 +5015,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124808135</v>
+        <v>124808188</v>
       </c>
       <c r="B43" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5026,21 +5031,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5050,10 +5055,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>466024</v>
+        <v>466015</v>
       </c>
       <c r="R43" t="n">
-        <v>7055801</v>
+        <v>7055934</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5086,11 +5091,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5117,7 +5117,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124808142</v>
+        <v>124808134</v>
       </c>
       <c r="B44" t="n">
         <v>57513</v>
@@ -5157,10 +5157,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>466212</v>
+        <v>466020</v>
       </c>
       <c r="R44" t="n">
-        <v>7056170</v>
+        <v>7055801</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5224,7 +5224,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124808151</v>
+        <v>124808135</v>
       </c>
       <c r="B45" t="n">
         <v>57513</v>
@@ -5264,10 +5264,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>466148</v>
+        <v>466024</v>
       </c>
       <c r="R45" t="n">
-        <v>7055732</v>
+        <v>7055801</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5331,7 +5331,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124808156</v>
+        <v>124808152</v>
       </c>
       <c r="B46" t="n">
         <v>57513</v>
@@ -5371,10 +5371,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>466027</v>
+        <v>466072</v>
       </c>
       <c r="R46" t="n">
-        <v>7055757</v>
+        <v>7055589</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5438,7 +5438,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124808126</v>
+        <v>124808149</v>
       </c>
       <c r="B47" t="n">
         <v>57513</v>
@@ -5478,10 +5478,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>465931</v>
+        <v>466219</v>
       </c>
       <c r="R47" t="n">
-        <v>7055792</v>
+        <v>7055842</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5545,7 +5545,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124808127</v>
+        <v>124808137</v>
       </c>
       <c r="B48" t="n">
         <v>57513</v>
@@ -5585,10 +5585,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>465979</v>
+        <v>466097</v>
       </c>
       <c r="R48" t="n">
-        <v>7055862</v>
+        <v>7055831</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5625,7 +5625,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">

--- a/artfynd/A 11097-2024 artfynd.xlsx
+++ b/artfynd/A 11097-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124808155</v>
+        <v>124808134</v>
       </c>
       <c r="B2" t="n">
         <v>57513</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>466025</v>
+        <v>466020</v>
       </c>
       <c r="R2" t="n">
-        <v>7055769</v>
+        <v>7055801</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124808158</v>
+        <v>124808160</v>
       </c>
       <c r="B3" t="n">
         <v>57513</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465957</v>
+        <v>465939</v>
       </c>
       <c r="R3" t="n">
-        <v>7055698</v>
+        <v>7055717</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124808127</v>
+        <v>124808152</v>
       </c>
       <c r="B4" t="n">
         <v>57513</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465979</v>
+        <v>466072</v>
       </c>
       <c r="R4" t="n">
-        <v>7055862</v>
+        <v>7055589</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124808162</v>
+        <v>124808138</v>
       </c>
       <c r="B5" t="n">
         <v>57513</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465856</v>
+        <v>466123</v>
       </c>
       <c r="R5" t="n">
-        <v>7055738</v>
+        <v>7055839</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124808183</v>
+        <v>124808123</v>
       </c>
       <c r="B6" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1146,7 +1146,7 @@
         <v>465924</v>
       </c>
       <c r="R6" t="n">
-        <v>7055722</v>
+        <v>7055720</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124808139</v>
+        <v>124808185</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466126</v>
+        <v>466191</v>
       </c>
       <c r="R7" t="n">
-        <v>7055914</v>
+        <v>7055781</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,11 +1281,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,7 +1307,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124808143</v>
+        <v>124808155</v>
       </c>
       <c r="B8" t="n">
         <v>57513</v>
@@ -1352,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466291</v>
+        <v>466025</v>
       </c>
       <c r="R8" t="n">
-        <v>7056076</v>
+        <v>7055769</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1419,7 +1414,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124808154</v>
+        <v>124808156</v>
       </c>
       <c r="B9" t="n">
         <v>57513</v>
@@ -1459,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466093</v>
+        <v>466027</v>
       </c>
       <c r="R9" t="n">
-        <v>7055760</v>
+        <v>7055757</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1526,7 +1521,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124808147</v>
+        <v>124808158</v>
       </c>
       <c r="B10" t="n">
         <v>57513</v>
@@ -1566,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466151</v>
+        <v>465957</v>
       </c>
       <c r="R10" t="n">
-        <v>7055999</v>
+        <v>7055698</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1633,7 +1628,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124808194</v>
+        <v>124808190</v>
       </c>
       <c r="B11" t="n">
         <v>91030</v>
@@ -1673,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466020</v>
+        <v>466147</v>
       </c>
       <c r="R11" t="n">
-        <v>7055742</v>
+        <v>7056067</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,7 +1730,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124808132</v>
+        <v>124808136</v>
       </c>
       <c r="B12" t="n">
         <v>57513</v>
@@ -1775,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466002</v>
+        <v>466032</v>
       </c>
       <c r="R12" t="n">
-        <v>7055866</v>
+        <v>7055802</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1842,10 +1837,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124808193</v>
+        <v>124808127</v>
       </c>
       <c r="B13" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1858,21 +1853,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1882,10 +1877,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466155</v>
+        <v>465979</v>
       </c>
       <c r="R13" t="n">
-        <v>7055735</v>
+        <v>7055862</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1918,6 +1913,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1944,10 +1944,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124808195</v>
+        <v>124808132</v>
       </c>
       <c r="B14" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1960,21 +1960,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1984,10 +1984,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>466026</v>
+        <v>466002</v>
       </c>
       <c r="R14" t="n">
-        <v>7055714</v>
+        <v>7055866</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2020,6 +2020,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2046,7 +2051,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124808129</v>
+        <v>124808137</v>
       </c>
       <c r="B15" t="n">
         <v>57513</v>
@@ -2086,10 +2091,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>465997</v>
+        <v>466097</v>
       </c>
       <c r="R15" t="n">
-        <v>7055926</v>
+        <v>7055831</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2153,7 +2158,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124808145</v>
+        <v>124808154</v>
       </c>
       <c r="B16" t="n">
         <v>57513</v>
@@ -2193,10 +2198,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466217</v>
+        <v>466093</v>
       </c>
       <c r="R16" t="n">
-        <v>7056120</v>
+        <v>7055760</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2260,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124808160</v>
+        <v>124808182</v>
       </c>
       <c r="B17" t="n">
-        <v>57513</v>
+        <v>79892</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2276,21 +2281,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2300,10 +2305,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>465939</v>
+        <v>466191</v>
       </c>
       <c r="R17" t="n">
-        <v>7055717</v>
+        <v>7055781</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2336,11 +2341,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2367,10 +2367,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124808189</v>
+        <v>124808140</v>
       </c>
       <c r="B18" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2383,21 +2383,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2407,10 +2407,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466286</v>
+        <v>466113</v>
       </c>
       <c r="R18" t="n">
-        <v>7056084</v>
+        <v>7055912</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2443,6 +2443,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2469,10 +2474,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124808123</v>
+        <v>124808126</v>
       </c>
       <c r="B19" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2485,21 +2490,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2509,10 +2514,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>465924</v>
+        <v>465931</v>
       </c>
       <c r="R19" t="n">
-        <v>7055720</v>
+        <v>7055792</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2545,6 +2550,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2571,7 +2581,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124808131</v>
+        <v>124808125</v>
       </c>
       <c r="B20" t="n">
         <v>57513</v>
@@ -2605,16 +2615,24 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Åkerån, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466023</v>
+        <v>466019</v>
       </c>
       <c r="R20" t="n">
-        <v>7055886</v>
+        <v>7055741</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2651,7 +2669,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Bohål ca 6m upp i bruten gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2678,7 +2696,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124808146</v>
+        <v>124808139</v>
       </c>
       <c r="B21" t="n">
         <v>57513</v>
@@ -2718,10 +2736,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>466210</v>
+        <v>466126</v>
       </c>
       <c r="R21" t="n">
-        <v>7056130</v>
+        <v>7055914</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2758,7 +2776,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2785,7 +2803,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124808142</v>
+        <v>124808131</v>
       </c>
       <c r="B22" t="n">
         <v>57513</v>
@@ -2825,10 +2843,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>466212</v>
+        <v>466023</v>
       </c>
       <c r="R22" t="n">
-        <v>7056170</v>
+        <v>7055886</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2892,10 +2910,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124808182</v>
+        <v>124808193</v>
       </c>
       <c r="B23" t="n">
-        <v>79892</v>
+        <v>91030</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2908,21 +2926,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2932,10 +2950,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>466191</v>
+        <v>466155</v>
       </c>
       <c r="R23" t="n">
-        <v>7055781</v>
+        <v>7055735</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2994,10 +3012,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124808187</v>
+        <v>124808159</v>
       </c>
       <c r="B24" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3010,21 +3028,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3034,10 +3052,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>465961</v>
+        <v>465930</v>
       </c>
       <c r="R24" t="n">
-        <v>7055835</v>
+        <v>7055704</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3070,6 +3088,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3096,7 +3119,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124808125</v>
+        <v>124808149</v>
       </c>
       <c r="B25" t="n">
         <v>57513</v>
@@ -3130,24 +3153,16 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Åkerån, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>466019</v>
+        <v>466219</v>
       </c>
       <c r="R25" t="n">
-        <v>7055741</v>
+        <v>7055842</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3184,7 +3199,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Bohål ca 6m upp i bruten gran</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3211,7 +3226,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124808148</v>
+        <v>124808157</v>
       </c>
       <c r="B26" t="n">
         <v>57513</v>
@@ -3251,10 +3266,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466190</v>
+        <v>466023</v>
       </c>
       <c r="R26" t="n">
-        <v>7055952</v>
+        <v>7055706</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3425,7 +3440,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124808136</v>
+        <v>124808143</v>
       </c>
       <c r="B28" t="n">
         <v>57513</v>
@@ -3465,10 +3480,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466032</v>
+        <v>466291</v>
       </c>
       <c r="R28" t="n">
-        <v>7055802</v>
+        <v>7056076</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3532,7 +3547,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124808144</v>
+        <v>124808162</v>
       </c>
       <c r="B29" t="n">
         <v>57513</v>
@@ -3572,10 +3587,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466231</v>
+        <v>465856</v>
       </c>
       <c r="R29" t="n">
-        <v>7056150</v>
+        <v>7055738</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3639,10 +3654,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124808140</v>
+        <v>124808183</v>
       </c>
       <c r="B30" t="n">
-        <v>57513</v>
+        <v>91299</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3655,21 +3670,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3679,10 +3694,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>466113</v>
+        <v>465924</v>
       </c>
       <c r="R30" t="n">
-        <v>7055912</v>
+        <v>7055722</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3715,11 +3730,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3746,7 +3756,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124808141</v>
+        <v>124808135</v>
       </c>
       <c r="B31" t="n">
         <v>57513</v>
@@ -3786,10 +3796,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466172</v>
+        <v>466024</v>
       </c>
       <c r="R31" t="n">
-        <v>7056129</v>
+        <v>7055801</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3853,10 +3863,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124808133</v>
+        <v>124808195</v>
       </c>
       <c r="B32" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3869,21 +3879,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3893,10 +3903,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466022</v>
+        <v>466026</v>
       </c>
       <c r="R32" t="n">
-        <v>7055840</v>
+        <v>7055714</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3929,11 +3939,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3960,10 +3965,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124808126</v>
+        <v>124808187</v>
       </c>
       <c r="B33" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3976,21 +3981,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4000,10 +4005,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>465931</v>
+        <v>465961</v>
       </c>
       <c r="R33" t="n">
-        <v>7055792</v>
+        <v>7055835</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4036,11 +4041,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4067,7 +4067,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124808157</v>
+        <v>124808161</v>
       </c>
       <c r="B34" t="n">
         <v>57513</v>
@@ -4107,10 +4107,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>466023</v>
+        <v>465859</v>
       </c>
       <c r="R34" t="n">
-        <v>7055706</v>
+        <v>7055744</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4174,7 +4174,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124808161</v>
+        <v>124808142</v>
       </c>
       <c r="B35" t="n">
         <v>57513</v>
@@ -4214,10 +4214,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>465859</v>
+        <v>466212</v>
       </c>
       <c r="R35" t="n">
-        <v>7055744</v>
+        <v>7056170</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4281,10 +4281,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124808185</v>
+        <v>124808144</v>
       </c>
       <c r="B36" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4297,21 +4297,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4321,10 +4321,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>466191</v>
+        <v>466231</v>
       </c>
       <c r="R36" t="n">
-        <v>7055781</v>
+        <v>7056150</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4357,6 +4357,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4383,10 +4388,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124808184</v>
+        <v>124808145</v>
       </c>
       <c r="B37" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4399,21 +4404,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4423,10 +4428,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>466183</v>
+        <v>466217</v>
       </c>
       <c r="R37" t="n">
-        <v>7056145</v>
+        <v>7056120</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4459,6 +4464,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4485,7 +4495,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124808156</v>
+        <v>124808129</v>
       </c>
       <c r="B38" t="n">
         <v>57513</v>
@@ -4525,10 +4535,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>466027</v>
+        <v>465997</v>
       </c>
       <c r="R38" t="n">
-        <v>7055757</v>
+        <v>7055926</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4565,7 +4575,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4592,7 +4602,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124808150</v>
+        <v>124808133</v>
       </c>
       <c r="B39" t="n">
         <v>57513</v>
@@ -4632,10 +4642,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>466187</v>
+        <v>466022</v>
       </c>
       <c r="R39" t="n">
-        <v>7055846</v>
+        <v>7055840</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4672,7 +4682,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4699,10 +4709,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124808138</v>
+        <v>124808194</v>
       </c>
       <c r="B40" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4715,21 +4725,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4739,10 +4749,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>466123</v>
+        <v>466020</v>
       </c>
       <c r="R40" t="n">
-        <v>7055839</v>
+        <v>7055742</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4775,11 +4785,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4806,10 +4811,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124808159</v>
+        <v>124808189</v>
       </c>
       <c r="B41" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4822,21 +4827,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4846,10 +4851,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>465930</v>
+        <v>466286</v>
       </c>
       <c r="R41" t="n">
-        <v>7055704</v>
+        <v>7056084</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4882,11 +4887,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4913,10 +4913,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124808190</v>
+        <v>124808150</v>
       </c>
       <c r="B42" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4929,21 +4929,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4953,10 +4953,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>466147</v>
+        <v>466187</v>
       </c>
       <c r="R42" t="n">
-        <v>7056067</v>
+        <v>7055846</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4989,6 +4989,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5015,10 +5020,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124808188</v>
+        <v>124808147</v>
       </c>
       <c r="B43" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5031,21 +5036,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5055,10 +5060,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>466015</v>
+        <v>466151</v>
       </c>
       <c r="R43" t="n">
-        <v>7055934</v>
+        <v>7055999</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5091,6 +5096,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5117,10 +5127,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124808134</v>
+        <v>124808188</v>
       </c>
       <c r="B44" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5133,21 +5143,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5157,10 +5167,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>466020</v>
+        <v>466015</v>
       </c>
       <c r="R44" t="n">
-        <v>7055801</v>
+        <v>7055934</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5193,11 +5203,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5224,7 +5229,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124808135</v>
+        <v>124808146</v>
       </c>
       <c r="B45" t="n">
         <v>57513</v>
@@ -5264,10 +5269,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>466024</v>
+        <v>466210</v>
       </c>
       <c r="R45" t="n">
-        <v>7055801</v>
+        <v>7056130</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5331,7 +5336,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124808152</v>
+        <v>124808141</v>
       </c>
       <c r="B46" t="n">
         <v>57513</v>
@@ -5371,10 +5376,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>466072</v>
+        <v>466172</v>
       </c>
       <c r="R46" t="n">
-        <v>7055589</v>
+        <v>7056129</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5438,10 +5443,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124808149</v>
+        <v>124808184</v>
       </c>
       <c r="B47" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5454,21 +5459,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5478,10 +5483,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>466219</v>
+        <v>466183</v>
       </c>
       <c r="R47" t="n">
-        <v>7055842</v>
+        <v>7056145</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5514,11 +5519,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5545,7 +5545,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124808137</v>
+        <v>124808148</v>
       </c>
       <c r="B48" t="n">
         <v>57513</v>
@@ -5585,10 +5585,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>466097</v>
+        <v>466190</v>
       </c>
       <c r="R48" t="n">
-        <v>7055831</v>
+        <v>7055952</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5625,7 +5625,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">

--- a/artfynd/A 11097-2024 artfynd.xlsx
+++ b/artfynd/A 11097-2024 artfynd.xlsx
@@ -1414,7 +1414,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124808156</v>
+        <v>124808158</v>
       </c>
       <c r="B9" t="n">
         <v>57513</v>
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466027</v>
+        <v>465957</v>
       </c>
       <c r="R9" t="n">
-        <v>7055757</v>
+        <v>7055698</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1521,7 +1521,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124808158</v>
+        <v>124808156</v>
       </c>
       <c r="B10" t="n">
         <v>57513</v>
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>465957</v>
+        <v>466027</v>
       </c>
       <c r="R10" t="n">
-        <v>7055698</v>
+        <v>7055757</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -3654,10 +3654,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124808183</v>
+        <v>124808135</v>
       </c>
       <c r="B30" t="n">
-        <v>91299</v>
+        <v>57513</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3670,21 +3670,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3694,10 +3694,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>465924</v>
+        <v>466024</v>
       </c>
       <c r="R30" t="n">
-        <v>7055722</v>
+        <v>7055801</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3730,6 +3730,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3756,10 +3761,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124808135</v>
+        <v>124808183</v>
       </c>
       <c r="B31" t="n">
-        <v>57513</v>
+        <v>91299</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3772,21 +3777,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3796,10 +3801,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466024</v>
+        <v>465924</v>
       </c>
       <c r="R31" t="n">
-        <v>7055801</v>
+        <v>7055722</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3832,11 +3837,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4281,10 +4281,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124808144</v>
+        <v>124808194</v>
       </c>
       <c r="B36" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4297,21 +4297,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4321,10 +4321,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>466231</v>
+        <v>466020</v>
       </c>
       <c r="R36" t="n">
-        <v>7056150</v>
+        <v>7055742</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4357,11 +4357,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4388,7 +4383,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124808145</v>
+        <v>124808144</v>
       </c>
       <c r="B37" t="n">
         <v>57513</v>
@@ -4428,10 +4423,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>466217</v>
+        <v>466231</v>
       </c>
       <c r="R37" t="n">
-        <v>7056120</v>
+        <v>7056150</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4495,7 +4490,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124808129</v>
+        <v>124808145</v>
       </c>
       <c r="B38" t="n">
         <v>57513</v>
@@ -4535,10 +4530,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>465997</v>
+        <v>466217</v>
       </c>
       <c r="R38" t="n">
-        <v>7055926</v>
+        <v>7056120</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4575,7 +4570,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4602,7 +4597,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124808133</v>
+        <v>124808129</v>
       </c>
       <c r="B39" t="n">
         <v>57513</v>
@@ -4642,10 +4637,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>466022</v>
+        <v>465997</v>
       </c>
       <c r="R39" t="n">
-        <v>7055840</v>
+        <v>7055926</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4682,7 +4677,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4709,10 +4704,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124808194</v>
+        <v>124808133</v>
       </c>
       <c r="B40" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4725,21 +4720,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4749,10 +4744,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>466020</v>
+        <v>466022</v>
       </c>
       <c r="R40" t="n">
-        <v>7055742</v>
+        <v>7055840</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4785,6 +4780,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 11097-2024 artfynd.xlsx
+++ b/artfynd/A 11097-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124808134</v>
+        <v>124808136</v>
       </c>
       <c r="B2" t="n">
         <v>57513</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>466020</v>
+        <v>466032</v>
       </c>
       <c r="R2" t="n">
-        <v>7055801</v>
+        <v>7055802</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124808160</v>
+        <v>124808183</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>91299</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465939</v>
+        <v>465924</v>
       </c>
       <c r="R3" t="n">
-        <v>7055717</v>
+        <v>7055722</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124808152</v>
+        <v>124808148</v>
       </c>
       <c r="B4" t="n">
         <v>57513</v>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>466072</v>
+        <v>466190</v>
       </c>
       <c r="R4" t="n">
-        <v>7055589</v>
+        <v>7055952</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124808138</v>
+        <v>124808137</v>
       </c>
       <c r="B5" t="n">
         <v>57513</v>
@@ -1036,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>466123</v>
+        <v>466097</v>
       </c>
       <c r="R5" t="n">
-        <v>7055839</v>
+        <v>7055831</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1071,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124808123</v>
+        <v>124808189</v>
       </c>
       <c r="B6" t="n">
-        <v>91012</v>
+        <v>91030</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>465924</v>
+        <v>466286</v>
       </c>
       <c r="R6" t="n">
-        <v>7055720</v>
+        <v>7056084</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124808185</v>
+        <v>124808144</v>
       </c>
       <c r="B7" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466191</v>
+        <v>466231</v>
       </c>
       <c r="R7" t="n">
-        <v>7055781</v>
+        <v>7056150</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,6 +1276,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,7 +1307,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124808155</v>
+        <v>124808134</v>
       </c>
       <c r="B8" t="n">
         <v>57513</v>
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466025</v>
+        <v>466020</v>
       </c>
       <c r="R8" t="n">
-        <v>7055769</v>
+        <v>7055801</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1414,7 +1414,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124808158</v>
+        <v>124808139</v>
       </c>
       <c r="B9" t="n">
         <v>57513</v>
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>465957</v>
+        <v>466126</v>
       </c>
       <c r="R9" t="n">
-        <v>7055698</v>
+        <v>7055914</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,7 +1521,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124808156</v>
+        <v>124808143</v>
       </c>
       <c r="B10" t="n">
         <v>57513</v>
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466027</v>
+        <v>466291</v>
       </c>
       <c r="R10" t="n">
-        <v>7055757</v>
+        <v>7056076</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1628,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124808190</v>
+        <v>124808127</v>
       </c>
       <c r="B11" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1644,21 +1644,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466147</v>
+        <v>465979</v>
       </c>
       <c r="R11" t="n">
-        <v>7056067</v>
+        <v>7055862</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1704,6 +1704,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1730,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124808136</v>
+        <v>124808193</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1746,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1770,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466032</v>
+        <v>466155</v>
       </c>
       <c r="R12" t="n">
-        <v>7055802</v>
+        <v>7055735</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1806,11 +1811,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1837,10 +1837,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124808127</v>
+        <v>124808185</v>
       </c>
       <c r="B13" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1853,21 +1853,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1877,10 +1877,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>465979</v>
+        <v>466191</v>
       </c>
       <c r="R13" t="n">
-        <v>7055862</v>
+        <v>7055781</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1913,11 +1913,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1944,10 +1939,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124808132</v>
+        <v>124808184</v>
       </c>
       <c r="B14" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1960,21 +1955,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1984,10 +1979,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>466002</v>
+        <v>466183</v>
       </c>
       <c r="R14" t="n">
-        <v>7055866</v>
+        <v>7056145</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2020,11 +2015,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2051,10 +2041,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124808137</v>
+        <v>124808187</v>
       </c>
       <c r="B15" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2067,21 +2057,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2091,10 +2081,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>466097</v>
+        <v>465961</v>
       </c>
       <c r="R15" t="n">
-        <v>7055831</v>
+        <v>7055835</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2127,11 +2117,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2158,7 +2143,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124808154</v>
+        <v>124808140</v>
       </c>
       <c r="B16" t="n">
         <v>57513</v>
@@ -2198,10 +2183,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466093</v>
+        <v>466113</v>
       </c>
       <c r="R16" t="n">
-        <v>7055760</v>
+        <v>7055912</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2265,10 +2250,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124808182</v>
+        <v>124808160</v>
       </c>
       <c r="B17" t="n">
-        <v>79892</v>
+        <v>57513</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2281,21 +2266,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2305,10 +2290,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466191</v>
+        <v>465939</v>
       </c>
       <c r="R17" t="n">
-        <v>7055781</v>
+        <v>7055717</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2341,6 +2326,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2367,10 +2357,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124808140</v>
+        <v>124808188</v>
       </c>
       <c r="B18" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2383,21 +2373,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2407,10 +2397,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466113</v>
+        <v>466015</v>
       </c>
       <c r="R18" t="n">
-        <v>7055912</v>
+        <v>7055934</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2443,11 +2433,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2474,7 +2459,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124808126</v>
+        <v>124808156</v>
       </c>
       <c r="B19" t="n">
         <v>57513</v>
@@ -2514,10 +2499,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>465931</v>
+        <v>466027</v>
       </c>
       <c r="R19" t="n">
-        <v>7055792</v>
+        <v>7055757</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2581,7 +2566,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124808125</v>
+        <v>124808154</v>
       </c>
       <c r="B20" t="n">
         <v>57513</v>
@@ -2615,24 +2600,16 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Åkerån, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466019</v>
+        <v>466093</v>
       </c>
       <c r="R20" t="n">
-        <v>7055741</v>
+        <v>7055760</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2669,7 +2646,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Bohål ca 6m upp i bruten gran</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2696,7 +2673,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124808139</v>
+        <v>124808152</v>
       </c>
       <c r="B21" t="n">
         <v>57513</v>
@@ -2736,10 +2713,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>466126</v>
+        <v>466072</v>
       </c>
       <c r="R21" t="n">
-        <v>7055914</v>
+        <v>7055589</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2776,7 +2753,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2803,10 +2780,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124808131</v>
+        <v>124808190</v>
       </c>
       <c r="B22" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2819,21 +2796,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2843,10 +2820,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>466023</v>
+        <v>466147</v>
       </c>
       <c r="R22" t="n">
-        <v>7055886</v>
+        <v>7056067</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2879,11 +2856,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2910,10 +2882,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124808193</v>
+        <v>124808149</v>
       </c>
       <c r="B23" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2926,21 +2898,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2950,10 +2922,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>466155</v>
+        <v>466219</v>
       </c>
       <c r="R23" t="n">
-        <v>7055735</v>
+        <v>7055842</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2986,6 +2958,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3012,7 +2989,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124808159</v>
+        <v>124808155</v>
       </c>
       <c r="B24" t="n">
         <v>57513</v>
@@ -3052,10 +3029,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>465930</v>
+        <v>466025</v>
       </c>
       <c r="R24" t="n">
-        <v>7055704</v>
+        <v>7055769</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3092,7 +3069,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3119,7 +3096,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124808149</v>
+        <v>124808132</v>
       </c>
       <c r="B25" t="n">
         <v>57513</v>
@@ -3159,10 +3136,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>466219</v>
+        <v>466002</v>
       </c>
       <c r="R25" t="n">
-        <v>7055842</v>
+        <v>7055866</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3199,7 +3176,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3226,10 +3203,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124808157</v>
+        <v>124808194</v>
       </c>
       <c r="B26" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3242,21 +3219,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3266,10 +3243,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466023</v>
+        <v>466020</v>
       </c>
       <c r="R26" t="n">
-        <v>7055706</v>
+        <v>7055742</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3302,11 +3279,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3333,7 +3305,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124808151</v>
+        <v>124808131</v>
       </c>
       <c r="B27" t="n">
         <v>57513</v>
@@ -3373,10 +3345,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466148</v>
+        <v>466023</v>
       </c>
       <c r="R27" t="n">
-        <v>7055732</v>
+        <v>7055886</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3440,7 +3412,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124808143</v>
+        <v>124808146</v>
       </c>
       <c r="B28" t="n">
         <v>57513</v>
@@ -3480,10 +3452,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466291</v>
+        <v>466210</v>
       </c>
       <c r="R28" t="n">
-        <v>7056076</v>
+        <v>7056130</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3547,10 +3519,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124808162</v>
+        <v>124808195</v>
       </c>
       <c r="B29" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3563,21 +3535,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3587,10 +3559,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>465856</v>
+        <v>466026</v>
       </c>
       <c r="R29" t="n">
-        <v>7055738</v>
+        <v>7055714</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3623,11 +3595,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3654,7 +3621,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124808135</v>
+        <v>124808141</v>
       </c>
       <c r="B30" t="n">
         <v>57513</v>
@@ -3694,10 +3661,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>466024</v>
+        <v>466172</v>
       </c>
       <c r="R30" t="n">
-        <v>7055801</v>
+        <v>7056129</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3761,10 +3728,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124808183</v>
+        <v>124808150</v>
       </c>
       <c r="B31" t="n">
-        <v>91299</v>
+        <v>57513</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3777,21 +3744,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3801,10 +3768,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>465924</v>
+        <v>466187</v>
       </c>
       <c r="R31" t="n">
-        <v>7055722</v>
+        <v>7055846</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3837,6 +3804,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3863,10 +3835,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124808195</v>
+        <v>124808123</v>
       </c>
       <c r="B32" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3879,21 +3851,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3903,10 +3875,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466026</v>
+        <v>465924</v>
       </c>
       <c r="R32" t="n">
-        <v>7055714</v>
+        <v>7055720</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3965,10 +3937,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124808187</v>
+        <v>124808161</v>
       </c>
       <c r="B33" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3981,21 +3953,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4005,10 +3977,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>465961</v>
+        <v>465859</v>
       </c>
       <c r="R33" t="n">
-        <v>7055835</v>
+        <v>7055744</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4041,6 +4013,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4067,7 +4044,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124808161</v>
+        <v>124808126</v>
       </c>
       <c r="B34" t="n">
         <v>57513</v>
@@ -4107,10 +4084,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>465859</v>
+        <v>465931</v>
       </c>
       <c r="R34" t="n">
-        <v>7055744</v>
+        <v>7055792</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4174,7 +4151,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124808142</v>
+        <v>124808138</v>
       </c>
       <c r="B35" t="n">
         <v>57513</v>
@@ -4214,10 +4191,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>466212</v>
+        <v>466123</v>
       </c>
       <c r="R35" t="n">
-        <v>7056170</v>
+        <v>7055839</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4281,10 +4258,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124808194</v>
+        <v>124808129</v>
       </c>
       <c r="B36" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4297,21 +4274,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4321,10 +4298,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>466020</v>
+        <v>465997</v>
       </c>
       <c r="R36" t="n">
-        <v>7055742</v>
+        <v>7055926</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4357,6 +4334,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4383,7 +4365,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124808144</v>
+        <v>124808142</v>
       </c>
       <c r="B37" t="n">
         <v>57513</v>
@@ -4423,10 +4405,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>466231</v>
+        <v>466212</v>
       </c>
       <c r="R37" t="n">
-        <v>7056150</v>
+        <v>7056170</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4490,7 +4472,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124808145</v>
+        <v>124808125</v>
       </c>
       <c r="B38" t="n">
         <v>57513</v>
@@ -4524,16 +4506,24 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Åkerån, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>466217</v>
+        <v>466019</v>
       </c>
       <c r="R38" t="n">
-        <v>7056120</v>
+        <v>7055741</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4570,7 +4560,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Bohål ca 6m upp i bruten gran</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4597,7 +4587,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124808129</v>
+        <v>124808162</v>
       </c>
       <c r="B39" t="n">
         <v>57513</v>
@@ -4637,10 +4627,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>465997</v>
+        <v>465856</v>
       </c>
       <c r="R39" t="n">
-        <v>7055926</v>
+        <v>7055738</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4677,7 +4667,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4704,7 +4694,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124808133</v>
+        <v>124808159</v>
       </c>
       <c r="B40" t="n">
         <v>57513</v>
@@ -4744,10 +4734,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>466022</v>
+        <v>465930</v>
       </c>
       <c r="R40" t="n">
-        <v>7055840</v>
+        <v>7055704</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4784,7 +4774,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4811,10 +4801,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124808189</v>
+        <v>124808133</v>
       </c>
       <c r="B41" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4827,21 +4817,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4851,10 +4841,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>466286</v>
+        <v>466022</v>
       </c>
       <c r="R41" t="n">
-        <v>7056084</v>
+        <v>7055840</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4887,6 +4877,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4913,7 +4908,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124808150</v>
+        <v>124808157</v>
       </c>
       <c r="B42" t="n">
         <v>57513</v>
@@ -4953,10 +4948,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>466187</v>
+        <v>466023</v>
       </c>
       <c r="R42" t="n">
-        <v>7055846</v>
+        <v>7055706</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4993,7 +4988,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5020,10 +5015,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124808147</v>
+        <v>124808182</v>
       </c>
       <c r="B43" t="n">
-        <v>57513</v>
+        <v>79892</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5036,21 +5031,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5060,10 +5055,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>466151</v>
+        <v>466191</v>
       </c>
       <c r="R43" t="n">
-        <v>7055999</v>
+        <v>7055781</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5096,11 +5091,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5127,10 +5117,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124808188</v>
+        <v>124808135</v>
       </c>
       <c r="B44" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5143,21 +5133,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5167,10 +5157,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>466015</v>
+        <v>466024</v>
       </c>
       <c r="R44" t="n">
-        <v>7055934</v>
+        <v>7055801</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5203,6 +5193,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5229,7 +5224,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124808146</v>
+        <v>124808147</v>
       </c>
       <c r="B45" t="n">
         <v>57513</v>
@@ -5269,10 +5264,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>466210</v>
+        <v>466151</v>
       </c>
       <c r="R45" t="n">
-        <v>7056130</v>
+        <v>7055999</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5336,7 +5331,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124808141</v>
+        <v>124808151</v>
       </c>
       <c r="B46" t="n">
         <v>57513</v>
@@ -5376,10 +5371,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>466172</v>
+        <v>466148</v>
       </c>
       <c r="R46" t="n">
-        <v>7056129</v>
+        <v>7055732</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5443,10 +5438,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124808184</v>
+        <v>124808158</v>
       </c>
       <c r="B47" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5459,21 +5454,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5483,10 +5478,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>466183</v>
+        <v>465957</v>
       </c>
       <c r="R47" t="n">
-        <v>7056145</v>
+        <v>7055698</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5519,6 +5514,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5545,7 +5545,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124808148</v>
+        <v>124808145</v>
       </c>
       <c r="B48" t="n">
         <v>57513</v>
@@ -5585,10 +5585,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>466190</v>
+        <v>466217</v>
       </c>
       <c r="R48" t="n">
-        <v>7055952</v>
+        <v>7056120</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>

--- a/artfynd/A 11097-2024 artfynd.xlsx
+++ b/artfynd/A 11097-2024 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124808183</v>
+        <v>124808148</v>
       </c>
       <c r="B3" t="n">
-        <v>91299</v>
+        <v>57513</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465924</v>
+        <v>466190</v>
       </c>
       <c r="R3" t="n">
-        <v>7055722</v>
+        <v>7055952</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,6 +858,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124808148</v>
+        <v>124808137</v>
       </c>
       <c r="B4" t="n">
         <v>57513</v>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>466190</v>
+        <v>466097</v>
       </c>
       <c r="R4" t="n">
-        <v>7055952</v>
+        <v>7055831</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124808137</v>
+        <v>124808183</v>
       </c>
       <c r="B5" t="n">
-        <v>57513</v>
+        <v>91299</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>466097</v>
+        <v>465924</v>
       </c>
       <c r="R5" t="n">
-        <v>7055831</v>
+        <v>7055722</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,11 +1072,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1200,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124808144</v>
+        <v>124808193</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1216,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466231</v>
+        <v>466155</v>
       </c>
       <c r="R7" t="n">
-        <v>7056150</v>
+        <v>7055735</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1276,11 +1276,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124808134</v>
+        <v>124808185</v>
       </c>
       <c r="B8" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,21 +1318,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1347,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466020</v>
+        <v>466191</v>
       </c>
       <c r="R8" t="n">
-        <v>7055801</v>
+        <v>7055781</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1383,11 +1378,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1414,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124808139</v>
+        <v>124808184</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1430,21 +1420,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1454,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466126</v>
+        <v>466183</v>
       </c>
       <c r="R9" t="n">
-        <v>7055914</v>
+        <v>7056145</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1490,11 +1480,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,7 +1506,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124808143</v>
+        <v>124808144</v>
       </c>
       <c r="B10" t="n">
         <v>57513</v>
@@ -1561,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466291</v>
+        <v>466231</v>
       </c>
       <c r="R10" t="n">
-        <v>7056076</v>
+        <v>7056150</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1628,7 +1613,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124808127</v>
+        <v>124808134</v>
       </c>
       <c r="B11" t="n">
         <v>57513</v>
@@ -1668,10 +1653,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>465979</v>
+        <v>466020</v>
       </c>
       <c r="R11" t="n">
-        <v>7055862</v>
+        <v>7055801</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,10 +1720,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124808193</v>
+        <v>124808139</v>
       </c>
       <c r="B12" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,21 +1736,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1760,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466155</v>
+        <v>466126</v>
       </c>
       <c r="R12" t="n">
-        <v>7055735</v>
+        <v>7055914</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1811,6 +1796,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1837,10 +1827,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124808185</v>
+        <v>124808143</v>
       </c>
       <c r="B13" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1853,21 +1843,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1877,10 +1867,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466191</v>
+        <v>466291</v>
       </c>
       <c r="R13" t="n">
-        <v>7055781</v>
+        <v>7056076</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1913,6 +1903,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1939,10 +1934,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124808184</v>
+        <v>124808127</v>
       </c>
       <c r="B14" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1955,21 +1950,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1979,10 +1974,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>466183</v>
+        <v>465979</v>
       </c>
       <c r="R14" t="n">
-        <v>7056145</v>
+        <v>7055862</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2015,6 +2010,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2041,10 +2041,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124808187</v>
+        <v>124808140</v>
       </c>
       <c r="B15" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2057,21 +2057,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>465961</v>
+        <v>466113</v>
       </c>
       <c r="R15" t="n">
-        <v>7055835</v>
+        <v>7055912</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2117,6 +2117,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2143,7 +2148,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124808140</v>
+        <v>124808160</v>
       </c>
       <c r="B16" t="n">
         <v>57513</v>
@@ -2183,10 +2188,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466113</v>
+        <v>465939</v>
       </c>
       <c r="R16" t="n">
-        <v>7055912</v>
+        <v>7055717</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2250,10 +2255,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124808160</v>
+        <v>124808187</v>
       </c>
       <c r="B17" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2266,21 +2271,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2290,10 +2295,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>465939</v>
+        <v>465961</v>
       </c>
       <c r="R17" t="n">
-        <v>7055717</v>
+        <v>7055835</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2326,11 +2331,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -3835,10 +3835,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124808123</v>
+        <v>124808161</v>
       </c>
       <c r="B32" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3851,21 +3851,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3875,10 +3875,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>465924</v>
+        <v>465859</v>
       </c>
       <c r="R32" t="n">
-        <v>7055720</v>
+        <v>7055744</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3911,6 +3911,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3937,7 +3942,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124808161</v>
+        <v>124808126</v>
       </c>
       <c r="B33" t="n">
         <v>57513</v>
@@ -3977,10 +3982,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>465859</v>
+        <v>465931</v>
       </c>
       <c r="R33" t="n">
-        <v>7055744</v>
+        <v>7055792</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4044,10 +4049,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124808126</v>
+        <v>124808123</v>
       </c>
       <c r="B34" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4060,21 +4065,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4084,10 +4089,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>465931</v>
+        <v>465924</v>
       </c>
       <c r="R34" t="n">
-        <v>7055792</v>
+        <v>7055720</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4120,11 +4125,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 11097-2024 artfynd.xlsx
+++ b/artfynd/A 11097-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124808136</v>
+        <v>124808188</v>
       </c>
       <c r="B2" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>466032</v>
+        <v>466015</v>
       </c>
       <c r="R2" t="n">
-        <v>7055802</v>
+        <v>7055934</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124808148</v>
+        <v>124808194</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466190</v>
+        <v>466020</v>
       </c>
       <c r="R3" t="n">
-        <v>7055952</v>
+        <v>7055742</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124808137</v>
+        <v>124808123</v>
       </c>
       <c r="B4" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>466097</v>
+        <v>465924</v>
       </c>
       <c r="R4" t="n">
-        <v>7055831</v>
+        <v>7055720</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,11 +955,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124808183</v>
+        <v>124808155</v>
       </c>
       <c r="B5" t="n">
-        <v>91299</v>
+        <v>57513</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465924</v>
+        <v>466025</v>
       </c>
       <c r="R5" t="n">
-        <v>7055722</v>
+        <v>7055769</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,6 +1057,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124808189</v>
+        <v>124808127</v>
       </c>
       <c r="B6" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466286</v>
+        <v>465979</v>
       </c>
       <c r="R6" t="n">
-        <v>7056084</v>
+        <v>7055862</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1174,6 +1164,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124808193</v>
+        <v>124808133</v>
       </c>
       <c r="B7" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1216,21 +1211,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466155</v>
+        <v>466022</v>
       </c>
       <c r="R7" t="n">
-        <v>7055735</v>
+        <v>7055840</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1276,6 +1271,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1302,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124808185</v>
+        <v>124808126</v>
       </c>
       <c r="B8" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1318,21 +1318,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466191</v>
+        <v>465931</v>
       </c>
       <c r="R8" t="n">
-        <v>7055781</v>
+        <v>7055792</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1378,6 +1378,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1404,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124808184</v>
+        <v>124808147</v>
       </c>
       <c r="B9" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1420,21 +1425,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1444,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466183</v>
+        <v>466151</v>
       </c>
       <c r="R9" t="n">
-        <v>7056145</v>
+        <v>7055999</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1480,6 +1485,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1506,10 +1516,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124808144</v>
+        <v>124808183</v>
       </c>
       <c r="B10" t="n">
-        <v>57513</v>
+        <v>91299</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1522,21 +1532,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1546,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466231</v>
+        <v>465924</v>
       </c>
       <c r="R10" t="n">
-        <v>7056150</v>
+        <v>7055722</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1582,11 +1592,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1613,7 +1618,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124808134</v>
+        <v>124808141</v>
       </c>
       <c r="B11" t="n">
         <v>57513</v>
@@ -1653,10 +1658,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466020</v>
+        <v>466172</v>
       </c>
       <c r="R11" t="n">
-        <v>7055801</v>
+        <v>7056129</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1720,7 +1725,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124808139</v>
+        <v>124808145</v>
       </c>
       <c r="B12" t="n">
         <v>57513</v>
@@ -1760,10 +1765,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466126</v>
+        <v>466217</v>
       </c>
       <c r="R12" t="n">
-        <v>7055914</v>
+        <v>7056120</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1800,7 +1805,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1827,7 +1832,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124808143</v>
+        <v>124808134</v>
       </c>
       <c r="B13" t="n">
         <v>57513</v>
@@ -1867,10 +1872,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466291</v>
+        <v>466020</v>
       </c>
       <c r="R13" t="n">
-        <v>7056076</v>
+        <v>7055801</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1934,7 +1939,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124808127</v>
+        <v>124808137</v>
       </c>
       <c r="B14" t="n">
         <v>57513</v>
@@ -1974,10 +1979,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>465979</v>
+        <v>466097</v>
       </c>
       <c r="R14" t="n">
-        <v>7055862</v>
+        <v>7055831</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2014,7 +2019,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2041,10 +2046,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124808140</v>
+        <v>124808189</v>
       </c>
       <c r="B15" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2057,21 +2062,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2081,10 +2086,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>466113</v>
+        <v>466286</v>
       </c>
       <c r="R15" t="n">
-        <v>7055912</v>
+        <v>7056084</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2117,11 +2122,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2148,7 +2148,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124808160</v>
+        <v>124808154</v>
       </c>
       <c r="B16" t="n">
         <v>57513</v>
@@ -2188,10 +2188,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>465939</v>
+        <v>466093</v>
       </c>
       <c r="R16" t="n">
-        <v>7055717</v>
+        <v>7055760</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2255,10 +2255,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124808187</v>
+        <v>124808138</v>
       </c>
       <c r="B17" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2271,21 +2271,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2295,10 +2295,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>465961</v>
+        <v>466123</v>
       </c>
       <c r="R17" t="n">
-        <v>7055835</v>
+        <v>7055839</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2331,6 +2331,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2357,7 +2362,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124808188</v>
+        <v>124808195</v>
       </c>
       <c r="B18" t="n">
         <v>91030</v>
@@ -2397,10 +2402,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466015</v>
+        <v>466026</v>
       </c>
       <c r="R18" t="n">
-        <v>7055934</v>
+        <v>7055714</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2459,7 +2464,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124808156</v>
+        <v>124808148</v>
       </c>
       <c r="B19" t="n">
         <v>57513</v>
@@ -2499,10 +2504,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466027</v>
+        <v>466190</v>
       </c>
       <c r="R19" t="n">
-        <v>7055757</v>
+        <v>7055952</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2566,7 +2571,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124808154</v>
+        <v>124808136</v>
       </c>
       <c r="B20" t="n">
         <v>57513</v>
@@ -2606,10 +2611,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466093</v>
+        <v>466032</v>
       </c>
       <c r="R20" t="n">
-        <v>7055760</v>
+        <v>7055802</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2673,7 +2678,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124808152</v>
+        <v>124808135</v>
       </c>
       <c r="B21" t="n">
         <v>57513</v>
@@ -2713,10 +2718,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>466072</v>
+        <v>466024</v>
       </c>
       <c r="R21" t="n">
-        <v>7055589</v>
+        <v>7055801</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2780,10 +2785,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124808190</v>
+        <v>124808142</v>
       </c>
       <c r="B22" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2796,21 +2801,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2820,10 +2825,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>466147</v>
+        <v>466212</v>
       </c>
       <c r="R22" t="n">
-        <v>7056067</v>
+        <v>7056170</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2856,6 +2861,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2882,7 +2892,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124808149</v>
+        <v>124808143</v>
       </c>
       <c r="B23" t="n">
         <v>57513</v>
@@ -2922,10 +2932,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>466219</v>
+        <v>466291</v>
       </c>
       <c r="R23" t="n">
-        <v>7055842</v>
+        <v>7056076</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2962,7 +2972,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2989,7 +2999,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124808155</v>
+        <v>124808159</v>
       </c>
       <c r="B24" t="n">
         <v>57513</v>
@@ -3029,10 +3039,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>466025</v>
+        <v>465930</v>
       </c>
       <c r="R24" t="n">
-        <v>7055769</v>
+        <v>7055704</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3069,7 +3079,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3096,10 +3106,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124808132</v>
+        <v>124808193</v>
       </c>
       <c r="B25" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3112,21 +3122,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3136,10 +3146,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>466002</v>
+        <v>466155</v>
       </c>
       <c r="R25" t="n">
-        <v>7055866</v>
+        <v>7055735</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3172,11 +3182,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3203,10 +3208,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124808194</v>
+        <v>124808125</v>
       </c>
       <c r="B26" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3219,34 +3224,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Åkerån, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466020</v>
+        <v>466019</v>
       </c>
       <c r="R26" t="n">
-        <v>7055742</v>
+        <v>7055741</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3279,6 +3292,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Bohål ca 6m upp i bruten gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3305,10 +3323,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124808131</v>
+        <v>124808182</v>
       </c>
       <c r="B27" t="n">
-        <v>57513</v>
+        <v>79892</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3321,21 +3339,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3345,10 +3363,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466023</v>
+        <v>466191</v>
       </c>
       <c r="R27" t="n">
-        <v>7055886</v>
+        <v>7055781</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3381,11 +3399,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3412,7 +3425,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124808146</v>
+        <v>124808139</v>
       </c>
       <c r="B28" t="n">
         <v>57513</v>
@@ -3452,10 +3465,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466210</v>
+        <v>466126</v>
       </c>
       <c r="R28" t="n">
-        <v>7056130</v>
+        <v>7055914</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3492,7 +3505,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3519,10 +3532,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124808195</v>
+        <v>124808146</v>
       </c>
       <c r="B29" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3535,21 +3548,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3559,10 +3572,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466026</v>
+        <v>466210</v>
       </c>
       <c r="R29" t="n">
-        <v>7055714</v>
+        <v>7056130</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3595,6 +3608,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3621,7 +3639,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124808141</v>
+        <v>124808162</v>
       </c>
       <c r="B30" t="n">
         <v>57513</v>
@@ -3661,10 +3679,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>466172</v>
+        <v>465856</v>
       </c>
       <c r="R30" t="n">
-        <v>7056129</v>
+        <v>7055738</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3728,7 +3746,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124808150</v>
+        <v>124808157</v>
       </c>
       <c r="B31" t="n">
         <v>57513</v>
@@ -3768,10 +3786,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466187</v>
+        <v>466023</v>
       </c>
       <c r="R31" t="n">
-        <v>7055846</v>
+        <v>7055706</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3808,7 +3826,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3835,7 +3853,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124808161</v>
+        <v>124808158</v>
       </c>
       <c r="B32" t="n">
         <v>57513</v>
@@ -3875,10 +3893,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>465859</v>
+        <v>465957</v>
       </c>
       <c r="R32" t="n">
-        <v>7055744</v>
+        <v>7055698</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3942,7 +3960,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124808126</v>
+        <v>124808140</v>
       </c>
       <c r="B33" t="n">
         <v>57513</v>
@@ -3982,10 +4000,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>465931</v>
+        <v>466113</v>
       </c>
       <c r="R33" t="n">
-        <v>7055792</v>
+        <v>7055912</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4049,10 +4067,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124808123</v>
+        <v>124808185</v>
       </c>
       <c r="B34" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4065,21 +4083,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4089,10 +4107,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>465924</v>
+        <v>466191</v>
       </c>
       <c r="R34" t="n">
-        <v>7055720</v>
+        <v>7055781</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4151,7 +4169,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124808138</v>
+        <v>124808156</v>
       </c>
       <c r="B35" t="n">
         <v>57513</v>
@@ -4191,10 +4209,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>466123</v>
+        <v>466027</v>
       </c>
       <c r="R35" t="n">
-        <v>7055839</v>
+        <v>7055757</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4258,7 +4276,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124808129</v>
+        <v>124808151</v>
       </c>
       <c r="B36" t="n">
         <v>57513</v>
@@ -4298,10 +4316,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>465997</v>
+        <v>466148</v>
       </c>
       <c r="R36" t="n">
-        <v>7055926</v>
+        <v>7055732</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4338,7 +4356,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4365,7 +4383,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124808142</v>
+        <v>124808131</v>
       </c>
       <c r="B37" t="n">
         <v>57513</v>
@@ -4405,10 +4423,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>466212</v>
+        <v>466023</v>
       </c>
       <c r="R37" t="n">
-        <v>7056170</v>
+        <v>7055886</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4472,7 +4490,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124808125</v>
+        <v>124808144</v>
       </c>
       <c r="B38" t="n">
         <v>57513</v>
@@ -4506,24 +4524,16 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Åkerån, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>466019</v>
+        <v>466231</v>
       </c>
       <c r="R38" t="n">
-        <v>7055741</v>
+        <v>7056150</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4560,7 +4570,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Bohål ca 6m upp i bruten gran</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4587,7 +4597,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124808162</v>
+        <v>124808160</v>
       </c>
       <c r="B39" t="n">
         <v>57513</v>
@@ -4627,10 +4637,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>465856</v>
+        <v>465939</v>
       </c>
       <c r="R39" t="n">
-        <v>7055738</v>
+        <v>7055717</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4694,7 +4704,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124808159</v>
+        <v>124808152</v>
       </c>
       <c r="B40" t="n">
         <v>57513</v>
@@ -4734,10 +4744,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>465930</v>
+        <v>466072</v>
       </c>
       <c r="R40" t="n">
-        <v>7055704</v>
+        <v>7055589</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4774,7 +4784,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4801,10 +4811,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124808133</v>
+        <v>124808184</v>
       </c>
       <c r="B41" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4817,21 +4827,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4841,10 +4851,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>466022</v>
+        <v>466183</v>
       </c>
       <c r="R41" t="n">
-        <v>7055840</v>
+        <v>7056145</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4877,11 +4887,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4908,7 +4913,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124808157</v>
+        <v>124808129</v>
       </c>
       <c r="B42" t="n">
         <v>57513</v>
@@ -4948,10 +4953,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>466023</v>
+        <v>465997</v>
       </c>
       <c r="R42" t="n">
-        <v>7055706</v>
+        <v>7055926</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4988,7 +4993,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5015,10 +5020,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124808182</v>
+        <v>124808161</v>
       </c>
       <c r="B43" t="n">
-        <v>79892</v>
+        <v>57513</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5031,21 +5036,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5055,10 +5060,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>466191</v>
+        <v>465859</v>
       </c>
       <c r="R43" t="n">
-        <v>7055781</v>
+        <v>7055744</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5091,6 +5096,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5117,10 +5127,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124808135</v>
+        <v>124808190</v>
       </c>
       <c r="B44" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5133,21 +5143,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5157,10 +5167,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>466024</v>
+        <v>466147</v>
       </c>
       <c r="R44" t="n">
-        <v>7055801</v>
+        <v>7056067</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5193,11 +5203,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5224,10 +5229,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124808147</v>
+        <v>124808187</v>
       </c>
       <c r="B45" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5240,21 +5245,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5264,10 +5269,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>466151</v>
+        <v>465961</v>
       </c>
       <c r="R45" t="n">
-        <v>7055999</v>
+        <v>7055835</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5300,11 +5305,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5331,7 +5331,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124808151</v>
+        <v>124808149</v>
       </c>
       <c r="B46" t="n">
         <v>57513</v>
@@ -5371,10 +5371,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>466148</v>
+        <v>466219</v>
       </c>
       <c r="R46" t="n">
-        <v>7055732</v>
+        <v>7055842</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5438,7 +5438,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124808158</v>
+        <v>124808132</v>
       </c>
       <c r="B47" t="n">
         <v>57513</v>
@@ -5478,10 +5478,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>465957</v>
+        <v>466002</v>
       </c>
       <c r="R47" t="n">
-        <v>7055698</v>
+        <v>7055866</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5545,7 +5545,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124808145</v>
+        <v>124808150</v>
       </c>
       <c r="B48" t="n">
         <v>57513</v>
@@ -5585,10 +5585,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>466217</v>
+        <v>466187</v>
       </c>
       <c r="R48" t="n">
-        <v>7056120</v>
+        <v>7055846</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5625,7 +5625,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">

--- a/artfynd/A 11097-2024 artfynd.xlsx
+++ b/artfynd/A 11097-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124808188</v>
+        <v>124808154</v>
       </c>
       <c r="B2" t="n">
-        <v>91030</v>
+        <v>57635</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>466015</v>
+        <v>466093</v>
       </c>
       <c r="R2" t="n">
-        <v>7055934</v>
+        <v>7055760</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124808194</v>
+        <v>124808193</v>
       </c>
       <c r="B3" t="n">
-        <v>91030</v>
+        <v>91184</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466020</v>
+        <v>466155</v>
       </c>
       <c r="R3" t="n">
-        <v>7055742</v>
+        <v>7055735</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124808123</v>
+        <v>124808126</v>
       </c>
       <c r="B4" t="n">
-        <v>91012</v>
+        <v>57635</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465924</v>
+        <v>465931</v>
       </c>
       <c r="R4" t="n">
-        <v>7055720</v>
+        <v>7055792</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,6 +960,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124808155</v>
+        <v>124808185</v>
       </c>
       <c r="B5" t="n">
-        <v>57513</v>
+        <v>80028</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>466025</v>
+        <v>466191</v>
       </c>
       <c r="R5" t="n">
-        <v>7055769</v>
+        <v>7055781</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1057,11 +1067,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124808127</v>
+        <v>124808138</v>
       </c>
       <c r="B6" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1128,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>465979</v>
+        <v>466123</v>
       </c>
       <c r="R6" t="n">
-        <v>7055862</v>
+        <v>7055839</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124808133</v>
+        <v>124808140</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1235,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466022</v>
+        <v>466113</v>
       </c>
       <c r="R7" t="n">
-        <v>7055840</v>
+        <v>7055912</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1302,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124808126</v>
+        <v>124808139</v>
       </c>
       <c r="B8" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1342,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>465931</v>
+        <v>466126</v>
       </c>
       <c r="R8" t="n">
-        <v>7055792</v>
+        <v>7055914</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1382,7 +1387,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1409,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124808147</v>
+        <v>124808162</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1449,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466151</v>
+        <v>465856</v>
       </c>
       <c r="R9" t="n">
-        <v>7055999</v>
+        <v>7055738</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1516,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124808183</v>
+        <v>124808150</v>
       </c>
       <c r="B10" t="n">
-        <v>91299</v>
+        <v>57635</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1532,21 +1537,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1556,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>465924</v>
+        <v>466187</v>
       </c>
       <c r="R10" t="n">
-        <v>7055722</v>
+        <v>7055846</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1592,6 +1597,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1618,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124808141</v>
+        <v>124808148</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1658,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466172</v>
+        <v>466190</v>
       </c>
       <c r="R11" t="n">
-        <v>7056129</v>
+        <v>7055952</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1725,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124808145</v>
+        <v>124808158</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1765,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466217</v>
+        <v>465957</v>
       </c>
       <c r="R12" t="n">
-        <v>7056120</v>
+        <v>7055698</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1832,10 +1842,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124808134</v>
+        <v>124808143</v>
       </c>
       <c r="B13" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1872,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466020</v>
+        <v>466291</v>
       </c>
       <c r="R13" t="n">
-        <v>7055801</v>
+        <v>7056076</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1939,10 +1949,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124808137</v>
+        <v>124808159</v>
       </c>
       <c r="B14" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1979,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>466097</v>
+        <v>465930</v>
       </c>
       <c r="R14" t="n">
-        <v>7055831</v>
+        <v>7055704</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2046,10 +2056,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124808189</v>
+        <v>124808160</v>
       </c>
       <c r="B15" t="n">
-        <v>91030</v>
+        <v>57635</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2062,21 +2072,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2086,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>466286</v>
+        <v>465939</v>
       </c>
       <c r="R15" t="n">
-        <v>7056084</v>
+        <v>7055717</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2122,6 +2132,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2148,10 +2163,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124808154</v>
+        <v>124808155</v>
       </c>
       <c r="B16" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2188,10 +2203,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466093</v>
+        <v>466025</v>
       </c>
       <c r="R16" t="n">
-        <v>7055760</v>
+        <v>7055769</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2255,10 +2270,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124808138</v>
+        <v>124808152</v>
       </c>
       <c r="B17" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2295,10 +2310,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466123</v>
+        <v>466072</v>
       </c>
       <c r="R17" t="n">
-        <v>7055839</v>
+        <v>7055589</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2362,10 +2377,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124808195</v>
+        <v>124808146</v>
       </c>
       <c r="B18" t="n">
-        <v>91030</v>
+        <v>57635</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2378,21 +2393,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2402,10 +2417,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466026</v>
+        <v>466210</v>
       </c>
       <c r="R18" t="n">
-        <v>7055714</v>
+        <v>7056130</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2438,6 +2453,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2464,10 +2484,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124808148</v>
+        <v>124808127</v>
       </c>
       <c r="B19" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2504,10 +2524,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466190</v>
+        <v>465979</v>
       </c>
       <c r="R19" t="n">
-        <v>7055952</v>
+        <v>7055862</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2571,10 +2591,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124808136</v>
+        <v>124808135</v>
       </c>
       <c r="B20" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2611,10 +2631,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466032</v>
+        <v>466024</v>
       </c>
       <c r="R20" t="n">
-        <v>7055802</v>
+        <v>7055801</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2678,10 +2698,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124808135</v>
+        <v>124808147</v>
       </c>
       <c r="B21" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2718,10 +2738,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>466024</v>
+        <v>466151</v>
       </c>
       <c r="R21" t="n">
-        <v>7055801</v>
+        <v>7055999</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2785,10 +2805,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124808142</v>
+        <v>124808194</v>
       </c>
       <c r="B22" t="n">
-        <v>57513</v>
+        <v>91184</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2801,21 +2821,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2825,10 +2845,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>466212</v>
+        <v>466020</v>
       </c>
       <c r="R22" t="n">
-        <v>7056170</v>
+        <v>7055742</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2861,11 +2881,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2892,10 +2907,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124808143</v>
+        <v>124808141</v>
       </c>
       <c r="B23" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2932,10 +2947,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>466291</v>
+        <v>466172</v>
       </c>
       <c r="R23" t="n">
-        <v>7056076</v>
+        <v>7056129</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2999,10 +3014,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124808159</v>
+        <v>124808189</v>
       </c>
       <c r="B24" t="n">
-        <v>57513</v>
+        <v>91184</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3015,21 +3030,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3039,10 +3054,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>465930</v>
+        <v>466286</v>
       </c>
       <c r="R24" t="n">
-        <v>7055704</v>
+        <v>7056084</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3075,11 +3090,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3106,10 +3116,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124808193</v>
+        <v>124808161</v>
       </c>
       <c r="B25" t="n">
-        <v>91030</v>
+        <v>57635</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3122,21 +3132,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3146,10 +3156,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>466155</v>
+        <v>465859</v>
       </c>
       <c r="R25" t="n">
-        <v>7055735</v>
+        <v>7055744</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3182,6 +3192,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3208,10 +3223,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124808125</v>
+        <v>124808132</v>
       </c>
       <c r="B26" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3242,24 +3257,16 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Åkerån, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466019</v>
+        <v>466002</v>
       </c>
       <c r="R26" t="n">
-        <v>7055741</v>
+        <v>7055866</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3296,7 +3303,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Bohål ca 6m upp i bruten gran</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3323,10 +3330,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124808182</v>
+        <v>124808133</v>
       </c>
       <c r="B27" t="n">
-        <v>79892</v>
+        <v>57635</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3339,21 +3346,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3363,10 +3370,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466191</v>
+        <v>466022</v>
       </c>
       <c r="R27" t="n">
-        <v>7055781</v>
+        <v>7055840</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3399,6 +3406,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3425,10 +3437,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124808139</v>
+        <v>124808151</v>
       </c>
       <c r="B28" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3465,10 +3477,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466126</v>
+        <v>466148</v>
       </c>
       <c r="R28" t="n">
-        <v>7055914</v>
+        <v>7055732</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3505,7 +3517,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3532,10 +3544,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124808146</v>
+        <v>124808149</v>
       </c>
       <c r="B29" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3572,10 +3584,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466210</v>
+        <v>466219</v>
       </c>
       <c r="R29" t="n">
-        <v>7056130</v>
+        <v>7055842</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3612,7 +3624,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3639,10 +3651,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124808162</v>
+        <v>124808184</v>
       </c>
       <c r="B30" t="n">
-        <v>57513</v>
+        <v>80028</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3655,21 +3667,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3679,10 +3691,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>465856</v>
+        <v>466183</v>
       </c>
       <c r="R30" t="n">
-        <v>7055738</v>
+        <v>7056145</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3715,11 +3727,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3746,10 +3753,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124808157</v>
+        <v>124808123</v>
       </c>
       <c r="B31" t="n">
-        <v>57513</v>
+        <v>91166</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3762,21 +3769,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3786,10 +3793,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466023</v>
+        <v>465924</v>
       </c>
       <c r="R31" t="n">
-        <v>7055706</v>
+        <v>7055720</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3822,11 +3829,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3853,10 +3855,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124808158</v>
+        <v>124808187</v>
       </c>
       <c r="B32" t="n">
-        <v>57513</v>
+        <v>91184</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3869,21 +3871,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3893,10 +3895,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>465957</v>
+        <v>465961</v>
       </c>
       <c r="R32" t="n">
-        <v>7055698</v>
+        <v>7055835</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3929,11 +3931,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3960,10 +3957,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124808140</v>
+        <v>124808144</v>
       </c>
       <c r="B33" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4000,10 +3997,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466113</v>
+        <v>466231</v>
       </c>
       <c r="R33" t="n">
-        <v>7055912</v>
+        <v>7056150</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4067,10 +4064,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124808185</v>
+        <v>124808190</v>
       </c>
       <c r="B34" t="n">
-        <v>79891</v>
+        <v>91184</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4083,21 +4080,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4107,10 +4104,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>466191</v>
+        <v>466147</v>
       </c>
       <c r="R34" t="n">
-        <v>7055781</v>
+        <v>7056067</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4169,10 +4166,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124808156</v>
+        <v>124808134</v>
       </c>
       <c r="B35" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4209,10 +4206,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>466027</v>
+        <v>466020</v>
       </c>
       <c r="R35" t="n">
-        <v>7055757</v>
+        <v>7055801</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4276,10 +4273,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124808151</v>
+        <v>124808142</v>
       </c>
       <c r="B36" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4316,10 +4313,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>466148</v>
+        <v>466212</v>
       </c>
       <c r="R36" t="n">
-        <v>7055732</v>
+        <v>7056170</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4383,10 +4380,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124808131</v>
+        <v>124808157</v>
       </c>
       <c r="B37" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4426,7 +4423,7 @@
         <v>466023</v>
       </c>
       <c r="R37" t="n">
-        <v>7055886</v>
+        <v>7055706</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4490,10 +4487,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124808144</v>
+        <v>124808183</v>
       </c>
       <c r="B38" t="n">
-        <v>57513</v>
+        <v>91459</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4506,21 +4503,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4530,10 +4527,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>466231</v>
+        <v>465924</v>
       </c>
       <c r="R38" t="n">
-        <v>7056150</v>
+        <v>7055722</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4566,11 +4563,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4597,10 +4589,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124808160</v>
+        <v>124808182</v>
       </c>
       <c r="B39" t="n">
-        <v>57513</v>
+        <v>80029</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4613,21 +4605,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4637,10 +4629,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>465939</v>
+        <v>466191</v>
       </c>
       <c r="R39" t="n">
-        <v>7055717</v>
+        <v>7055781</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4673,11 +4665,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4704,10 +4691,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124808152</v>
+        <v>124808145</v>
       </c>
       <c r="B40" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4744,10 +4731,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>466072</v>
+        <v>466217</v>
       </c>
       <c r="R40" t="n">
-        <v>7055589</v>
+        <v>7056120</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4811,10 +4798,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124808184</v>
+        <v>124808125</v>
       </c>
       <c r="B41" t="n">
-        <v>79891</v>
+        <v>57635</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4827,34 +4814,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Åkerån, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>466183</v>
+        <v>466019</v>
       </c>
       <c r="R41" t="n">
-        <v>7056145</v>
+        <v>7055741</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4887,6 +4882,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Bohål ca 6m upp i bruten gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4913,10 +4913,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124808129</v>
+        <v>124808156</v>
       </c>
       <c r="B42" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4953,10 +4953,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>465997</v>
+        <v>466027</v>
       </c>
       <c r="R42" t="n">
-        <v>7055926</v>
+        <v>7055757</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5020,10 +5020,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124808161</v>
+        <v>124808131</v>
       </c>
       <c r="B43" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5060,10 +5060,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>465859</v>
+        <v>466023</v>
       </c>
       <c r="R43" t="n">
-        <v>7055744</v>
+        <v>7055886</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5127,10 +5127,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124808190</v>
+        <v>124808136</v>
       </c>
       <c r="B44" t="n">
-        <v>91030</v>
+        <v>57635</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5143,21 +5143,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5167,10 +5167,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>466147</v>
+        <v>466032</v>
       </c>
       <c r="R44" t="n">
-        <v>7056067</v>
+        <v>7055802</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5203,6 +5203,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5229,10 +5234,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124808187</v>
+        <v>124808137</v>
       </c>
       <c r="B45" t="n">
-        <v>91030</v>
+        <v>57635</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5245,21 +5250,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5269,10 +5274,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>465961</v>
+        <v>466097</v>
       </c>
       <c r="R45" t="n">
-        <v>7055835</v>
+        <v>7055831</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5305,6 +5310,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5331,10 +5341,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124808149</v>
+        <v>124808188</v>
       </c>
       <c r="B46" t="n">
-        <v>57513</v>
+        <v>91184</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5347,21 +5357,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5371,10 +5381,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>466219</v>
+        <v>466015</v>
       </c>
       <c r="R46" t="n">
-        <v>7055842</v>
+        <v>7055934</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5407,11 +5417,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5438,10 +5443,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124808132</v>
+        <v>124808195</v>
       </c>
       <c r="B47" t="n">
-        <v>57513</v>
+        <v>91184</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5454,21 +5459,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5478,10 +5483,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>466002</v>
+        <v>466026</v>
       </c>
       <c r="R47" t="n">
-        <v>7055866</v>
+        <v>7055714</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5514,11 +5519,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5545,10 +5545,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124808150</v>
+        <v>124808129</v>
       </c>
       <c r="B48" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5585,10 +5585,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>466187</v>
+        <v>465997</v>
       </c>
       <c r="R48" t="n">
-        <v>7055846</v>
+        <v>7055926</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>

--- a/artfynd/A 11097-2024 artfynd.xlsx
+++ b/artfynd/A 11097-2024 artfynd.xlsx
@@ -3116,7 +3116,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124808161</v>
+        <v>124808151</v>
       </c>
       <c r="B25" t="n">
         <v>57635</v>
@@ -3156,10 +3156,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>465859</v>
+        <v>466148</v>
       </c>
       <c r="R25" t="n">
-        <v>7055744</v>
+        <v>7055732</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3223,7 +3223,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124808132</v>
+        <v>124808161</v>
       </c>
       <c r="B26" t="n">
         <v>57635</v>
@@ -3263,10 +3263,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466002</v>
+        <v>465859</v>
       </c>
       <c r="R26" t="n">
-        <v>7055866</v>
+        <v>7055744</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3330,7 +3330,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124808133</v>
+        <v>124808132</v>
       </c>
       <c r="B27" t="n">
         <v>57635</v>
@@ -3370,10 +3370,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466022</v>
+        <v>466002</v>
       </c>
       <c r="R27" t="n">
-        <v>7055840</v>
+        <v>7055866</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3437,7 +3437,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124808151</v>
+        <v>124808133</v>
       </c>
       <c r="B28" t="n">
         <v>57635</v>
@@ -3477,10 +3477,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466148</v>
+        <v>466022</v>
       </c>
       <c r="R28" t="n">
-        <v>7055732</v>
+        <v>7055840</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4064,10 +4064,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124808190</v>
+        <v>124808134</v>
       </c>
       <c r="B34" t="n">
-        <v>91184</v>
+        <v>57635</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4080,21 +4080,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4104,10 +4104,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>466147</v>
+        <v>466020</v>
       </c>
       <c r="R34" t="n">
-        <v>7056067</v>
+        <v>7055801</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4140,6 +4140,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4166,7 +4171,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124808134</v>
+        <v>124808142</v>
       </c>
       <c r="B35" t="n">
         <v>57635</v>
@@ -4206,10 +4211,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>466020</v>
+        <v>466212</v>
       </c>
       <c r="R35" t="n">
-        <v>7055801</v>
+        <v>7056170</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4273,7 +4278,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124808142</v>
+        <v>124808157</v>
       </c>
       <c r="B36" t="n">
         <v>57635</v>
@@ -4313,10 +4318,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>466212</v>
+        <v>466023</v>
       </c>
       <c r="R36" t="n">
-        <v>7056170</v>
+        <v>7055706</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4380,10 +4385,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124808157</v>
+        <v>124808190</v>
       </c>
       <c r="B37" t="n">
-        <v>57635</v>
+        <v>91184</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4396,21 +4401,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4420,10 +4425,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>466023</v>
+        <v>466147</v>
       </c>
       <c r="R37" t="n">
-        <v>7055706</v>
+        <v>7056067</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4456,11 +4461,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5341,10 +5341,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124808188</v>
+        <v>124808129</v>
       </c>
       <c r="B46" t="n">
-        <v>91184</v>
+        <v>57635</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5357,21 +5357,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5381,10 +5381,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>466015</v>
+        <v>465997</v>
       </c>
       <c r="R46" t="n">
-        <v>7055934</v>
+        <v>7055926</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5417,6 +5417,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5443,7 +5448,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124808195</v>
+        <v>124808188</v>
       </c>
       <c r="B47" t="n">
         <v>91184</v>
@@ -5483,10 +5488,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>466026</v>
+        <v>466015</v>
       </c>
       <c r="R47" t="n">
-        <v>7055714</v>
+        <v>7055934</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5545,10 +5550,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124808129</v>
+        <v>124808195</v>
       </c>
       <c r="B48" t="n">
-        <v>57635</v>
+        <v>91184</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5561,21 +5566,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5585,10 +5590,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>465997</v>
+        <v>466026</v>
       </c>
       <c r="R48" t="n">
-        <v>7055926</v>
+        <v>7055714</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5621,11 +5626,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">

--- a/artfynd/A 11097-2024 artfynd.xlsx
+++ b/artfynd/A 11097-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124808154</v>
+        <v>124808135</v>
       </c>
       <c r="B2" t="n">
         <v>57635</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>466093</v>
+        <v>466024</v>
       </c>
       <c r="R2" t="n">
-        <v>7055760</v>
+        <v>7055801</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124808193</v>
+        <v>124808189</v>
       </c>
       <c r="B3" t="n">
         <v>91184</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466155</v>
+        <v>466286</v>
       </c>
       <c r="R3" t="n">
-        <v>7055735</v>
+        <v>7056084</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124808126</v>
+        <v>124808193</v>
       </c>
       <c r="B4" t="n">
-        <v>57635</v>
+        <v>91184</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465931</v>
+        <v>466155</v>
       </c>
       <c r="R4" t="n">
-        <v>7055792</v>
+        <v>7055735</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,11 +960,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124808185</v>
+        <v>124808154</v>
       </c>
       <c r="B5" t="n">
-        <v>80028</v>
+        <v>57635</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>466191</v>
+        <v>466093</v>
       </c>
       <c r="R5" t="n">
-        <v>7055781</v>
+        <v>7055760</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,6 +1062,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124808138</v>
+        <v>124808183</v>
       </c>
       <c r="B6" t="n">
-        <v>57635</v>
+        <v>91459</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466123</v>
+        <v>465924</v>
       </c>
       <c r="R6" t="n">
-        <v>7055839</v>
+        <v>7055722</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,11 +1169,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,7 +1195,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124808140</v>
+        <v>124808158</v>
       </c>
       <c r="B7" t="n">
         <v>57635</v>
@@ -1240,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466113</v>
+        <v>465957</v>
       </c>
       <c r="R7" t="n">
-        <v>7055912</v>
+        <v>7055698</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1307,7 +1302,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124808139</v>
+        <v>124808148</v>
       </c>
       <c r="B8" t="n">
         <v>57635</v>
@@ -1347,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466126</v>
+        <v>466190</v>
       </c>
       <c r="R8" t="n">
-        <v>7055914</v>
+        <v>7055952</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1382,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1414,7 +1409,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124808162</v>
+        <v>124808160</v>
       </c>
       <c r="B9" t="n">
         <v>57635</v>
@@ -1454,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>465856</v>
+        <v>465939</v>
       </c>
       <c r="R9" t="n">
-        <v>7055738</v>
+        <v>7055717</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1521,7 +1516,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124808150</v>
+        <v>124808149</v>
       </c>
       <c r="B10" t="n">
         <v>57635</v>
@@ -1561,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466187</v>
+        <v>466219</v>
       </c>
       <c r="R10" t="n">
-        <v>7055846</v>
+        <v>7055842</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1628,7 +1623,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124808148</v>
+        <v>124808150</v>
       </c>
       <c r="B11" t="n">
         <v>57635</v>
@@ -1668,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466190</v>
+        <v>466187</v>
       </c>
       <c r="R11" t="n">
-        <v>7055952</v>
+        <v>7055846</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,7 +1703,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,10 +1730,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124808158</v>
+        <v>124808195</v>
       </c>
       <c r="B12" t="n">
-        <v>57635</v>
+        <v>91184</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>465957</v>
+        <v>466026</v>
       </c>
       <c r="R12" t="n">
-        <v>7055698</v>
+        <v>7055714</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1811,11 +1806,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1842,10 +1832,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124808143</v>
+        <v>124808182</v>
       </c>
       <c r="B13" t="n">
-        <v>57635</v>
+        <v>80029</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1858,21 +1848,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1882,10 +1872,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466291</v>
+        <v>466191</v>
       </c>
       <c r="R13" t="n">
-        <v>7056076</v>
+        <v>7055781</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1918,11 +1908,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1949,7 +1934,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124808159</v>
+        <v>124808140</v>
       </c>
       <c r="B14" t="n">
         <v>57635</v>
@@ -1989,10 +1974,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>465930</v>
+        <v>466113</v>
       </c>
       <c r="R14" t="n">
-        <v>7055704</v>
+        <v>7055912</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2014,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2056,7 +2041,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124808160</v>
+        <v>124808142</v>
       </c>
       <c r="B15" t="n">
         <v>57635</v>
@@ -2096,10 +2081,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>465939</v>
+        <v>466212</v>
       </c>
       <c r="R15" t="n">
-        <v>7055717</v>
+        <v>7056170</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2163,7 +2148,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124808155</v>
+        <v>124808162</v>
       </c>
       <c r="B16" t="n">
         <v>57635</v>
@@ -2203,10 +2188,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466025</v>
+        <v>465856</v>
       </c>
       <c r="R16" t="n">
-        <v>7055769</v>
+        <v>7055738</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2270,7 +2255,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124808152</v>
+        <v>124808138</v>
       </c>
       <c r="B17" t="n">
         <v>57635</v>
@@ -2310,10 +2295,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466072</v>
+        <v>466123</v>
       </c>
       <c r="R17" t="n">
-        <v>7055589</v>
+        <v>7055839</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2377,10 +2362,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124808146</v>
+        <v>124808188</v>
       </c>
       <c r="B18" t="n">
-        <v>57635</v>
+        <v>91184</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2393,21 +2378,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2417,10 +2402,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466210</v>
+        <v>466015</v>
       </c>
       <c r="R18" t="n">
-        <v>7056130</v>
+        <v>7055934</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2453,11 +2438,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2484,10 +2464,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124808127</v>
+        <v>124808123</v>
       </c>
       <c r="B19" t="n">
-        <v>57635</v>
+        <v>91166</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2500,21 +2480,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2524,10 +2504,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>465979</v>
+        <v>465924</v>
       </c>
       <c r="R19" t="n">
-        <v>7055862</v>
+        <v>7055720</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2560,11 +2540,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2591,7 +2566,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124808135</v>
+        <v>124808161</v>
       </c>
       <c r="B20" t="n">
         <v>57635</v>
@@ -2631,10 +2606,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466024</v>
+        <v>465859</v>
       </c>
       <c r="R20" t="n">
-        <v>7055801</v>
+        <v>7055744</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2698,7 +2673,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124808147</v>
+        <v>124808134</v>
       </c>
       <c r="B21" t="n">
         <v>57635</v>
@@ -2738,10 +2713,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>466151</v>
+        <v>466020</v>
       </c>
       <c r="R21" t="n">
-        <v>7055999</v>
+        <v>7055801</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2805,10 +2780,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124808194</v>
+        <v>124808136</v>
       </c>
       <c r="B22" t="n">
-        <v>91184</v>
+        <v>57635</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2821,21 +2796,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2845,10 +2820,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>466020</v>
+        <v>466032</v>
       </c>
       <c r="R22" t="n">
-        <v>7055742</v>
+        <v>7055802</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2881,6 +2856,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2907,7 +2887,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124808141</v>
+        <v>124808132</v>
       </c>
       <c r="B23" t="n">
         <v>57635</v>
@@ -2947,10 +2927,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>466172</v>
+        <v>466002</v>
       </c>
       <c r="R23" t="n">
-        <v>7056129</v>
+        <v>7055866</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3014,10 +2994,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124808189</v>
+        <v>124808137</v>
       </c>
       <c r="B24" t="n">
-        <v>91184</v>
+        <v>57635</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3030,21 +3010,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3054,10 +3034,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>466286</v>
+        <v>466097</v>
       </c>
       <c r="R24" t="n">
-        <v>7056084</v>
+        <v>7055831</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3090,6 +3070,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3116,7 +3101,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124808151</v>
+        <v>124808129</v>
       </c>
       <c r="B25" t="n">
         <v>57635</v>
@@ -3156,10 +3141,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>466148</v>
+        <v>465997</v>
       </c>
       <c r="R25" t="n">
-        <v>7055732</v>
+        <v>7055926</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3196,7 +3181,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3223,7 +3208,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124808161</v>
+        <v>124808141</v>
       </c>
       <c r="B26" t="n">
         <v>57635</v>
@@ -3263,10 +3248,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>465859</v>
+        <v>466172</v>
       </c>
       <c r="R26" t="n">
-        <v>7055744</v>
+        <v>7056129</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3330,7 +3315,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124808132</v>
+        <v>124808131</v>
       </c>
       <c r="B27" t="n">
         <v>57635</v>
@@ -3370,10 +3355,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466002</v>
+        <v>466023</v>
       </c>
       <c r="R27" t="n">
-        <v>7055866</v>
+        <v>7055886</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3437,7 +3422,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124808133</v>
+        <v>124808147</v>
       </c>
       <c r="B28" t="n">
         <v>57635</v>
@@ -3477,10 +3462,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466022</v>
+        <v>466151</v>
       </c>
       <c r="R28" t="n">
-        <v>7055840</v>
+        <v>7055999</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3544,7 +3529,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124808149</v>
+        <v>124808127</v>
       </c>
       <c r="B29" t="n">
         <v>57635</v>
@@ -3584,10 +3569,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466219</v>
+        <v>465979</v>
       </c>
       <c r="R29" t="n">
-        <v>7055842</v>
+        <v>7055862</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3624,7 +3609,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3651,10 +3636,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124808184</v>
+        <v>124808133</v>
       </c>
       <c r="B30" t="n">
-        <v>80028</v>
+        <v>57635</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3667,21 +3652,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3691,10 +3676,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>466183</v>
+        <v>466022</v>
       </c>
       <c r="R30" t="n">
-        <v>7056145</v>
+        <v>7055840</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3727,6 +3712,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3753,10 +3743,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124808123</v>
+        <v>124808151</v>
       </c>
       <c r="B31" t="n">
-        <v>91166</v>
+        <v>57635</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3769,21 +3759,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3793,10 +3783,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>465924</v>
+        <v>466148</v>
       </c>
       <c r="R31" t="n">
-        <v>7055720</v>
+        <v>7055732</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3829,6 +3819,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3855,10 +3850,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124808187</v>
+        <v>124808184</v>
       </c>
       <c r="B32" t="n">
-        <v>91184</v>
+        <v>80028</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3871,21 +3866,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3895,10 +3890,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>465961</v>
+        <v>466183</v>
       </c>
       <c r="R32" t="n">
-        <v>7055835</v>
+        <v>7056145</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3957,10 +3952,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124808144</v>
+        <v>124808185</v>
       </c>
       <c r="B33" t="n">
-        <v>57635</v>
+        <v>80028</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3973,21 +3968,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3997,10 +3992,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466231</v>
+        <v>466191</v>
       </c>
       <c r="R33" t="n">
-        <v>7056150</v>
+        <v>7055781</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4033,11 +4028,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4064,7 +4054,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124808134</v>
+        <v>124808145</v>
       </c>
       <c r="B34" t="n">
         <v>57635</v>
@@ -4104,10 +4094,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>466020</v>
+        <v>466217</v>
       </c>
       <c r="R34" t="n">
-        <v>7055801</v>
+        <v>7056120</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4171,7 +4161,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124808142</v>
+        <v>124808159</v>
       </c>
       <c r="B35" t="n">
         <v>57635</v>
@@ -4211,10 +4201,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>466212</v>
+        <v>465930</v>
       </c>
       <c r="R35" t="n">
-        <v>7056170</v>
+        <v>7055704</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4251,7 +4241,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4278,7 +4268,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124808157</v>
+        <v>124808156</v>
       </c>
       <c r="B36" t="n">
         <v>57635</v>
@@ -4318,10 +4308,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>466023</v>
+        <v>466027</v>
       </c>
       <c r="R36" t="n">
-        <v>7055706</v>
+        <v>7055757</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4385,10 +4375,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124808190</v>
+        <v>124808146</v>
       </c>
       <c r="B37" t="n">
-        <v>91184</v>
+        <v>57635</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4401,21 +4391,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4425,10 +4415,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>466147</v>
+        <v>466210</v>
       </c>
       <c r="R37" t="n">
-        <v>7056067</v>
+        <v>7056130</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4461,6 +4451,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4487,10 +4482,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124808183</v>
+        <v>124808190</v>
       </c>
       <c r="B38" t="n">
-        <v>91459</v>
+        <v>91184</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4503,21 +4498,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4527,10 +4522,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>465924</v>
+        <v>466147</v>
       </c>
       <c r="R38" t="n">
-        <v>7055722</v>
+        <v>7056067</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4589,10 +4584,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124808182</v>
+        <v>124808144</v>
       </c>
       <c r="B39" t="n">
-        <v>80029</v>
+        <v>57635</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4605,21 +4600,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4629,10 +4624,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>466191</v>
+        <v>466231</v>
       </c>
       <c r="R39" t="n">
-        <v>7055781</v>
+        <v>7056150</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4665,6 +4660,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4691,7 +4691,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124808145</v>
+        <v>124808125</v>
       </c>
       <c r="B40" t="n">
         <v>57635</v>
@@ -4725,16 +4725,24 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Åkerån, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>466217</v>
+        <v>466019</v>
       </c>
       <c r="R40" t="n">
-        <v>7056120</v>
+        <v>7055741</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4771,7 +4779,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Bohål ca 6m upp i bruten gran</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4798,7 +4806,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124808125</v>
+        <v>124808152</v>
       </c>
       <c r="B41" t="n">
         <v>57635</v>
@@ -4832,24 +4840,16 @@
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Åkerån, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>466019</v>
+        <v>466072</v>
       </c>
       <c r="R41" t="n">
-        <v>7055741</v>
+        <v>7055589</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4886,7 +4886,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Bohål ca 6m upp i bruten gran</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4913,7 +4913,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124808156</v>
+        <v>124808126</v>
       </c>
       <c r="B42" t="n">
         <v>57635</v>
@@ -4953,10 +4953,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>466027</v>
+        <v>465931</v>
       </c>
       <c r="R42" t="n">
-        <v>7055757</v>
+        <v>7055792</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5020,10 +5020,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124808131</v>
+        <v>124808194</v>
       </c>
       <c r="B43" t="n">
-        <v>57635</v>
+        <v>91184</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5036,21 +5036,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5060,10 +5060,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>466023</v>
+        <v>466020</v>
       </c>
       <c r="R43" t="n">
-        <v>7055886</v>
+        <v>7055742</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5096,11 +5096,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5127,10 +5122,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124808136</v>
+        <v>124808187</v>
       </c>
       <c r="B44" t="n">
-        <v>57635</v>
+        <v>91184</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5143,21 +5138,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5167,10 +5162,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>466032</v>
+        <v>465961</v>
       </c>
       <c r="R44" t="n">
-        <v>7055802</v>
+        <v>7055835</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5203,11 +5198,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5234,7 +5224,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124808137</v>
+        <v>124808139</v>
       </c>
       <c r="B45" t="n">
         <v>57635</v>
@@ -5274,10 +5264,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>466097</v>
+        <v>466126</v>
       </c>
       <c r="R45" t="n">
-        <v>7055831</v>
+        <v>7055914</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5314,7 +5304,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5341,7 +5331,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124808129</v>
+        <v>124808155</v>
       </c>
       <c r="B46" t="n">
         <v>57635</v>
@@ -5381,10 +5371,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>465997</v>
+        <v>466025</v>
       </c>
       <c r="R46" t="n">
-        <v>7055926</v>
+        <v>7055769</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5421,7 +5411,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5448,10 +5438,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124808188</v>
+        <v>124808143</v>
       </c>
       <c r="B47" t="n">
-        <v>91184</v>
+        <v>57635</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5464,21 +5454,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5488,10 +5478,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>466015</v>
+        <v>466291</v>
       </c>
       <c r="R47" t="n">
-        <v>7055934</v>
+        <v>7056076</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5524,6 +5514,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5550,10 +5545,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124808195</v>
+        <v>124808157</v>
       </c>
       <c r="B48" t="n">
-        <v>91184</v>
+        <v>57635</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5566,21 +5561,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5590,10 +5585,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>466026</v>
+        <v>466023</v>
       </c>
       <c r="R48" t="n">
-        <v>7055714</v>
+        <v>7055706</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5626,6 +5621,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">

--- a/artfynd/A 11097-2024 artfynd.xlsx
+++ b/artfynd/A 11097-2024 artfynd.xlsx
@@ -4806,10 +4806,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124808152</v>
+        <v>124808194</v>
       </c>
       <c r="B41" t="n">
-        <v>57635</v>
+        <v>91184</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4822,21 +4822,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4846,10 +4846,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>466072</v>
+        <v>466020</v>
       </c>
       <c r="R41" t="n">
-        <v>7055589</v>
+        <v>7055742</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4882,11 +4882,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4913,7 +4908,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124808126</v>
+        <v>124808152</v>
       </c>
       <c r="B42" t="n">
         <v>57635</v>
@@ -4953,10 +4948,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>465931</v>
+        <v>466072</v>
       </c>
       <c r="R42" t="n">
-        <v>7055792</v>
+        <v>7055589</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5020,10 +5015,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124808194</v>
+        <v>124808126</v>
       </c>
       <c r="B43" t="n">
-        <v>91184</v>
+        <v>57635</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5036,21 +5031,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5060,10 +5055,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>466020</v>
+        <v>465931</v>
       </c>
       <c r="R43" t="n">
-        <v>7055742</v>
+        <v>7055792</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5096,6 +5091,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">

--- a/artfynd/A 11097-2024 artfynd.xlsx
+++ b/artfynd/A 11097-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>124808135</v>
       </c>
       <c r="B2" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>124808154</v>
       </c>
       <c r="B5" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>124808158</v>
       </c>
       <c r="B7" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>124808148</v>
       </c>
       <c r="B8" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>124808160</v>
       </c>
       <c r="B9" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>124808149</v>
       </c>
       <c r="B10" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>124808150</v>
       </c>
       <c r="B11" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>124808140</v>
       </c>
       <c r="B14" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>124808142</v>
       </c>
       <c r="B15" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
         <v>124808162</v>
       </c>
       <c r="B16" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         <v>124808138</v>
       </c>
       <c r="B17" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
         <v>124808161</v>
       </c>
       <c r="B20" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         <v>124808134</v>
       </c>
       <c r="B21" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2718,7 +2718,7 @@
         <v>124808136</v>
       </c>
       <c r="B22" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         <v>124808132</v>
       </c>
       <c r="B23" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         <v>124808137</v>
       </c>
       <c r="B24" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         <v>124808129</v>
       </c>
       <c r="B25" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3126,7 +3126,7 @@
         <v>124808141</v>
       </c>
       <c r="B26" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3228,7 +3228,7 @@
         <v>124808131</v>
       </c>
       <c r="B27" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3330,7 +3330,7 @@
         <v>124808147</v>
       </c>
       <c r="B28" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
         <v>124808127</v>
       </c>
       <c r="B29" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
         <v>124808133</v>
       </c>
       <c r="B30" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3636,7 +3636,7 @@
         <v>124808151</v>
       </c>
       <c r="B31" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3942,7 +3942,7 @@
         <v>124808145</v>
       </c>
       <c r="B34" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4044,7 +4044,7 @@
         <v>124808159</v>
       </c>
       <c r="B35" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         <v>124808156</v>
       </c>
       <c r="B36" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4248,7 +4248,7 @@
         <v>124808146</v>
       </c>
       <c r="B37" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4452,7 +4452,7 @@
         <v>124808144</v>
       </c>
       <c r="B39" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4554,7 +4554,7 @@
         <v>124808125</v>
       </c>
       <c r="B40" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         <v>124808152</v>
       </c>
       <c r="B42" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4868,7 +4868,7 @@
         <v>124808126</v>
       </c>
       <c r="B43" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5072,7 +5072,7 @@
         <v>124808139</v>
       </c>
       <c r="B45" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>124808155</v>
       </c>
       <c r="B46" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5276,7 +5276,7 @@
         <v>124808143</v>
       </c>
       <c r="B47" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5378,7 +5378,7 @@
         <v>124808157</v>
       </c>
       <c r="B48" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 11097-2024 artfynd.xlsx
+++ b/artfynd/A 11097-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>124808135</v>
       </c>
       <c r="B2" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>124808154</v>
       </c>
       <c r="B5" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>124808158</v>
       </c>
       <c r="B7" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>124808148</v>
       </c>
       <c r="B8" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>124808160</v>
       </c>
       <c r="B9" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>124808149</v>
       </c>
       <c r="B10" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>124808150</v>
       </c>
       <c r="B11" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>124808140</v>
       </c>
       <c r="B14" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>124808142</v>
       </c>
       <c r="B15" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
         <v>124808162</v>
       </c>
       <c r="B16" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         <v>124808138</v>
       </c>
       <c r="B17" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
         <v>124808161</v>
       </c>
       <c r="B20" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         <v>124808134</v>
       </c>
       <c r="B21" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2718,7 +2718,7 @@
         <v>124808136</v>
       </c>
       <c r="B22" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         <v>124808132</v>
       </c>
       <c r="B23" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         <v>124808137</v>
       </c>
       <c r="B24" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         <v>124808129</v>
       </c>
       <c r="B25" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3126,7 +3126,7 @@
         <v>124808141</v>
       </c>
       <c r="B26" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3228,7 +3228,7 @@
         <v>124808131</v>
       </c>
       <c r="B27" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3330,7 +3330,7 @@
         <v>124808147</v>
       </c>
       <c r="B28" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
         <v>124808127</v>
       </c>
       <c r="B29" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
         <v>124808133</v>
       </c>
       <c r="B30" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3636,7 +3636,7 @@
         <v>124808151</v>
       </c>
       <c r="B31" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3942,7 +3942,7 @@
         <v>124808145</v>
       </c>
       <c r="B34" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4044,7 +4044,7 @@
         <v>124808159</v>
       </c>
       <c r="B35" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         <v>124808156</v>
       </c>
       <c r="B36" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4248,7 +4248,7 @@
         <v>124808146</v>
       </c>
       <c r="B37" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4452,7 +4452,7 @@
         <v>124808144</v>
       </c>
       <c r="B39" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4554,7 +4554,7 @@
         <v>124808125</v>
       </c>
       <c r="B40" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         <v>124808152</v>
       </c>
       <c r="B42" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4868,7 +4868,7 @@
         <v>124808126</v>
       </c>
       <c r="B43" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5072,7 +5072,7 @@
         <v>124808139</v>
       </c>
       <c r="B45" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>124808155</v>
       </c>
       <c r="B46" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5276,7 +5276,7 @@
         <v>124808143</v>
       </c>
       <c r="B47" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5378,7 +5378,7 @@
         <v>124808157</v>
       </c>
       <c r="B48" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 11097-2024 artfynd.xlsx
+++ b/artfynd/A 11097-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>124808135</v>
       </c>
       <c r="B2" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>124808154</v>
       </c>
       <c r="B5" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>124808158</v>
       </c>
       <c r="B7" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>124808148</v>
       </c>
       <c r="B8" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>124808160</v>
       </c>
       <c r="B9" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>124808149</v>
       </c>
       <c r="B10" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>124808150</v>
       </c>
       <c r="B11" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>124808140</v>
       </c>
       <c r="B14" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>124808142</v>
       </c>
       <c r="B15" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
         <v>124808162</v>
       </c>
       <c r="B16" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         <v>124808138</v>
       </c>
       <c r="B17" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
         <v>124808161</v>
       </c>
       <c r="B20" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         <v>124808134</v>
       </c>
       <c r="B21" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2718,7 +2718,7 @@
         <v>124808136</v>
       </c>
       <c r="B22" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         <v>124808132</v>
       </c>
       <c r="B23" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         <v>124808137</v>
       </c>
       <c r="B24" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         <v>124808129</v>
       </c>
       <c r="B25" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3126,7 +3126,7 @@
         <v>124808141</v>
       </c>
       <c r="B26" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3228,7 +3228,7 @@
         <v>124808131</v>
       </c>
       <c r="B27" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3330,7 +3330,7 @@
         <v>124808147</v>
       </c>
       <c r="B28" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
         <v>124808127</v>
       </c>
       <c r="B29" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
         <v>124808133</v>
       </c>
       <c r="B30" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3636,7 +3636,7 @@
         <v>124808151</v>
       </c>
       <c r="B31" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3942,7 +3942,7 @@
         <v>124808145</v>
       </c>
       <c r="B34" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4044,7 +4044,7 @@
         <v>124808159</v>
       </c>
       <c r="B35" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         <v>124808156</v>
       </c>
       <c r="B36" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4248,7 +4248,7 @@
         <v>124808146</v>
       </c>
       <c r="B37" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4452,7 +4452,7 @@
         <v>124808144</v>
       </c>
       <c r="B39" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4554,7 +4554,7 @@
         <v>124808125</v>
       </c>
       <c r="B40" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         <v>124808152</v>
       </c>
       <c r="B42" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4868,7 +4868,7 @@
         <v>124808126</v>
       </c>
       <c r="B43" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5072,7 +5072,7 @@
         <v>124808139</v>
       </c>
       <c r="B45" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>124808155</v>
       </c>
       <c r="B46" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5276,7 +5276,7 @@
         <v>124808143</v>
       </c>
       <c r="B47" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5378,7 +5378,7 @@
         <v>124808157</v>
       </c>
       <c r="B48" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 11097-2024 artfynd.xlsx
+++ b/artfynd/A 11097-2024 artfynd.xlsx
@@ -4554,7 +4554,7 @@
         <v>124808125</v>
       </c>
       <c r="B40" t="n">
-        <v>57657</v>
+        <v>57864</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 11097-2024 artfynd.xlsx
+++ b/artfynd/A 11097-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY48"/>
+  <dimension ref="A1:AY41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124808135</v>
+        <v>124808183</v>
       </c>
       <c r="B2" t="n">
-        <v>57657</v>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>466024</v>
+        <v>465924</v>
       </c>
       <c r="R2" t="n">
-        <v>7055801</v>
+        <v>7055722</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124808189</v>
+        <v>124808123</v>
       </c>
       <c r="B3" t="n">
-        <v>91184</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466286</v>
+        <v>465924</v>
       </c>
       <c r="R3" t="n">
-        <v>7056084</v>
+        <v>7055720</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124808193</v>
+        <v>124808182</v>
       </c>
       <c r="B4" t="n">
-        <v>91184</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>466155</v>
+        <v>466191</v>
       </c>
       <c r="R4" t="n">
-        <v>7055735</v>
+        <v>7055781</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124808154</v>
+        <v>124808184</v>
       </c>
       <c r="B5" t="n">
-        <v>57657</v>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -992,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1016,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>466093</v>
+        <v>466183</v>
       </c>
       <c r="R5" t="n">
-        <v>7055760</v>
+        <v>7056145</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1052,11 +1037,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1083,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124808183</v>
+        <v>124808185</v>
       </c>
       <c r="B6" t="n">
-        <v>91459</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>465924</v>
+        <v>466191</v>
       </c>
       <c r="R6" t="n">
-        <v>7055722</v>
+        <v>7055781</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124808158</v>
+        <v>124808125</v>
       </c>
       <c r="B7" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1214,16 +1189,24 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Åkerån, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>465957</v>
+        <v>466019</v>
       </c>
       <c r="R7" t="n">
-        <v>7055698</v>
+        <v>7055741</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1260,14 +1243,14 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Bohål ca 6m upp i bruten gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG7" t="b">
         <v>0</v>
@@ -1287,10 +1270,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124808148</v>
+        <v>124808126</v>
       </c>
       <c r="B8" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1322,10 +1305,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466190</v>
+        <v>465931</v>
       </c>
       <c r="R8" t="n">
-        <v>7055952</v>
+        <v>7055792</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1372,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124808160</v>
+        <v>124808127</v>
       </c>
       <c r="B9" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1424,10 +1407,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>465939</v>
+        <v>465979</v>
       </c>
       <c r="R9" t="n">
-        <v>7055717</v>
+        <v>7055862</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1474,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124808149</v>
+        <v>124808129</v>
       </c>
       <c r="B10" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1526,10 +1509,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466219</v>
+        <v>465997</v>
       </c>
       <c r="R10" t="n">
-        <v>7055842</v>
+        <v>7055926</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1576,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124808150</v>
+        <v>124808131</v>
       </c>
       <c r="B11" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1628,10 +1611,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466187</v>
+        <v>466023</v>
       </c>
       <c r="R11" t="n">
-        <v>7055846</v>
+        <v>7055886</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1668,7 +1651,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1695,15 +1678,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124808195</v>
+        <v>124808132</v>
       </c>
       <c r="B12" t="n">
-        <v>91184</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1711,21 +1689,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1713,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466026</v>
+        <v>466002</v>
       </c>
       <c r="R12" t="n">
-        <v>7055714</v>
+        <v>7055866</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1771,6 +1749,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1797,15 +1780,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124808182</v>
+        <v>124808133</v>
       </c>
       <c r="B13" t="n">
-        <v>80029</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1813,21 +1791,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1815,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466191</v>
+        <v>466022</v>
       </c>
       <c r="R13" t="n">
-        <v>7055781</v>
+        <v>7055840</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1873,6 +1851,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1899,10 +1882,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124808140</v>
+        <v>124808134</v>
       </c>
       <c r="B14" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1934,10 +1917,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>466113</v>
+        <v>466020</v>
       </c>
       <c r="R14" t="n">
-        <v>7055912</v>
+        <v>7055801</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,10 +1984,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124808142</v>
+        <v>124808135</v>
       </c>
       <c r="B15" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,10 +2019,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>466212</v>
+        <v>466024</v>
       </c>
       <c r="R15" t="n">
-        <v>7056170</v>
+        <v>7055801</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,10 +2086,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124808162</v>
+        <v>124808136</v>
       </c>
       <c r="B16" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2138,10 +2121,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>465856</v>
+        <v>466032</v>
       </c>
       <c r="R16" t="n">
-        <v>7055738</v>
+        <v>7055802</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,10 +2188,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124808138</v>
+        <v>124808137</v>
       </c>
       <c r="B17" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2240,10 +2223,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466123</v>
+        <v>466097</v>
       </c>
       <c r="R17" t="n">
-        <v>7055839</v>
+        <v>7055831</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2280,7 +2263,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2307,15 +2290,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124808188</v>
+        <v>124808138</v>
       </c>
       <c r="B18" t="n">
-        <v>91184</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2323,21 +2301,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2347,10 +2325,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466015</v>
+        <v>466123</v>
       </c>
       <c r="R18" t="n">
-        <v>7055934</v>
+        <v>7055839</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2383,6 +2361,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2409,15 +2392,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124808123</v>
+        <v>124808139</v>
       </c>
       <c r="B19" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2425,21 +2403,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2449,10 +2427,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>465924</v>
+        <v>466126</v>
       </c>
       <c r="R19" t="n">
-        <v>7055720</v>
+        <v>7055914</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2485,6 +2463,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2511,10 +2494,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124808161</v>
+        <v>124808140</v>
       </c>
       <c r="B20" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2546,10 +2529,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>465859</v>
+        <v>466113</v>
       </c>
       <c r="R20" t="n">
-        <v>7055744</v>
+        <v>7055912</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,10 +2596,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124808134</v>
+        <v>124808141</v>
       </c>
       <c r="B21" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2648,10 +2631,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>466020</v>
+        <v>466172</v>
       </c>
       <c r="R21" t="n">
-        <v>7055801</v>
+        <v>7056129</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,10 +2698,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124808136</v>
+        <v>124808142</v>
       </c>
       <c r="B22" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2750,10 +2733,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>466032</v>
+        <v>466212</v>
       </c>
       <c r="R22" t="n">
-        <v>7055802</v>
+        <v>7056170</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2817,10 +2800,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124808132</v>
+        <v>124808143</v>
       </c>
       <c r="B23" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2852,10 +2835,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>466002</v>
+        <v>466291</v>
       </c>
       <c r="R23" t="n">
-        <v>7055866</v>
+        <v>7056076</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2919,10 +2902,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124808137</v>
+        <v>124808144</v>
       </c>
       <c r="B24" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2954,10 +2937,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>466097</v>
+        <v>466231</v>
       </c>
       <c r="R24" t="n">
-        <v>7055831</v>
+        <v>7056150</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2994,7 +2977,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3021,10 +3004,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124808129</v>
+        <v>124808145</v>
       </c>
       <c r="B25" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3056,10 +3039,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>465997</v>
+        <v>466217</v>
       </c>
       <c r="R25" t="n">
-        <v>7055926</v>
+        <v>7056120</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3096,7 +3079,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3123,10 +3106,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124808141</v>
+        <v>124808146</v>
       </c>
       <c r="B26" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3158,10 +3141,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466172</v>
+        <v>466210</v>
       </c>
       <c r="R26" t="n">
-        <v>7056129</v>
+        <v>7056130</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3225,10 +3208,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124808131</v>
+        <v>124808147</v>
       </c>
       <c r="B27" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3260,10 +3243,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466023</v>
+        <v>466151</v>
       </c>
       <c r="R27" t="n">
-        <v>7055886</v>
+        <v>7055999</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3327,10 +3310,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124808147</v>
+        <v>124808148</v>
       </c>
       <c r="B28" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3362,10 +3345,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466151</v>
+        <v>466190</v>
       </c>
       <c r="R28" t="n">
-        <v>7055999</v>
+        <v>7055952</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3429,10 +3412,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124808127</v>
+        <v>124808149</v>
       </c>
       <c r="B29" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3464,10 +3447,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>465979</v>
+        <v>466219</v>
       </c>
       <c r="R29" t="n">
-        <v>7055862</v>
+        <v>7055842</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3504,7 +3487,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3531,10 +3514,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124808133</v>
+        <v>124808150</v>
       </c>
       <c r="B30" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3566,10 +3549,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>466022</v>
+        <v>466187</v>
       </c>
       <c r="R30" t="n">
-        <v>7055840</v>
+        <v>7055846</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3606,7 +3589,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3636,7 +3619,7 @@
         <v>124808151</v>
       </c>
       <c r="B31" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3735,15 +3718,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124808184</v>
+        <v>124808152</v>
       </c>
       <c r="B32" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3751,21 +3729,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3775,10 +3753,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466183</v>
+        <v>466072</v>
       </c>
       <c r="R32" t="n">
-        <v>7056145</v>
+        <v>7055589</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3811,6 +3789,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3837,15 +3820,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124808185</v>
+        <v>124808154</v>
       </c>
       <c r="B33" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3853,21 +3831,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3877,10 +3855,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466191</v>
+        <v>466093</v>
       </c>
       <c r="R33" t="n">
-        <v>7055781</v>
+        <v>7055760</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3913,6 +3891,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3939,10 +3922,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124808145</v>
+        <v>124808155</v>
       </c>
       <c r="B34" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3974,10 +3957,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>466217</v>
+        <v>466025</v>
       </c>
       <c r="R34" t="n">
-        <v>7056120</v>
+        <v>7055769</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4041,10 +4024,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124808159</v>
+        <v>124808156</v>
       </c>
       <c r="B35" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4076,10 +4059,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>465930</v>
+        <v>466027</v>
       </c>
       <c r="R35" t="n">
-        <v>7055704</v>
+        <v>7055757</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4116,7 +4099,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4143,10 +4126,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124808156</v>
+        <v>124808157</v>
       </c>
       <c r="B36" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4178,10 +4161,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>466027</v>
+        <v>466023</v>
       </c>
       <c r="R36" t="n">
-        <v>7055757</v>
+        <v>7055706</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4245,10 +4228,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124808146</v>
+        <v>124808158</v>
       </c>
       <c r="B37" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4280,10 +4263,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>466210</v>
+        <v>465957</v>
       </c>
       <c r="R37" t="n">
-        <v>7056130</v>
+        <v>7055698</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4347,15 +4330,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124808190</v>
+        <v>124808159</v>
       </c>
       <c r="B38" t="n">
-        <v>91184</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4363,21 +4341,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4387,10 +4365,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>466147</v>
+        <v>465930</v>
       </c>
       <c r="R38" t="n">
-        <v>7056067</v>
+        <v>7055704</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4423,6 +4401,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4449,10 +4432,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124808144</v>
+        <v>124808160</v>
       </c>
       <c r="B39" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4484,10 +4467,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>466231</v>
+        <v>465939</v>
       </c>
       <c r="R39" t="n">
-        <v>7056150</v>
+        <v>7055717</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4551,10 +4534,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124808125</v>
+        <v>124808161</v>
       </c>
       <c r="B40" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4580,24 +4563,16 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Åkerån, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>466019</v>
+        <v>465859</v>
       </c>
       <c r="R40" t="n">
-        <v>7055741</v>
+        <v>7055744</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4634,14 +4609,14 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Bohål ca 6m upp i bruten gran</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="b">
         <v>0</v>
@@ -4661,15 +4636,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124808194</v>
+        <v>124808162</v>
       </c>
       <c r="B41" t="n">
-        <v>91184</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4677,21 +4647,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4701,10 +4671,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>466020</v>
+        <v>465856</v>
       </c>
       <c r="R41" t="n">
-        <v>7055742</v>
+        <v>7055738</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4739,6 +4709,11 @@
           <t>2025-05-06</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -4760,720 +4735,6 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>124808152</v>
-      </c>
-      <c r="B42" t="n">
-        <v>57657</v>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>Åkerån, Jmt</t>
-        </is>
-      </c>
-      <c r="Q42" t="n">
-        <v>466072</v>
-      </c>
-      <c r="R42" t="n">
-        <v>7055589</v>
-      </c>
-      <c r="S42" t="n">
-        <v>10</v>
-      </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W42" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AA42" t="inlineStr">
-        <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
-      <c r="AD42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT42" t="inlineStr"/>
-      <c r="AW42" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>124808126</v>
-      </c>
-      <c r="B43" t="n">
-        <v>57657</v>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>Åkerån, Jmt</t>
-        </is>
-      </c>
-      <c r="Q43" t="n">
-        <v>465931</v>
-      </c>
-      <c r="R43" t="n">
-        <v>7055792</v>
-      </c>
-      <c r="S43" t="n">
-        <v>10</v>
-      </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V43" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W43" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y43" t="inlineStr">
-        <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AA43" t="inlineStr">
-        <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
-      <c r="AD43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT43" t="inlineStr"/>
-      <c r="AW43" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>124808187</v>
-      </c>
-      <c r="B44" t="n">
-        <v>91184</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E44" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>Åkerån, Jmt</t>
-        </is>
-      </c>
-      <c r="Q44" t="n">
-        <v>465961</v>
-      </c>
-      <c r="R44" t="n">
-        <v>7055835</v>
-      </c>
-      <c r="S44" t="n">
-        <v>10</v>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W44" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y44" t="inlineStr">
-        <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AA44" t="inlineStr">
-        <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AD44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT44" t="inlineStr"/>
-      <c r="AW44" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>124808139</v>
-      </c>
-      <c r="B45" t="n">
-        <v>57657</v>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E45" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>Åkerån, Jmt</t>
-        </is>
-      </c>
-      <c r="Q45" t="n">
-        <v>466126</v>
-      </c>
-      <c r="R45" t="n">
-        <v>7055914</v>
-      </c>
-      <c r="S45" t="n">
-        <v>10</v>
-      </c>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W45" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y45" t="inlineStr">
-        <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AA45" t="inlineStr">
-        <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
-      <c r="AD45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT45" t="inlineStr"/>
-      <c r="AW45" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY45" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>124808155</v>
-      </c>
-      <c r="B46" t="n">
-        <v>57657</v>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E46" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>Åkerån, Jmt</t>
-        </is>
-      </c>
-      <c r="Q46" t="n">
-        <v>466025</v>
-      </c>
-      <c r="R46" t="n">
-        <v>7055769</v>
-      </c>
-      <c r="S46" t="n">
-        <v>10</v>
-      </c>
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U46" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V46" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W46" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y46" t="inlineStr">
-        <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AA46" t="inlineStr">
-        <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
-      <c r="AD46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT46" t="inlineStr"/>
-      <c r="AW46" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>124808143</v>
-      </c>
-      <c r="B47" t="n">
-        <v>57657</v>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E47" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>Åkerån, Jmt</t>
-        </is>
-      </c>
-      <c r="Q47" t="n">
-        <v>466291</v>
-      </c>
-      <c r="R47" t="n">
-        <v>7056076</v>
-      </c>
-      <c r="S47" t="n">
-        <v>10</v>
-      </c>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V47" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W47" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y47" t="inlineStr">
-        <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AA47" t="inlineStr">
-        <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
-      <c r="AD47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT47" t="inlineStr"/>
-      <c r="AW47" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>124808157</v>
-      </c>
-      <c r="B48" t="n">
-        <v>57657</v>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E48" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>Åkerån, Jmt</t>
-        </is>
-      </c>
-      <c r="Q48" t="n">
-        <v>466023</v>
-      </c>
-      <c r="R48" t="n">
-        <v>7055706</v>
-      </c>
-      <c r="S48" t="n">
-        <v>10</v>
-      </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W48" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y48" t="inlineStr">
-        <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AA48" t="inlineStr">
-        <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
-      <c r="AD48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT48" t="inlineStr"/>
-      <c r="AW48" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY48" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 11097-2024 artfynd.xlsx
+++ b/artfynd/A 11097-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY41"/>
+  <dimension ref="A1:AZ41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124808183</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124808123</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124808182</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124808184</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124808185</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1267,6 +1297,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124808125</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1369,6 +1404,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124808126</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1471,6 +1511,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124808127</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1573,6 +1618,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124808129</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1675,6 +1725,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124808131</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1777,6 +1832,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124808132</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1879,6 +1939,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124808133</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1981,6 +2046,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124808134</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2083,6 +2153,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124808135</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2185,6 +2260,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124808136</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2287,6 +2367,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124808137</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2389,6 +2474,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124808138</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2491,6 +2581,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124808139</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2593,6 +2688,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124808140</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2695,6 +2795,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124808141</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2797,6 +2902,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124808142</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2899,6 +3009,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124808143</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3001,6 +3116,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124808144</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3103,6 +3223,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124808145</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3205,6 +3330,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124808146</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3307,6 +3437,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124808147</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3409,6 +3544,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124808148</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3511,6 +3651,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124808149</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3613,6 +3758,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124808150</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3715,6 +3865,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124808151</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3817,6 +3972,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124808152</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3919,6 +4079,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124808154</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4021,6 +4186,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124808155</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4123,6 +4293,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124808156</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4225,6 +4400,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124808157</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4327,6 +4507,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124808158</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4429,6 +4614,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124808159</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4531,6 +4721,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124808160</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4633,6 +4828,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124808161</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4735,8 +4935,55 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124808162</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>